--- a/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
+++ b/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
@@ -409,9 +409,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -835,7 +841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB597D2-6ED2-451E-B556-BCBE59DEB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A556D134-D782-4EA3-9011-4A25D0C1B9A7}">
   <dimension ref="A1:G248"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
+++ b/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="74">
   <si>
     <t>Sor/Spec Code</t>
   </si>
@@ -225,6 +225,18 @@
   </si>
   <si>
     <t>Say ₹ 684.94 + 169.38 x Cost Index</t>
+  </si>
+  <si>
+    <t>Supply &amp; laying of one number PVC insulated and PVC sheathed armoured copper power cable of 1.1KV grade of the following sizes in ground including excavation of trench of size 35 x 75 cm, refilling the trench etc. as required but excluding sand cushioning and protective covering (in ordinary soil). 4 core 10 sq mm (90.12.37.33)</t>
+  </si>
+  <si>
+    <t>MR858</t>
+  </si>
+  <si>
+    <t>10 sqmm 4 core PVC /XLPE insulated armoured cable with copper conductors for working voltages up to and including 1100 volts conforming IS 1584/part I/ 1988 for PVC IS 7098 part I for XLPE</t>
+  </si>
+  <si>
+    <t>Say ₹ 633.78 + 169.38 x Cost Index</t>
   </si>
 </sst>
 </file>
@@ -234,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="177" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -245,6 +257,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
@@ -261,18 +287,17 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Cambria"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -295,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -375,77 +400,103 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -457,14 +508,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -841,11 +907,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A556D134-D782-4EA3-9011-4A25D0C1B9A7}">
-  <dimension ref="A1:G248"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1250D54E-3823-45FF-A7AC-1C0D06A4BAA6}">
+  <dimension ref="A1:H279"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="12.75">
+    <row r="1" spans="1:8" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,28 +927,30 @@
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" ht="12.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="12.75">
-      <c r="A3" s="7" t="s">
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3"/>
@@ -891,29 +959,31 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" ht="12.75">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="10">
         <v>50</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:7" ht="12.75">
-      <c r="A5" s="8" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:8" ht="12.75">
+      <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="3"/>
@@ -921,9 +991,10 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="12.75">
-      <c r="A6" s="9" t="s">
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="12.75">
+      <c r="A6" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="3"/>
@@ -932,393 +1003,424 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="12.75">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11" t="s">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" ht="12.75">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="15" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="12"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" ht="12.75">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="13" t="s">
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="12.75">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="17">
         <v>50</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="17">
         <v>118.64</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="17">
         <f>D8*E8</f>
         <v>5932</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="12.75">
-      <c r="A9" s="11" t="s">
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" ht="12.75">
+      <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="12"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="12.75">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="13" t="s">
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="12.75">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17">
         <f>F8*5%</f>
         <v>296.60</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="12.75">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11" t="s">
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="12.75">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="12.75">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="13" t="s">
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="12.75">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="17">
         <v>7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="17">
         <v>675</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="17">
         <f>D12*E12</f>
         <v>4725</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="12.75">
-      <c r="A13" s="11" t="s">
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="12.75">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="12"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="12.75">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="13" t="s">
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" ht="12.75">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17">
         <f>(F8+F10+F12)*1%</f>
         <v>109.536</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="12.75">
-      <c r="A15" s="9" t="s">
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" ht="12.75">
+      <c r="A15" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="8">
+      <c r="D15" s="10">
         <v>50</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="10">
         <f>F8+F10+F12+F14</f>
         <v>11063.136</v>
       </c>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:7" ht="12.75">
-      <c r="A16" s="9" t="s">
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" ht="12.75">
+      <c r="A16" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="8">
+      <c r="D16" s="10">
         <v>1</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="10">
         <f>F15/D15</f>
         <v>221.26272</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7" ht="12.75">
-      <c r="A17" s="9" t="s">
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:8" ht="12.75">
+      <c r="A17" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="15">
+      <c r="E17" s="19">
         <f>F8*105%*101%/D15</f>
         <v>125.81771999999999</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="10">
         <f>E17*1%</f>
         <v>1.2581772</v>
       </c>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7" ht="12.75">
-      <c r="A18" s="9" t="s">
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" ht="12.75">
+      <c r="A18" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8">
+      <c r="E18" s="10"/>
+      <c r="F18" s="10">
         <f>F16+F17</f>
         <v>222.52089720000001</v>
       </c>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:7" ht="12.75">
-      <c r="A19" s="9" t="s">
+      <c r="G18" s="10"/>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:8" ht="12.75">
+      <c r="A19" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="8">
+      <c r="E19" s="10">
         <f>F18</f>
         <v>222.52089720000001</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="10">
         <f>E19*15%</f>
         <v>33.378134580000001</v>
       </c>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:7" ht="12.75">
-      <c r="A20" s="16" t="s">
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="1:8" ht="12.75">
+      <c r="A20" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="17">
+      <c r="E20" s="10"/>
+      <c r="F20" s="21">
         <f>ROUND(F18+F19,2)</f>
         <v>255.90</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7" ht="12.75">
-      <c r="A21" s="11">
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:8" ht="12.75">
+      <c r="A21" s="14">
         <v>1001</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="13"/>
+      <c r="C21" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" ht="12.75">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="13" t="s">
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="1:8" ht="12.75">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="17">
         <v>1</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="17">
         <v>806</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="17">
         <f>E22*D22</f>
         <v>806</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="12.75">
-      <c r="A23" s="11" t="s">
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="1:8" ht="12.75">
+      <c r="A23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7" ht="12.75">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="13" t="s">
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8" ht="12.75">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17">
         <f>F22*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="12.75">
-      <c r="A25" s="13">
+      <c r="H24" s="16">
+        <f>F24+F14</f>
+        <v>117.596</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="12.75">
+      <c r="A25" s="17">
         <v>14.40</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="12" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="26" spans="1:7" ht="12.75">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13" t="s">
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="16"/>
+    </row>
+    <row r="26" spans="1:8" ht="12.75">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="17">
         <v>13.13</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="17">
         <v>498.87</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="17">
         <f>D26*E26</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="12.75">
-      <c r="A27" s="9" t="s">
+      <c r="H26" s="16"/>
+    </row>
+    <row r="27" spans="1:8" ht="12.75">
+      <c r="A27" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="8">
+      <c r="D27" s="10">
         <v>50</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="10">
         <f>F22+F24+F26</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" ht="12.75">
-      <c r="A28" s="9" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:8" ht="12.75">
+      <c r="A28" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="8">
+      <c r="D28" s="10">
         <v>1</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="10">
         <f>F27/D27</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" ht="12.75">
-      <c r="A29" s="9" t="s">
+      <c r="G28" s="10"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" ht="12.75">
+      <c r="A29" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="8">
+      <c r="E29" s="10">
         <f>F28</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="10">
         <f>E29*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" ht="12.75">
-      <c r="A30" s="16" t="s">
+      <c r="G29" s="10"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="1:8" ht="12.75">
+      <c r="A30" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="17">
+      <c r="E30" s="10"/>
+      <c r="F30" s="21">
         <f>ROUND(F28+F29,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:7" ht="12.75">
-      <c r="A31" s="18" t="s">
+      <c r="G30" s="10"/>
+      <c r="H30" s="11">
+        <f>F30+F20</f>
+        <v>425.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="12.75">
+      <c r="A31" s="22" t="s">
         <v>40</v>
       </c>
       <c r="B31" s="3"/>
@@ -1326,11 +1428,12 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="12.75">
+      <c r="H31" s="23"/>
+    </row>
+    <row r="32" spans="1:8" ht="12.75">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,28 +1449,30 @@
         <v>3</v>
       </c>
       <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7" ht="12.75">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6" t="s">
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8" ht="12.75">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="12.75">
-      <c r="A34" s="7" t="s">
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" ht="12.75">
+      <c r="A34" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="3"/>
@@ -1376,29 +1481,31 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="4"/>
-    </row>
-    <row r="35" spans="1:7" ht="12.75">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8" t="s">
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8" ht="12.75">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="10">
         <v>50</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-    </row>
-    <row r="36" spans="1:7" ht="12.75">
-      <c r="A36" s="8" t="s">
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="1:8" ht="12.75">
+      <c r="A36" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="3"/>
@@ -1406,9 +1513,10 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7" ht="12.75">
-      <c r="A37" s="9" t="s">
+      <c r="H36" s="11"/>
+    </row>
+    <row r="37" spans="1:8" ht="12.75">
+      <c r="A37" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="3"/>
@@ -1417,393 +1525,424 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="1:7" ht="12.75">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11" t="s">
+      <c r="H37" s="11"/>
+    </row>
+    <row r="38" spans="1:8" ht="12.75">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="15"/>
       <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="1:7" ht="12.75">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="13" t="s">
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" ht="12.75">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="17">
         <v>50</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="17">
         <v>159.32</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="17">
         <f>D39*E39</f>
         <v>7966</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="12.75">
-      <c r="A40" s="11" t="s">
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="1:8" ht="12.75">
+      <c r="A40" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="12" t="s">
+      <c r="B40" s="13"/>
+      <c r="C40" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="1:7" ht="12.75">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="13" t="s">
+      <c r="H40" s="16"/>
+    </row>
+    <row r="41" spans="1:8" ht="12.75">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13">
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17">
         <f>F39*5%</f>
         <v>398.30</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="12.75">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11" t="s">
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" ht="12.75">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="15"/>
       <c r="G42" s="4"/>
-    </row>
-    <row r="43" spans="1:7" ht="12.75">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="13" t="s">
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="1:8" ht="12.75">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="17">
         <v>7</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="17">
         <v>675</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="17">
         <f>D43*E43</f>
         <v>4725</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="12.75">
-      <c r="A44" s="11" t="s">
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" spans="1:8" ht="12.75">
+      <c r="A44" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="14" t="s">
+      <c r="B44" s="13"/>
+      <c r="C44" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="12"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="1:7" ht="12.75">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="13" t="s">
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="1:8" ht="12.75">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13">
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17">
         <f>(F39+F41+F43)*1%</f>
         <v>130.893</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="12.75">
-      <c r="A46" s="9" t="s">
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8" ht="12.75">
+      <c r="A46" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="8">
+      <c r="D46" s="10">
         <v>50</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="10">
         <f>F39+F41+F43+F45</f>
         <v>13220.192999999999</v>
       </c>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" spans="1:7" ht="12.75">
-      <c r="A47" s="9" t="s">
+      <c r="G46" s="10"/>
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="1:8" ht="12.75">
+      <c r="A47" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="8">
+      <c r="D47" s="10">
         <v>1</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="10">
         <f>F46/D46</f>
         <v>264.40386000000001</v>
       </c>
-      <c r="G47" s="8"/>
-    </row>
-    <row r="48" spans="1:7" ht="12.75">
-      <c r="A48" s="9" t="s">
+      <c r="G47" s="10"/>
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="1:8" ht="12.75">
+      <c r="A48" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="15">
+      <c r="E48" s="19">
         <f>F39*105%*101%/D46</f>
         <v>168.95885999999999</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="10">
         <f>E48*1%</f>
         <v>1.6895886</v>
       </c>
-      <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="1:7" ht="12.75">
-      <c r="A49" s="9" t="s">
+      <c r="G48" s="10"/>
+      <c r="H48" s="11"/>
+    </row>
+    <row r="49" spans="1:8" ht="12.75">
+      <c r="A49" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8">
+      <c r="E49" s="10"/>
+      <c r="F49" s="10">
         <f>F47+F48</f>
         <v>266.09344859999999</v>
       </c>
-      <c r="G49" s="8"/>
-    </row>
-    <row r="50" spans="1:7" ht="12.75">
-      <c r="A50" s="9" t="s">
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="1:8" ht="12.75">
+      <c r="A50" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="8">
+      <c r="E50" s="10">
         <f>F49</f>
         <v>266.09344859999999</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="10">
         <f>E50*15%</f>
         <v>39.914017289999997</v>
       </c>
-      <c r="G50" s="8"/>
-    </row>
-    <row r="51" spans="1:7" ht="12.75">
-      <c r="A51" s="16" t="s">
+      <c r="G50" s="10"/>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="1:8" ht="12.75">
+      <c r="A51" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="17">
+      <c r="E51" s="10"/>
+      <c r="F51" s="21">
         <f>ROUND(F49+F50,2)</f>
         <v>306.01</v>
       </c>
-      <c r="G51" s="8"/>
-    </row>
-    <row r="52" spans="1:7" ht="12.75">
-      <c r="A52" s="11">
+      <c r="G51" s="10"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="1:8" ht="12.75">
+      <c r="A52" s="14">
         <v>1001</v>
       </c>
-      <c r="B52" s="10"/>
-      <c r="C52" s="12" t="s">
+      <c r="B52" s="13"/>
+      <c r="C52" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="12"/>
+      <c r="F52" s="15"/>
       <c r="G52" s="4"/>
-    </row>
-    <row r="53" spans="1:7" ht="12.75">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="13" t="s">
+      <c r="H52" s="16"/>
+    </row>
+    <row r="53" spans="1:8" ht="12.75">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="17">
         <v>1</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="17">
         <v>806</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="17">
         <f>E53*D53</f>
         <v>806</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="G53" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="12.75">
-      <c r="A54" s="11" t="s">
+      <c r="H53" s="16"/>
+    </row>
+    <row r="54" spans="1:8" ht="12.75">
+      <c r="A54" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="14" t="s">
+      <c r="B54" s="13"/>
+      <c r="C54" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="12"/>
+      <c r="F54" s="15"/>
       <c r="G54" s="4"/>
-    </row>
-    <row r="55" spans="1:7" ht="12.75">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="13" t="s">
+      <c r="H54" s="16"/>
+    </row>
+    <row r="55" spans="1:8" ht="12.75">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13">
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17">
         <f>F53*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="12.75">
-      <c r="A56" s="13">
+      <c r="H55" s="16">
+        <f>F55+F45</f>
+        <v>138.953</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="12.75">
+      <c r="A56" s="17">
         <v>14.40</v>
       </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="12" t="s">
+      <c r="B56" s="17"/>
+      <c r="C56" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-    </row>
-    <row r="57" spans="1:7" ht="12.75">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13" t="s">
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="16"/>
+    </row>
+    <row r="57" spans="1:8" ht="12.75">
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="17">
         <v>13.13</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="17">
         <v>498.87</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="17">
         <f>D57*E57</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="12.75">
-      <c r="A58" s="9" t="s">
+      <c r="H57" s="16"/>
+    </row>
+    <row r="58" spans="1:8" ht="12.75">
+      <c r="A58" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="8">
+      <c r="D58" s="10">
         <v>50</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="10">
         <f>F53+F55+F57</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G58" s="8"/>
-    </row>
-    <row r="59" spans="1:7" ht="12.75">
-      <c r="A59" s="9" t="s">
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
+    </row>
+    <row r="59" spans="1:8" ht="12.75">
+      <c r="A59" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="8">
+      <c r="D59" s="10">
         <v>1</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="10">
         <f>F58/D58</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G59" s="8"/>
-    </row>
-    <row r="60" spans="1:7" ht="12.75">
-      <c r="A60" s="9" t="s">
+      <c r="G59" s="10"/>
+      <c r="H59" s="11"/>
+    </row>
+    <row r="60" spans="1:8" ht="12.75">
+      <c r="A60" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="8">
+      <c r="E60" s="10">
         <f>F59</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="10">
         <f>E60*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G60" s="8"/>
-    </row>
-    <row r="61" spans="1:7" ht="12.75">
-      <c r="A61" s="16" t="s">
+      <c r="G60" s="10"/>
+      <c r="H60" s="11"/>
+    </row>
+    <row r="61" spans="1:8" ht="12.75">
+      <c r="A61" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="17">
+      <c r="E61" s="10"/>
+      <c r="F61" s="21">
         <f>ROUND(F59+F60,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G61" s="8"/>
-    </row>
-    <row r="62" spans="1:7" ht="12.75">
-      <c r="A62" s="18" t="s">
+      <c r="G61" s="10"/>
+      <c r="H61" s="11">
+        <f>F61+F51</f>
+        <v>475.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="12.75">
+      <c r="A62" s="22" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="3"/>
@@ -1811,11 +1950,12 @@
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="12.75">
+      <c r="H62" s="23"/>
+    </row>
+    <row r="63" spans="1:8" ht="12.75">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
@@ -1831,28 +1971,30 @@
         <v>3</v>
       </c>
       <c r="G63" s="4"/>
-    </row>
-    <row r="64" spans="1:7" ht="12.75">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="6" t="s">
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:8" ht="12.75">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="12.75">
-      <c r="A65" s="7" t="s">
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="1:8" ht="12.75">
+      <c r="A65" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B65" s="3"/>
@@ -1861,29 +2003,31 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="4"/>
-    </row>
-    <row r="66" spans="1:7" ht="12.75">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8" t="s">
+      <c r="H65" s="9"/>
+    </row>
+    <row r="66" spans="1:8" ht="12.75">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="10">
         <v>50</v>
       </c>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-    </row>
-    <row r="67" spans="1:7" ht="12.75">
-      <c r="A67" s="8" t="s">
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="11"/>
+    </row>
+    <row r="67" spans="1:8" ht="12.75">
+      <c r="A67" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="3"/>
@@ -1891,9 +2035,10 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="4"/>
-    </row>
-    <row r="68" spans="1:7" ht="12.75">
-      <c r="A68" s="9" t="s">
+      <c r="H67" s="11"/>
+    </row>
+    <row r="68" spans="1:8" ht="12.75">
+      <c r="A68" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B68" s="3"/>
@@ -1902,393 +2047,430 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="4"/>
-    </row>
-    <row r="69" spans="1:7" ht="12.75">
-      <c r="A69" s="10"/>
-      <c r="B69" s="11" t="s">
+      <c r="H68" s="11"/>
+    </row>
+    <row r="69" spans="1:8" ht="12.75">
+      <c r="A69" s="13"/>
+      <c r="B69" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="15" t="s">
         <v>48</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="12"/>
+      <c r="F69" s="15"/>
       <c r="G69" s="4"/>
-    </row>
-    <row r="70" spans="1:7" ht="12.75">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="13" t="s">
+      <c r="H69" s="16"/>
+    </row>
+    <row r="70" spans="1:8" ht="12.75">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70" s="17">
         <v>50</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="17">
         <v>241.53</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="17">
         <f>D70*E70</f>
         <v>12076.50</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="12.75">
-      <c r="A71" s="11" t="s">
+      <c r="H70" s="16"/>
+    </row>
+    <row r="71" spans="1:8" ht="12.75">
+      <c r="A71" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="12" t="s">
+      <c r="B71" s="13"/>
+      <c r="C71" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="12"/>
+      <c r="F71" s="15"/>
       <c r="G71" s="4"/>
-    </row>
-    <row r="72" spans="1:7" ht="12.75">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="13" t="s">
+      <c r="H71" s="16"/>
+    </row>
+    <row r="72" spans="1:8" ht="12.75">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13">
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17">
         <f>F70*5%</f>
         <v>603.825</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="12.75">
-      <c r="A73" s="10"/>
-      <c r="B73" s="11" t="s">
+      <c r="H72" s="16"/>
+    </row>
+    <row r="73" spans="1:8" ht="12.75">
+      <c r="A73" s="13"/>
+      <c r="B73" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="12"/>
+      <c r="F73" s="15"/>
       <c r="G73" s="4"/>
-    </row>
-    <row r="74" spans="1:7" ht="12.75">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="13" t="s">
+      <c r="H73" s="16"/>
+    </row>
+    <row r="74" spans="1:8" ht="12.75">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D74" s="17">
         <v>7</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="17">
         <v>675</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="17">
         <f>D74*E74</f>
         <v>4725</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="G74" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="12.75">
-      <c r="A75" s="11" t="s">
+      <c r="H74" s="16"/>
+    </row>
+    <row r="75" spans="1:8" ht="12.75">
+      <c r="A75" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="14" t="s">
+      <c r="B75" s="13"/>
+      <c r="C75" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="12"/>
+      <c r="F75" s="15"/>
       <c r="G75" s="4"/>
-    </row>
-    <row r="76" spans="1:7" ht="12.75">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="13" t="s">
+      <c r="H75" s="16"/>
+    </row>
+    <row r="76" spans="1:8" ht="12.75">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13">
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17">
         <f>(F70+F72+F74)*1%</f>
         <v>174.05324999999999</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="12.75">
-      <c r="A77" s="9" t="s">
+      <c r="H76" s="16"/>
+    </row>
+    <row r="77" spans="1:8" ht="12.75">
+      <c r="A77" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="8">
+      <c r="D77" s="10">
         <v>50</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="10">
         <f>F70+F72+F74+F76</f>
         <v>17579.378250000002</v>
       </c>
-      <c r="G77" s="8"/>
-    </row>
-    <row r="78" spans="1:7" ht="12.75">
-      <c r="A78" s="9" t="s">
+      <c r="G77" s="10"/>
+      <c r="H77" s="11"/>
+    </row>
+    <row r="78" spans="1:8" ht="12.75">
+      <c r="A78" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="8">
+      <c r="D78" s="10">
         <v>1</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="10">
         <f>F77/D77</f>
         <v>351.58756499999998</v>
       </c>
-      <c r="G78" s="8"/>
-    </row>
-    <row r="79" spans="1:7" ht="12.75">
-      <c r="A79" s="9" t="s">
+      <c r="G78" s="10"/>
+      <c r="H78" s="11"/>
+    </row>
+    <row r="79" spans="1:8" ht="12.75">
+      <c r="A79" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="15">
+      <c r="E79" s="19">
         <f>F70*105%*101%/D77</f>
         <v>256.14256499999999</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="10">
         <f>E79*1%</f>
         <v>2.5614256499999999</v>
       </c>
-      <c r="G79" s="8"/>
-    </row>
-    <row r="80" spans="1:7" ht="12.75">
-      <c r="A80" s="9" t="s">
+      <c r="G79" s="10"/>
+      <c r="H79" s="11"/>
+    </row>
+    <row r="80" spans="1:8" ht="12.75">
+      <c r="A80" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8">
+      <c r="E80" s="10"/>
+      <c r="F80" s="10">
         <f>F78+F79</f>
         <v>354.14899070000001</v>
       </c>
-      <c r="G80" s="8"/>
-    </row>
-    <row r="81" spans="1:7" ht="12.75">
-      <c r="A81" s="9" t="s">
+      <c r="G80" s="10"/>
+      <c r="H80" s="11"/>
+    </row>
+    <row r="81" spans="1:8" ht="12.75">
+      <c r="A81" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="8">
+      <c r="E81" s="10">
         <f>F80</f>
         <v>354.14899070000001</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="10">
         <f>E81*15%</f>
         <v>53.122348600000002</v>
       </c>
-      <c r="G81" s="8"/>
-    </row>
-    <row r="82" spans="1:7" ht="12.75">
-      <c r="A82" s="16" t="s">
+      <c r="G81" s="10"/>
+      <c r="H81" s="11"/>
+    </row>
+    <row r="82" spans="1:8" ht="12.75">
+      <c r="A82" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="17">
+      <c r="E82" s="10"/>
+      <c r="F82" s="21">
         <f>ROUND(F80+F81,2)</f>
         <v>407.27</v>
       </c>
-      <c r="G82" s="8"/>
-    </row>
-    <row r="83" spans="1:7" ht="12.75">
-      <c r="A83" s="11">
+      <c r="G82" s="10"/>
+      <c r="H82" s="11"/>
+    </row>
+    <row r="83" spans="1:8" ht="12.75">
+      <c r="A83" s="14">
         <v>1001</v>
       </c>
-      <c r="B83" s="10"/>
-      <c r="C83" s="12" t="s">
+      <c r="B83" s="13"/>
+      <c r="C83" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="12"/>
+      <c r="F83" s="15"/>
       <c r="G83" s="4"/>
-    </row>
-    <row r="84" spans="1:7" ht="12.75">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="13" t="s">
+      <c r="H83" s="16"/>
+    </row>
+    <row r="84" spans="1:8" ht="12.75">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D84" s="13">
+      <c r="D84" s="17">
         <v>1</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="17">
         <v>806</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="17">
         <f>E84*D84</f>
         <v>806</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="G84" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="12.75">
-      <c r="A85" s="11" t="s">
+      <c r="H84" s="16"/>
+    </row>
+    <row r="85" spans="1:8" ht="12.75">
+      <c r="A85" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="10"/>
-      <c r="C85" s="14" t="s">
+      <c r="B85" s="13"/>
+      <c r="C85" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="12"/>
+      <c r="F85" s="15"/>
       <c r="G85" s="4"/>
-    </row>
-    <row r="86" spans="1:7" ht="12.75">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="13" t="s">
+      <c r="H85" s="16"/>
+    </row>
+    <row r="86" spans="1:8" ht="12.75">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13">
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17">
         <f>F84*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="G86" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="12.75">
-      <c r="A87" s="13">
+      <c r="H86" s="16">
+        <f>F86+F76</f>
+        <v>182.11324999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="12.75">
+      <c r="A87" s="17">
         <v>14.40</v>
       </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="12" t="s">
+      <c r="B87" s="17"/>
+      <c r="C87" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-    </row>
-    <row r="88" spans="1:7" ht="12.75">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13" t="s">
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="16"/>
+    </row>
+    <row r="88" spans="1:8" ht="12.75">
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="13">
+      <c r="D88" s="17">
         <v>13.13</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="17">
         <v>498.87</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="17">
         <f>D88*E88</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G88" s="13" t="s">
+      <c r="G88" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="12.75">
-      <c r="A89" s="9" t="s">
+      <c r="H88" s="16"/>
+    </row>
+    <row r="89" spans="1:8" ht="12.75">
+      <c r="A89" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="8">
+      <c r="D89" s="10">
         <v>50</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E89" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="10">
         <f>F84+F86+F88</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G89" s="8"/>
-    </row>
-    <row r="90" spans="1:7" ht="12.75">
-      <c r="A90" s="9" t="s">
+      <c r="G89" s="10"/>
+      <c r="H89" s="11"/>
+    </row>
+    <row r="90" spans="1:8" ht="12.75">
+      <c r="A90" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="8">
+      <c r="D90" s="10">
         <v>1</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="10">
         <f>F89/D89</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G90" s="8"/>
-    </row>
-    <row r="91" spans="1:7" ht="12.75">
-      <c r="A91" s="9" t="s">
+      <c r="G90" s="10"/>
+      <c r="H90" s="11">
+        <f>F90+F80</f>
+        <v>501.43345269999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="12.75">
+      <c r="A91" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="8">
+      <c r="E91" s="10">
         <f>F90</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="10">
         <f>E91*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G91" s="8"/>
-    </row>
-    <row r="92" spans="1:7" ht="12.75">
-      <c r="A92" s="16" t="s">
+      <c r="G91" s="10"/>
+      <c r="H91" s="11">
+        <f>F91+F81</f>
+        <v>75.215017900000007</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="12.75">
+      <c r="A92" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="17">
+      <c r="E92" s="10"/>
+      <c r="F92" s="21">
         <f>ROUND(F90+F91,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G92" s="8"/>
-    </row>
-    <row r="93" spans="1:7" ht="12.75">
-      <c r="A93" s="18" t="s">
+      <c r="G92" s="10"/>
+      <c r="H92" s="11">
+        <f>F92+F82</f>
+        <v>576.65</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="12.75">
+      <c r="A93" s="22" t="s">
         <v>49</v>
       </c>
       <c r="B93" s="3"/>
@@ -2296,11 +2478,12 @@
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="17" t="s">
+      <c r="G93" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="12.75">
+      <c r="H93" s="23"/>
+    </row>
+    <row r="94" spans="1:8" ht="12.75">
       <c r="A94" s="1" t="s">
         <v>0</v>
       </c>
@@ -2316,28 +2499,30 @@
         <v>3</v>
       </c>
       <c r="G94" s="4"/>
-    </row>
-    <row r="95" spans="1:7" ht="12.75">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="6" t="s">
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="1:8" ht="12.75">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="E95" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G95" s="6" t="s">
+      <c r="G95" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="12.75">
-      <c r="A96" s="7" t="s">
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8" ht="12.75">
+      <c r="A96" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B96" s="3"/>
@@ -2346,29 +2531,31 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="4"/>
-    </row>
-    <row r="97" spans="1:7" ht="12.75">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8" t="s">
+      <c r="H96" s="9"/>
+    </row>
+    <row r="97" spans="1:8" ht="12.75">
+      <c r="A97" s="10"/>
+      <c r="B97" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="10">
         <v>50</v>
       </c>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-    </row>
-    <row r="98" spans="1:7" ht="12.75">
-      <c r="A98" s="8" t="s">
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="11"/>
+    </row>
+    <row r="98" spans="1:8" ht="12.75">
+      <c r="A98" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C98" s="3"/>
@@ -2376,9 +2563,10 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="4"/>
-    </row>
-    <row r="99" spans="1:7" ht="12.75">
-      <c r="A99" s="9" t="s">
+      <c r="H98" s="11"/>
+    </row>
+    <row r="99" spans="1:8" ht="12.75">
+      <c r="A99" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B99" s="3"/>
@@ -2387,393 +2575,424 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="4"/>
-    </row>
-    <row r="100" spans="1:7" ht="12.75">
-      <c r="A100" s="10"/>
-      <c r="B100" s="11" t="s">
+      <c r="H99" s="11"/>
+    </row>
+    <row r="100" spans="1:8" ht="12.75">
+      <c r="A100" s="13"/>
+      <c r="B100" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="15" t="s">
         <v>52</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="12"/>
+      <c r="F100" s="15"/>
       <c r="G100" s="4"/>
-    </row>
-    <row r="101" spans="1:7" ht="12.75">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="13" t="s">
+      <c r="H100" s="16"/>
+    </row>
+    <row r="101" spans="1:8" ht="12.75">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D101" s="13">
+      <c r="D101" s="17">
         <v>50</v>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="17">
         <v>343.22</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="17">
         <f>D101*E101</f>
         <v>17161</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="12.75">
-      <c r="A102" s="11" t="s">
+      <c r="H101" s="16"/>
+    </row>
+    <row r="102" spans="1:8" ht="12.75">
+      <c r="A102" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B102" s="10"/>
-      <c r="C102" s="12" t="s">
+      <c r="B102" s="13"/>
+      <c r="C102" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="4"/>
-      <c r="F102" s="12"/>
+      <c r="F102" s="15"/>
       <c r="G102" s="4"/>
-    </row>
-    <row r="103" spans="1:7" ht="12.75">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="13" t="s">
+      <c r="H102" s="16"/>
+    </row>
+    <row r="103" spans="1:8" ht="12.75">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13">
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17">
         <f>F101*5%</f>
         <v>858.05</v>
       </c>
-      <c r="G103" s="13" t="s">
+      <c r="G103" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="12.75">
-      <c r="A104" s="10"/>
-      <c r="B104" s="11" t="s">
+      <c r="H103" s="16"/>
+    </row>
+    <row r="104" spans="1:8" ht="12.75">
+      <c r="A104" s="13"/>
+      <c r="B104" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
-      <c r="F104" s="12"/>
+      <c r="F104" s="15"/>
       <c r="G104" s="4"/>
-    </row>
-    <row r="105" spans="1:7" ht="12.75">
-      <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="13" t="s">
+      <c r="H104" s="16"/>
+    </row>
+    <row r="105" spans="1:8" ht="12.75">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D105" s="13">
+      <c r="D105" s="17">
         <v>7</v>
       </c>
-      <c r="E105" s="13">
+      <c r="E105" s="17">
         <v>675</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105" s="17">
         <f>D105*E105</f>
         <v>4725</v>
       </c>
-      <c r="G105" s="13" t="s">
+      <c r="G105" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="12.75">
-      <c r="A106" s="11" t="s">
+      <c r="H105" s="16"/>
+    </row>
+    <row r="106" spans="1:8" ht="12.75">
+      <c r="A106" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B106" s="10"/>
-      <c r="C106" s="14" t="s">
+      <c r="B106" s="13"/>
+      <c r="C106" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="4"/>
-      <c r="F106" s="12"/>
+      <c r="F106" s="15"/>
       <c r="G106" s="4"/>
-    </row>
-    <row r="107" spans="1:7" ht="12.75">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="13" t="s">
+      <c r="H106" s="16"/>
+    </row>
+    <row r="107" spans="1:8" ht="12.75">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13">
+      <c r="D107" s="17"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="17">
         <f>(F101+F103+F105)*1%</f>
         <v>227.44049999999999</v>
       </c>
-      <c r="G107" s="13" t="s">
+      <c r="G107" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="12.75">
-      <c r="A108" s="9" t="s">
+      <c r="H107" s="16"/>
+    </row>
+    <row r="108" spans="1:8" ht="12.75">
+      <c r="A108" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
-      <c r="D108" s="8">
+      <c r="D108" s="10">
         <v>50</v>
       </c>
-      <c r="E108" s="8" t="s">
+      <c r="E108" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="10">
         <f>F101+F103+F105+F107</f>
         <v>22971.4905</v>
       </c>
-      <c r="G108" s="8"/>
-    </row>
-    <row r="109" spans="1:7" ht="12.75">
-      <c r="A109" s="9" t="s">
+      <c r="G108" s="10"/>
+      <c r="H108" s="11"/>
+    </row>
+    <row r="109" spans="1:8" ht="12.75">
+      <c r="A109" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
-      <c r="D109" s="8">
+      <c r="D109" s="10">
         <v>1</v>
       </c>
-      <c r="E109" s="8" t="s">
+      <c r="E109" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="10">
         <f>F108/D108</f>
         <v>459.42980999999997</v>
       </c>
-      <c r="G109" s="8"/>
-    </row>
-    <row r="110" spans="1:7" ht="12.75">
-      <c r="A110" s="9" t="s">
+      <c r="G109" s="10"/>
+      <c r="H109" s="11"/>
+    </row>
+    <row r="110" spans="1:8" ht="12.75">
+      <c r="A110" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="4"/>
-      <c r="E110" s="15">
+      <c r="E110" s="19">
         <f>F101*105%*101%/D108</f>
         <v>363.98480999999998</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="10">
         <f>E110*1%</f>
         <v>3.6398481</v>
       </c>
-      <c r="G110" s="8"/>
-    </row>
-    <row r="111" spans="1:7" ht="12.75">
-      <c r="A111" s="9" t="s">
+      <c r="G110" s="10"/>
+      <c r="H110" s="11"/>
+    </row>
+    <row r="111" spans="1:8" ht="12.75">
+      <c r="A111" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="4"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8">
+      <c r="E111" s="10"/>
+      <c r="F111" s="10">
         <f>F109+F110</f>
         <v>463.06965810000003</v>
       </c>
-      <c r="G111" s="8"/>
-    </row>
-    <row r="112" spans="1:7" ht="12.75">
-      <c r="A112" s="9" t="s">
+      <c r="G111" s="10"/>
+      <c r="H111" s="11"/>
+    </row>
+    <row r="112" spans="1:8" ht="12.75">
+      <c r="A112" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="4"/>
-      <c r="E112" s="8">
+      <c r="E112" s="10">
         <f>F111</f>
         <v>463.06965810000003</v>
       </c>
-      <c r="F112" s="8">
+      <c r="F112" s="10">
         <f>E112*15%</f>
         <v>69.460448720000002</v>
       </c>
-      <c r="G112" s="8"/>
-    </row>
-    <row r="113" spans="1:7" ht="12.75">
-      <c r="A113" s="16" t="s">
+      <c r="G112" s="10"/>
+      <c r="H112" s="11"/>
+    </row>
+    <row r="113" spans="1:8" ht="12.75">
+      <c r="A113" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="4"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="17">
+      <c r="E113" s="10"/>
+      <c r="F113" s="21">
         <f>ROUND(F111+F112,2)</f>
         <v>532.53</v>
       </c>
-      <c r="G113" s="8"/>
-    </row>
-    <row r="114" spans="1:7" ht="12.75">
-      <c r="A114" s="11">
+      <c r="G113" s="10"/>
+      <c r="H113" s="11"/>
+    </row>
+    <row r="114" spans="1:8" ht="12.75">
+      <c r="A114" s="14">
         <v>1001</v>
       </c>
-      <c r="B114" s="10"/>
-      <c r="C114" s="12" t="s">
+      <c r="B114" s="13"/>
+      <c r="C114" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="4"/>
-      <c r="F114" s="12"/>
+      <c r="F114" s="15"/>
       <c r="G114" s="4"/>
-    </row>
-    <row r="115" spans="1:7" ht="12.75">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="13" t="s">
+      <c r="H114" s="16"/>
+    </row>
+    <row r="115" spans="1:8" ht="12.75">
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D115" s="13">
+      <c r="D115" s="17">
         <v>1</v>
       </c>
-      <c r="E115" s="13">
+      <c r="E115" s="17">
         <v>806</v>
       </c>
-      <c r="F115" s="13">
+      <c r="F115" s="17">
         <f>E115*D115</f>
         <v>806</v>
       </c>
-      <c r="G115" s="13" t="s">
+      <c r="G115" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="12.75">
-      <c r="A116" s="11" t="s">
+      <c r="H115" s="16"/>
+    </row>
+    <row r="116" spans="1:8" ht="12.75">
+      <c r="A116" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="10"/>
-      <c r="C116" s="14" t="s">
+      <c r="B116" s="13"/>
+      <c r="C116" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="4"/>
-      <c r="F116" s="12"/>
+      <c r="F116" s="15"/>
       <c r="G116" s="4"/>
-    </row>
-    <row r="117" spans="1:7" ht="12.75">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="13" t="s">
+      <c r="H116" s="16"/>
+    </row>
+    <row r="117" spans="1:8" ht="12.75">
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
-      <c r="F117" s="13">
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="17">
         <f>F115*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G117" s="13" t="s">
+      <c r="G117" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="12.75">
-      <c r="A118" s="13">
+      <c r="H117" s="16">
+        <f>F117+F107</f>
+        <v>235.50049999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="12.75">
+      <c r="A118" s="17">
         <v>14.40</v>
       </c>
-      <c r="B118" s="13"/>
-      <c r="C118" s="12" t="s">
+      <c r="B118" s="17"/>
+      <c r="C118" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="4"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-    </row>
-    <row r="119" spans="1:7" ht="12.75">
-      <c r="A119" s="13"/>
-      <c r="B119" s="13"/>
-      <c r="C119" s="13" t="s">
+      <c r="F118" s="17"/>
+      <c r="G118" s="17"/>
+      <c r="H118" s="16"/>
+    </row>
+    <row r="119" spans="1:8" ht="12.75">
+      <c r="A119" s="17"/>
+      <c r="B119" s="17"/>
+      <c r="C119" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D119" s="13">
+      <c r="D119" s="17">
         <v>13.13</v>
       </c>
-      <c r="E119" s="13">
+      <c r="E119" s="17">
         <v>498.87</v>
       </c>
-      <c r="F119" s="13">
+      <c r="F119" s="17">
         <f>D119*E119</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G119" s="13" t="s">
+      <c r="G119" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="12.75">
-      <c r="A120" s="9" t="s">
+      <c r="H119" s="16"/>
+    </row>
+    <row r="120" spans="1:8" ht="12.75">
+      <c r="A120" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="8">
+      <c r="D120" s="10">
         <v>50</v>
       </c>
-      <c r="E120" s="8" t="s">
+      <c r="E120" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="10">
         <f>F115+F117+F119</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G120" s="8"/>
-    </row>
-    <row r="121" spans="1:7" ht="12.75">
-      <c r="A121" s="9" t="s">
+      <c r="G120" s="10"/>
+      <c r="H120" s="11"/>
+    </row>
+    <row r="121" spans="1:8" ht="12.75">
+      <c r="A121" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="8">
+      <c r="D121" s="10">
         <v>1</v>
       </c>
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="10">
         <f>F120/D120</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G121" s="8"/>
-    </row>
-    <row r="122" spans="1:7" ht="12.75">
-      <c r="A122" s="9" t="s">
+      <c r="G121" s="10"/>
+      <c r="H121" s="11"/>
+    </row>
+    <row r="122" spans="1:8" ht="12.75">
+      <c r="A122" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="4"/>
-      <c r="E122" s="8">
+      <c r="E122" s="10">
         <f>F121</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="10">
         <f>E122*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G122" s="8"/>
-    </row>
-    <row r="123" spans="1:7" ht="12.75">
-      <c r="A123" s="16" t="s">
+      <c r="G122" s="10"/>
+      <c r="H122" s="11"/>
+    </row>
+    <row r="123" spans="1:8" ht="12.75">
+      <c r="A123" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="4"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="17">
+      <c r="E123" s="10"/>
+      <c r="F123" s="21">
         <f>ROUND(F121+F122,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G123" s="8"/>
-    </row>
-    <row r="124" spans="1:7" ht="12.75">
-      <c r="A124" s="18" t="s">
+      <c r="G123" s="10"/>
+      <c r="H123" s="11">
+        <f>F123+F113</f>
+        <v>701.91</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="12.75">
+      <c r="A124" s="22" t="s">
         <v>53</v>
       </c>
       <c r="B124" s="3"/>
@@ -2781,11 +3000,12 @@
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="4"/>
-      <c r="G124" s="17" t="s">
+      <c r="G124" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="12.75">
+      <c r="H124" s="23"/>
+    </row>
+    <row r="125" spans="1:8" ht="12.75">
       <c r="A125" s="1" t="s">
         <v>0</v>
       </c>
@@ -2801,28 +3021,30 @@
         <v>3</v>
       </c>
       <c r="G125" s="4"/>
-    </row>
-    <row r="126" spans="1:7" ht="12.75">
-      <c r="A126" s="5"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="6" t="s">
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="1:8" ht="12.75">
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E126" s="6" t="s">
+      <c r="E126" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G126" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="12.75">
-      <c r="A127" s="7" t="s">
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="1:8" ht="12.75">
+      <c r="A127" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="3"/>
@@ -2831,29 +3053,31 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="4"/>
-    </row>
-    <row r="128" spans="1:7" ht="12.75">
-      <c r="A128" s="8"/>
-      <c r="B128" s="8" t="s">
+      <c r="H127" s="9"/>
+    </row>
+    <row r="128" spans="1:8" ht="12.75">
+      <c r="A128" s="10"/>
+      <c r="B128" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D128" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="10">
         <v>50</v>
       </c>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
-    </row>
-    <row r="129" spans="1:7" ht="12.75">
-      <c r="A129" s="8" t="s">
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
+      <c r="H128" s="11"/>
+    </row>
+    <row r="129" spans="1:8" ht="12.75">
+      <c r="A129" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B129" s="9" t="s">
+      <c r="B129" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="3"/>
@@ -2861,9 +3085,10 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="4"/>
-    </row>
-    <row r="130" spans="1:7" ht="12.75">
-      <c r="A130" s="9" t="s">
+      <c r="H129" s="11"/>
+    </row>
+    <row r="130" spans="1:8" ht="12.75">
+      <c r="A130" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B130" s="3"/>
@@ -2872,393 +3097,427 @@
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="4"/>
-    </row>
-    <row r="131" spans="1:7" ht="12.75">
-      <c r="A131" s="10"/>
-      <c r="B131" s="11" t="s">
+      <c r="H130" s="11"/>
+    </row>
+    <row r="131" spans="1:8" ht="12.75">
+      <c r="A131" s="13"/>
+      <c r="B131" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C131" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="4"/>
-      <c r="F131" s="12"/>
+      <c r="F131" s="15"/>
       <c r="G131" s="4"/>
-    </row>
-    <row r="132" spans="1:7" ht="12.75">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="13" t="s">
+      <c r="H131" s="16"/>
+    </row>
+    <row r="132" spans="1:8" ht="12.75">
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="13">
+      <c r="D132" s="17">
         <v>50</v>
       </c>
-      <c r="E132" s="13">
+      <c r="E132" s="17">
         <v>153.39</v>
       </c>
-      <c r="F132" s="13">
+      <c r="F132" s="17">
         <f>D132*E132</f>
         <v>7669.50</v>
       </c>
-      <c r="G132" s="13" t="s">
+      <c r="G132" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="12.75">
-      <c r="A133" s="11" t="s">
+      <c r="H132" s="16"/>
+    </row>
+    <row r="133" spans="1:8" ht="12.75">
+      <c r="A133" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B133" s="10"/>
-      <c r="C133" s="12" t="s">
+      <c r="B133" s="13"/>
+      <c r="C133" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="4"/>
-      <c r="F133" s="12"/>
+      <c r="F133" s="15"/>
       <c r="G133" s="4"/>
-    </row>
-    <row r="134" spans="1:7" ht="12.75">
-      <c r="A134" s="5"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="13" t="s">
+      <c r="H133" s="16"/>
+    </row>
+    <row r="134" spans="1:8" ht="12.75">
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13">
+      <c r="D134" s="17"/>
+      <c r="E134" s="17"/>
+      <c r="F134" s="17">
         <f>F132*5%</f>
         <v>383.475</v>
       </c>
-      <c r="G134" s="13" t="s">
+      <c r="G134" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="12.75">
-      <c r="A135" s="10"/>
-      <c r="B135" s="11" t="s">
+      <c r="H134" s="16"/>
+    </row>
+    <row r="135" spans="1:8" ht="12.75">
+      <c r="A135" s="13"/>
+      <c r="B135" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C135" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="4"/>
-      <c r="F135" s="12"/>
+      <c r="F135" s="15"/>
       <c r="G135" s="4"/>
-    </row>
-    <row r="136" spans="1:7" ht="12.75">
-      <c r="A136" s="5"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="13" t="s">
+      <c r="H135" s="16"/>
+    </row>
+    <row r="136" spans="1:8" ht="12.75">
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D136" s="13">
+      <c r="D136" s="17">
         <v>7</v>
       </c>
-      <c r="E136" s="13">
+      <c r="E136" s="17">
         <v>675</v>
       </c>
-      <c r="F136" s="13">
+      <c r="F136" s="17">
         <f>D136*E136</f>
         <v>4725</v>
       </c>
-      <c r="G136" s="13" t="s">
+      <c r="G136" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="12.75">
-      <c r="A137" s="11" t="s">
+      <c r="H136" s="16"/>
+    </row>
+    <row r="137" spans="1:8" ht="12.75">
+      <c r="A137" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B137" s="10"/>
-      <c r="C137" s="14" t="s">
+      <c r="B137" s="13"/>
+      <c r="C137" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="4"/>
-      <c r="F137" s="12"/>
+      <c r="F137" s="15"/>
       <c r="G137" s="4"/>
-    </row>
-    <row r="138" spans="1:7" ht="12.75">
-      <c r="A138" s="5"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="13" t="s">
+      <c r="H137" s="16"/>
+    </row>
+    <row r="138" spans="1:8" ht="12.75">
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
-      <c r="F138" s="13">
+      <c r="D138" s="17"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="17">
         <f>(F132+F134+F136)*1%</f>
         <v>127.77975000000001</v>
       </c>
-      <c r="G138" s="13" t="s">
+      <c r="G138" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="12.75">
-      <c r="A139" s="9" t="s">
+      <c r="H138" s="16"/>
+    </row>
+    <row r="139" spans="1:8" ht="12.75">
+      <c r="A139" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="4"/>
-      <c r="D139" s="8">
+      <c r="D139" s="10">
         <v>50</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="10">
         <f>F132+F134+F136+F138</f>
         <v>12905.75475</v>
       </c>
-      <c r="G139" s="8"/>
-    </row>
-    <row r="140" spans="1:7" ht="12.75">
-      <c r="A140" s="9" t="s">
+      <c r="G139" s="10"/>
+      <c r="H139" s="11"/>
+    </row>
+    <row r="140" spans="1:8" ht="12.75">
+      <c r="A140" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="4"/>
-      <c r="D140" s="8">
+      <c r="D140" s="10">
         <v>1</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F140" s="8">
+      <c r="F140" s="10">
         <f>F139/D139</f>
         <v>258.115095</v>
       </c>
-      <c r="G140" s="8"/>
-    </row>
-    <row r="141" spans="1:7" ht="12.75">
-      <c r="A141" s="9" t="s">
+      <c r="G140" s="10"/>
+      <c r="H140" s="11"/>
+    </row>
+    <row r="141" spans="1:8" ht="12.75">
+      <c r="A141" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="4"/>
-      <c r="E141" s="15">
+      <c r="E141" s="19">
         <f>F132*105%*101%/D139</f>
         <v>162.670095</v>
       </c>
-      <c r="F141" s="8">
+      <c r="F141" s="10">
         <f>E141*1%</f>
         <v>1.62670095</v>
       </c>
-      <c r="G141" s="8"/>
-    </row>
-    <row r="142" spans="1:7" ht="12.75">
-      <c r="A142" s="9" t="s">
+      <c r="G141" s="10"/>
+      <c r="H141" s="11"/>
+    </row>
+    <row r="142" spans="1:8" ht="12.75">
+      <c r="A142" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="4"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8">
+      <c r="E142" s="10"/>
+      <c r="F142" s="10">
         <f>F140+F141</f>
         <v>259.74179600000002</v>
       </c>
-      <c r="G142" s="8"/>
-    </row>
-    <row r="143" spans="1:7" ht="12.75">
-      <c r="A143" s="9" t="s">
+      <c r="G142" s="10"/>
+      <c r="H142" s="11"/>
+    </row>
+    <row r="143" spans="1:8" ht="12.75">
+      <c r="A143" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="8">
+      <c r="E143" s="10">
         <f>F142</f>
         <v>259.74179600000002</v>
       </c>
-      <c r="F143" s="8">
+      <c r="F143" s="10">
         <f>E143*15%</f>
         <v>38.961269389999998</v>
       </c>
-      <c r="G143" s="8"/>
-    </row>
-    <row r="144" spans="1:7" ht="12.75">
-      <c r="A144" s="16" t="s">
+      <c r="G143" s="10"/>
+      <c r="H143" s="11"/>
+    </row>
+    <row r="144" spans="1:8" ht="12.75">
+      <c r="A144" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="4"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="17">
+      <c r="E144" s="10"/>
+      <c r="F144" s="21">
         <f>ROUND(F142+F143,2)</f>
         <v>298.70</v>
       </c>
-      <c r="G144" s="8"/>
-    </row>
-    <row r="145" spans="1:7" ht="12.75">
-      <c r="A145" s="11">
+      <c r="G144" s="10"/>
+      <c r="H144" s="11"/>
+    </row>
+    <row r="145" spans="1:8" ht="12.75">
+      <c r="A145" s="14">
         <v>1001</v>
       </c>
-      <c r="B145" s="10"/>
-      <c r="C145" s="12" t="s">
+      <c r="B145" s="13"/>
+      <c r="C145" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="4"/>
-      <c r="F145" s="12"/>
+      <c r="F145" s="15"/>
       <c r="G145" s="4"/>
-    </row>
-    <row r="146" spans="1:7" ht="12.75">
-      <c r="A146" s="5"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="13" t="s">
+      <c r="H145" s="16"/>
+    </row>
+    <row r="146" spans="1:8" ht="12.75">
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D146" s="13">
+      <c r="D146" s="17">
         <v>1</v>
       </c>
-      <c r="E146" s="13">
+      <c r="E146" s="17">
         <v>806</v>
       </c>
-      <c r="F146" s="13">
+      <c r="F146" s="17">
         <f>E146*D146</f>
         <v>806</v>
       </c>
-      <c r="G146" s="13" t="s">
+      <c r="G146" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="12.75">
-      <c r="A147" s="11" t="s">
+      <c r="H146" s="16"/>
+    </row>
+    <row r="147" spans="1:8" ht="12.75">
+      <c r="A147" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B147" s="10"/>
-      <c r="C147" s="14" t="s">
+      <c r="B147" s="13"/>
+      <c r="C147" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="4"/>
-      <c r="F147" s="12"/>
+      <c r="F147" s="15"/>
       <c r="G147" s="4"/>
-    </row>
-    <row r="148" spans="1:7" ht="12.75">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="13" t="s">
+      <c r="H147" s="16"/>
+    </row>
+    <row r="148" spans="1:8" ht="12.75">
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13">
+      <c r="D148" s="17"/>
+      <c r="E148" s="17"/>
+      <c r="F148" s="17">
         <f>F146*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G148" s="13" t="s">
+      <c r="G148" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="12.75">
-      <c r="A149" s="13">
+      <c r="H148" s="16">
+        <f>F148+F138</f>
+        <v>135.83975000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="12.75">
+      <c r="A149" s="17">
         <v>14.40</v>
       </c>
-      <c r="B149" s="13"/>
-      <c r="C149" s="12" t="s">
+      <c r="B149" s="17"/>
+      <c r="C149" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="4"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="13"/>
-    </row>
-    <row r="150" spans="1:7" ht="12.75">
-      <c r="A150" s="13"/>
-      <c r="B150" s="13"/>
-      <c r="C150" s="13" t="s">
+      <c r="F149" s="17"/>
+      <c r="G149" s="17"/>
+      <c r="H149" s="16"/>
+    </row>
+    <row r="150" spans="1:8" ht="12.75">
+      <c r="A150" s="17"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D150" s="13">
+      <c r="D150" s="17">
         <v>13.13</v>
       </c>
-      <c r="E150" s="13">
+      <c r="E150" s="17">
         <v>498.87</v>
       </c>
-      <c r="F150" s="13">
+      <c r="F150" s="17">
         <f>D150*E150</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G150" s="13" t="s">
+      <c r="G150" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="12.75">
-      <c r="A151" s="9" t="s">
+      <c r="H150" s="16"/>
+    </row>
+    <row r="151" spans="1:8" ht="12.75">
+      <c r="A151" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="8">
+      <c r="D151" s="10">
         <v>50</v>
       </c>
-      <c r="E151" s="8" t="s">
+      <c r="E151" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="8">
+      <c r="F151" s="10">
         <f>F146+F148+F150</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G151" s="8"/>
-    </row>
-    <row r="152" spans="1:7" ht="12.75">
-      <c r="A152" s="9" t="s">
+      <c r="G151" s="10"/>
+      <c r="H151" s="11"/>
+    </row>
+    <row r="152" spans="1:8" ht="12.75">
+      <c r="A152" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="8">
+      <c r="D152" s="10">
         <v>1</v>
       </c>
-      <c r="E152" s="8" t="s">
+      <c r="E152" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F152" s="8">
+      <c r="F152" s="10">
         <f>F151/D151</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G152" s="8"/>
-    </row>
-    <row r="153" spans="1:7" ht="12.75">
-      <c r="A153" s="9" t="s">
+      <c r="G152" s="10"/>
+      <c r="H152" s="11"/>
+    </row>
+    <row r="153" spans="1:8" ht="12.75">
+      <c r="A153" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="8">
+      <c r="E153" s="10">
         <f>F152</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F153" s="8">
+      <c r="F153" s="10">
         <f>E153*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G153" s="8"/>
-    </row>
-    <row r="154" spans="1:7" ht="12.75">
-      <c r="A154" s="16" t="s">
+      <c r="G153" s="10"/>
+      <c r="H153" s="11">
+        <f>E153+E143</f>
+        <v>407.02625799999998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="12.75">
+      <c r="A154" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="17">
+      <c r="E154" s="10"/>
+      <c r="F154" s="21">
         <f>ROUND(F152+F153,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G154" s="8"/>
-    </row>
-    <row r="155" spans="1:7" ht="12.75">
-      <c r="A155" s="18" t="s">
+      <c r="G154" s="10"/>
+      <c r="H154" s="11">
+        <f>F154+F144</f>
+        <v>468.08</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="12.75">
+      <c r="A155" s="22" t="s">
         <v>57</v>
       </c>
       <c r="B155" s="3"/>
@@ -3266,11 +3525,12 @@
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="4"/>
-      <c r="G155" s="17" t="s">
+      <c r="G155" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="12.75">
+      <c r="H155" s="23"/>
+    </row>
+    <row r="156" spans="1:8" ht="12.75">
       <c r="A156" s="1" t="s">
         <v>0</v>
       </c>
@@ -3286,28 +3546,30 @@
         <v>3</v>
       </c>
       <c r="G156" s="4"/>
-    </row>
-    <row r="157" spans="1:7" ht="12.75">
-      <c r="A157" s="5"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6" t="s">
+      <c r="H156" s="5"/>
+    </row>
+    <row r="157" spans="1:8" ht="12.75">
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D157" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E157" s="6" t="s">
+      <c r="E157" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F157" s="6" t="s">
+      <c r="F157" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G157" s="6" t="s">
+      <c r="G157" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="12.75">
-      <c r="A158" s="7" t="s">
+      <c r="H157" s="5"/>
+    </row>
+    <row r="158" spans="1:8" ht="12.75">
+      <c r="A158" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B158" s="3"/>
@@ -3316,29 +3578,31 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="4"/>
-    </row>
-    <row r="159" spans="1:7" ht="12.75">
-      <c r="A159" s="8"/>
-      <c r="B159" s="8" t="s">
+      <c r="H158" s="9"/>
+    </row>
+    <row r="159" spans="1:8" ht="12.75">
+      <c r="A159" s="10"/>
+      <c r="B159" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D159" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E159" s="8">
+      <c r="E159" s="10">
         <v>50</v>
       </c>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8"/>
-    </row>
-    <row r="160" spans="1:7" ht="12.75">
-      <c r="A160" s="8" t="s">
+      <c r="F159" s="10"/>
+      <c r="G159" s="10"/>
+      <c r="H159" s="11"/>
+    </row>
+    <row r="160" spans="1:8" ht="12.75">
+      <c r="A160" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C160" s="3"/>
@@ -3346,9 +3610,10 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="4"/>
-    </row>
-    <row r="161" spans="1:7" ht="12.75">
-      <c r="A161" s="9" t="s">
+      <c r="H160" s="11"/>
+    </row>
+    <row r="161" spans="1:8" ht="12.75">
+      <c r="A161" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B161" s="3"/>
@@ -3357,393 +3622,427 @@
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="4"/>
-    </row>
-    <row r="162" spans="1:7" ht="12.75">
-      <c r="A162" s="10"/>
-      <c r="B162" s="11" t="s">
+      <c r="H161" s="11"/>
+    </row>
+    <row r="162" spans="1:8" ht="12.75">
+      <c r="A162" s="13"/>
+      <c r="B162" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="15" t="s">
         <v>60</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="4"/>
-      <c r="F162" s="12"/>
+      <c r="F162" s="15"/>
       <c r="G162" s="4"/>
-    </row>
-    <row r="163" spans="1:7" ht="12.75">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="13" t="s">
+      <c r="H162" s="16"/>
+    </row>
+    <row r="163" spans="1:8" ht="12.75">
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D163" s="13">
+      <c r="D163" s="17">
         <v>50</v>
       </c>
-      <c r="E163" s="13">
+      <c r="E163" s="17">
         <v>211.86</v>
       </c>
-      <c r="F163" s="13">
+      <c r="F163" s="17">
         <f>D163*E163</f>
         <v>10593</v>
       </c>
-      <c r="G163" s="13" t="s">
+      <c r="G163" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="12.75">
-      <c r="A164" s="11" t="s">
+      <c r="H163" s="16"/>
+    </row>
+    <row r="164" spans="1:8" ht="12.75">
+      <c r="A164" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B164" s="10"/>
-      <c r="C164" s="12" t="s">
+      <c r="B164" s="13"/>
+      <c r="C164" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="12"/>
+      <c r="F164" s="15"/>
       <c r="G164" s="4"/>
-    </row>
-    <row r="165" spans="1:7" ht="12.75">
-      <c r="A165" s="5"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="13" t="s">
+      <c r="H164" s="16"/>
+    </row>
+    <row r="165" spans="1:8" ht="12.75">
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D165" s="13"/>
-      <c r="E165" s="13"/>
-      <c r="F165" s="13">
+      <c r="D165" s="17"/>
+      <c r="E165" s="17"/>
+      <c r="F165" s="17">
         <f>F163*5%</f>
         <v>529.65</v>
       </c>
-      <c r="G165" s="13" t="s">
+      <c r="G165" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="12.75">
-      <c r="A166" s="10"/>
-      <c r="B166" s="11" t="s">
+      <c r="H165" s="16"/>
+    </row>
+    <row r="166" spans="1:8" ht="12.75">
+      <c r="A166" s="13"/>
+      <c r="B166" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C166" s="12" t="s">
+      <c r="C166" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="4"/>
-      <c r="F166" s="12"/>
+      <c r="F166" s="15"/>
       <c r="G166" s="4"/>
-    </row>
-    <row r="167" spans="1:7" ht="12.75">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="13" t="s">
+      <c r="H166" s="16"/>
+    </row>
+    <row r="167" spans="1:8" ht="12.75">
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D167" s="13">
+      <c r="D167" s="17">
         <v>7</v>
       </c>
-      <c r="E167" s="13">
+      <c r="E167" s="17">
         <v>675</v>
       </c>
-      <c r="F167" s="13">
+      <c r="F167" s="17">
         <f>D167*E167</f>
         <v>4725</v>
       </c>
-      <c r="G167" s="13" t="s">
+      <c r="G167" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" ht="12.75">
-      <c r="A168" s="11" t="s">
+      <c r="H167" s="16"/>
+    </row>
+    <row r="168" spans="1:8" ht="12.75">
+      <c r="A168" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B168" s="10"/>
-      <c r="C168" s="14" t="s">
+      <c r="B168" s="13"/>
+      <c r="C168" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="4"/>
-      <c r="F168" s="12"/>
+      <c r="F168" s="15"/>
       <c r="G168" s="4"/>
-    </row>
-    <row r="169" spans="1:7" ht="12.75">
-      <c r="A169" s="5"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="13" t="s">
+      <c r="H168" s="16"/>
+    </row>
+    <row r="169" spans="1:8" ht="12.75">
+      <c r="A169" s="6"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D169" s="13"/>
-      <c r="E169" s="13"/>
-      <c r="F169" s="13">
+      <c r="D169" s="17"/>
+      <c r="E169" s="17"/>
+      <c r="F169" s="17">
         <f>(F163+F165+F167)*1%</f>
         <v>158.47649999999999</v>
       </c>
-      <c r="G169" s="13" t="s">
+      <c r="G169" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="12.75">
-      <c r="A170" s="9" t="s">
+      <c r="H169" s="16"/>
+    </row>
+    <row r="170" spans="1:8" ht="12.75">
+      <c r="A170" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="4"/>
-      <c r="D170" s="8">
+      <c r="D170" s="10">
         <v>50</v>
       </c>
-      <c r="E170" s="8" t="s">
+      <c r="E170" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F170" s="8">
+      <c r="F170" s="10">
         <f>F163+F165+F167+F169</f>
         <v>16006.1265</v>
       </c>
-      <c r="G170" s="8"/>
-    </row>
-    <row r="171" spans="1:7" ht="12.75">
-      <c r="A171" s="9" t="s">
+      <c r="G170" s="10"/>
+      <c r="H170" s="11"/>
+    </row>
+    <row r="171" spans="1:8" ht="12.75">
+      <c r="A171" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="4"/>
-      <c r="D171" s="8">
+      <c r="D171" s="10">
         <v>1</v>
       </c>
-      <c r="E171" s="8" t="s">
+      <c r="E171" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F171" s="8">
+      <c r="F171" s="10">
         <f>F170/D170</f>
         <v>320.12252999999998</v>
       </c>
-      <c r="G171" s="8"/>
-    </row>
-    <row r="172" spans="1:7" ht="12.75">
-      <c r="A172" s="9" t="s">
+      <c r="G171" s="10"/>
+      <c r="H171" s="11"/>
+    </row>
+    <row r="172" spans="1:8" ht="12.75">
+      <c r="A172" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="4"/>
-      <c r="E172" s="15">
+      <c r="E172" s="19">
         <f>F163*105%*101%/D170</f>
         <v>224.67752999999999</v>
       </c>
-      <c r="F172" s="8">
+      <c r="F172" s="10">
         <f>E172*1%</f>
         <v>2.2467752999999999</v>
       </c>
-      <c r="G172" s="8"/>
-    </row>
-    <row r="173" spans="1:7" ht="12.75">
-      <c r="A173" s="9" t="s">
+      <c r="G172" s="10"/>
+      <c r="H172" s="11"/>
+    </row>
+    <row r="173" spans="1:8" ht="12.75">
+      <c r="A173" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="4"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8">
+      <c r="E173" s="10"/>
+      <c r="F173" s="10">
         <f>F171+F172</f>
         <v>322.36930530000001</v>
       </c>
-      <c r="G173" s="8"/>
-    </row>
-    <row r="174" spans="1:7" ht="12.75">
-      <c r="A174" s="9" t="s">
+      <c r="G173" s="10"/>
+      <c r="H173" s="11"/>
+    </row>
+    <row r="174" spans="1:8" ht="12.75">
+      <c r="A174" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="4"/>
-      <c r="E174" s="8">
+      <c r="E174" s="10">
         <f>F173</f>
         <v>322.36930530000001</v>
       </c>
-      <c r="F174" s="8">
+      <c r="F174" s="10">
         <f>E174*15%</f>
         <v>48.355395799999997</v>
       </c>
-      <c r="G174" s="8"/>
-    </row>
-    <row r="175" spans="1:7" ht="12.75">
-      <c r="A175" s="16" t="s">
+      <c r="G174" s="10"/>
+      <c r="H174" s="11"/>
+    </row>
+    <row r="175" spans="1:8" ht="12.75">
+      <c r="A175" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="4"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="17">
+      <c r="E175" s="10"/>
+      <c r="F175" s="21">
         <f>ROUND(F173+F174,2)</f>
         <v>370.72</v>
       </c>
-      <c r="G175" s="8"/>
-    </row>
-    <row r="176" spans="1:7" ht="12.75">
-      <c r="A176" s="11">
+      <c r="G175" s="10"/>
+      <c r="H175" s="11"/>
+    </row>
+    <row r="176" spans="1:8" ht="12.75">
+      <c r="A176" s="14">
         <v>1001</v>
       </c>
-      <c r="B176" s="10"/>
-      <c r="C176" s="12" t="s">
+      <c r="B176" s="13"/>
+      <c r="C176" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="4"/>
-      <c r="F176" s="12"/>
+      <c r="F176" s="15"/>
       <c r="G176" s="4"/>
-    </row>
-    <row r="177" spans="1:7" ht="12.75">
-      <c r="A177" s="5"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="13" t="s">
+      <c r="H176" s="16"/>
+    </row>
+    <row r="177" spans="1:8" ht="12.75">
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D177" s="13">
+      <c r="D177" s="17">
         <v>1</v>
       </c>
-      <c r="E177" s="13">
+      <c r="E177" s="17">
         <v>806</v>
       </c>
-      <c r="F177" s="13">
+      <c r="F177" s="17">
         <f>E177*D177</f>
         <v>806</v>
       </c>
-      <c r="G177" s="13" t="s">
+      <c r="G177" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="12.75">
-      <c r="A178" s="11" t="s">
+      <c r="H177" s="16"/>
+    </row>
+    <row r="178" spans="1:8" ht="12.75">
+      <c r="A178" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B178" s="10"/>
-      <c r="C178" s="14" t="s">
+      <c r="B178" s="13"/>
+      <c r="C178" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="4"/>
-      <c r="F178" s="12"/>
+      <c r="F178" s="15"/>
       <c r="G178" s="4"/>
-    </row>
-    <row r="179" spans="1:7" ht="12.75">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="13" t="s">
+      <c r="H178" s="16"/>
+    </row>
+    <row r="179" spans="1:8" ht="12.75">
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D179" s="13"/>
-      <c r="E179" s="13"/>
-      <c r="F179" s="13">
+      <c r="D179" s="17"/>
+      <c r="E179" s="17"/>
+      <c r="F179" s="17">
         <f>F177*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G179" s="13" t="s">
+      <c r="G179" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="12.75">
-      <c r="A180" s="13">
+      <c r="H179" s="16">
+        <f>F179+F169</f>
+        <v>166.53649999999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="12.75">
+      <c r="A180" s="17">
         <v>14.40</v>
       </c>
-      <c r="B180" s="13"/>
-      <c r="C180" s="12" t="s">
+      <c r="B180" s="17"/>
+      <c r="C180" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="4"/>
-      <c r="F180" s="13"/>
-      <c r="G180" s="13"/>
-    </row>
-    <row r="181" spans="1:7" ht="12.75">
-      <c r="A181" s="13"/>
-      <c r="B181" s="13"/>
-      <c r="C181" s="13" t="s">
+      <c r="F180" s="17"/>
+      <c r="G180" s="17"/>
+      <c r="H180" s="16"/>
+    </row>
+    <row r="181" spans="1:8" ht="12.75">
+      <c r="A181" s="17"/>
+      <c r="B181" s="17"/>
+      <c r="C181" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D181" s="13">
+      <c r="D181" s="17">
         <v>13.13</v>
       </c>
-      <c r="E181" s="13">
+      <c r="E181" s="17">
         <v>498.87</v>
       </c>
-      <c r="F181" s="13">
+      <c r="F181" s="17">
         <f>D181*E181</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G181" s="13" t="s">
+      <c r="G181" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="12.75">
-      <c r="A182" s="9" t="s">
+      <c r="H181" s="16"/>
+    </row>
+    <row r="182" spans="1:8" ht="12.75">
+      <c r="A182" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="4"/>
-      <c r="D182" s="8">
+      <c r="D182" s="10">
         <v>50</v>
       </c>
-      <c r="E182" s="8" t="s">
+      <c r="E182" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F182" s="8">
+      <c r="F182" s="10">
         <f>F177+F179+F181</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G182" s="8"/>
-    </row>
-    <row r="183" spans="1:7" ht="12.75">
-      <c r="A183" s="9" t="s">
+      <c r="G182" s="10"/>
+      <c r="H182" s="11"/>
+    </row>
+    <row r="183" spans="1:8" ht="12.75">
+      <c r="A183" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="4"/>
-      <c r="D183" s="8">
+      <c r="D183" s="10">
         <v>1</v>
       </c>
-      <c r="E183" s="8" t="s">
+      <c r="E183" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F183" s="8">
+      <c r="F183" s="10">
         <f>F182/D182</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G183" s="8"/>
-    </row>
-    <row r="184" spans="1:7" ht="12.75">
-      <c r="A184" s="9" t="s">
+      <c r="G183" s="10"/>
+      <c r="H183" s="11"/>
+    </row>
+    <row r="184" spans="1:8" ht="12.75">
+      <c r="A184" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="4"/>
-      <c r="E184" s="8">
+      <c r="E184" s="10">
         <f>F183</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F184" s="8">
+      <c r="F184" s="10">
         <f>E184*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G184" s="8"/>
-    </row>
-    <row r="185" spans="1:7" ht="12.75">
-      <c r="A185" s="16" t="s">
+      <c r="G184" s="10"/>
+      <c r="H184" s="11">
+        <f>E184+E174</f>
+        <v>469.65376730000003</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="12.75">
+      <c r="A185" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="4"/>
-      <c r="E185" s="8"/>
-      <c r="F185" s="17">
+      <c r="E185" s="10"/>
+      <c r="F185" s="21">
         <f>ROUND(F183+F184,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G185" s="8"/>
-    </row>
-    <row r="186" spans="1:7" ht="12.75">
-      <c r="A186" s="18" t="s">
+      <c r="G185" s="10"/>
+      <c r="H185" s="11">
+        <f>F185+F175</f>
+        <v>540.10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="12.75">
+      <c r="A186" s="22" t="s">
         <v>61</v>
       </c>
       <c r="B186" s="3"/>
@@ -3751,11 +4050,12 @@
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
       <c r="F186" s="4"/>
-      <c r="G186" s="17" t="s">
+      <c r="G186" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="12.75">
+      <c r="H186" s="23"/>
+    </row>
+    <row r="187" spans="1:8" ht="12.75">
       <c r="A187" s="1" t="s">
         <v>0</v>
       </c>
@@ -3771,28 +4071,30 @@
         <v>3</v>
       </c>
       <c r="G187" s="4"/>
-    </row>
-    <row r="188" spans="1:7" ht="12.75">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="6" t="s">
+      <c r="H187" s="5"/>
+    </row>
+    <row r="188" spans="1:8" ht="12.75">
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="6" t="s">
+      <c r="D188" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E188" s="6" t="s">
+      <c r="E188" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F188" s="6" t="s">
+      <c r="F188" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G188" s="6" t="s">
+      <c r="G188" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" ht="12.75">
-      <c r="A189" s="7" t="s">
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8" ht="12.75">
+      <c r="A189" s="8" t="s">
         <v>62</v>
       </c>
       <c r="B189" s="3"/>
@@ -3801,29 +4103,31 @@
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="4"/>
-    </row>
-    <row r="190" spans="1:7" ht="12.75">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8" t="s">
+      <c r="H189" s="9"/>
+    </row>
+    <row r="190" spans="1:8" ht="12.75">
+      <c r="A190" s="10"/>
+      <c r="B190" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D190" s="8" t="s">
+      <c r="D190" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E190" s="8">
+      <c r="E190" s="10">
         <v>50</v>
       </c>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8"/>
-    </row>
-    <row r="191" spans="1:7" ht="12.75">
-      <c r="A191" s="8" t="s">
+      <c r="F190" s="10"/>
+      <c r="G190" s="10"/>
+      <c r="H190" s="11"/>
+    </row>
+    <row r="191" spans="1:8" ht="12.75">
+      <c r="A191" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B191" s="9" t="s">
+      <c r="B191" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C191" s="3"/>
@@ -3831,9 +4135,10 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="4"/>
-    </row>
-    <row r="192" spans="1:7" ht="12.75">
-      <c r="A192" s="9" t="s">
+      <c r="H191" s="11"/>
+    </row>
+    <row r="192" spans="1:8" ht="12.75">
+      <c r="A192" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B192" s="3"/>
@@ -3842,393 +4147,427 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="4"/>
-    </row>
-    <row r="193" spans="1:7" ht="12.75">
-      <c r="A193" s="10"/>
-      <c r="B193" s="11" t="s">
+      <c r="H192" s="11"/>
+    </row>
+    <row r="193" spans="1:8" ht="12.75">
+      <c r="A193" s="13"/>
+      <c r="B193" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C193" s="12" t="s">
+      <c r="C193" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="12"/>
+      <c r="F193" s="15"/>
       <c r="G193" s="4"/>
-    </row>
-    <row r="194" spans="1:7" ht="12.75">
-      <c r="A194" s="5"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="13" t="s">
+      <c r="H193" s="16"/>
+    </row>
+    <row r="194" spans="1:8" ht="12.75">
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D194" s="13">
+      <c r="D194" s="17">
         <v>50</v>
       </c>
-      <c r="E194" s="13">
+      <c r="E194" s="17">
         <v>329.66</v>
       </c>
-      <c r="F194" s="13">
+      <c r="F194" s="17">
         <f>D194*E194</f>
         <v>16483</v>
       </c>
-      <c r="G194" s="13" t="s">
+      <c r="G194" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="12.75">
-      <c r="A195" s="11" t="s">
+      <c r="H194" s="16"/>
+    </row>
+    <row r="195" spans="1:8" ht="12.75">
+      <c r="A195" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B195" s="10"/>
-      <c r="C195" s="12" t="s">
+      <c r="B195" s="13"/>
+      <c r="C195" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="12"/>
+      <c r="F195" s="15"/>
       <c r="G195" s="4"/>
-    </row>
-    <row r="196" spans="1:7" ht="12.75">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="13" t="s">
+      <c r="H195" s="16"/>
+    </row>
+    <row r="196" spans="1:8" ht="12.75">
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D196" s="13"/>
-      <c r="E196" s="13"/>
-      <c r="F196" s="13">
+      <c r="D196" s="17"/>
+      <c r="E196" s="17"/>
+      <c r="F196" s="17">
         <f>F194*5%</f>
         <v>824.15</v>
       </c>
-      <c r="G196" s="13" t="s">
+      <c r="G196" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="12.75">
-      <c r="A197" s="10"/>
-      <c r="B197" s="11" t="s">
+      <c r="H196" s="16"/>
+    </row>
+    <row r="197" spans="1:8" ht="12.75">
+      <c r="A197" s="13"/>
+      <c r="B197" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C197" s="12" t="s">
+      <c r="C197" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="12"/>
+      <c r="F197" s="15"/>
       <c r="G197" s="4"/>
-    </row>
-    <row r="198" spans="1:7" ht="12.75">
-      <c r="A198" s="5"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="13" t="s">
+      <c r="H197" s="16"/>
+    </row>
+    <row r="198" spans="1:8" ht="12.75">
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D198" s="13">
+      <c r="D198" s="17">
         <v>7</v>
       </c>
-      <c r="E198" s="13">
+      <c r="E198" s="17">
         <v>675</v>
       </c>
-      <c r="F198" s="13">
+      <c r="F198" s="17">
         <f>D198*E198</f>
         <v>4725</v>
       </c>
-      <c r="G198" s="13" t="s">
+      <c r="G198" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="12.75">
-      <c r="A199" s="11" t="s">
+      <c r="H198" s="16"/>
+    </row>
+    <row r="199" spans="1:8" ht="12.75">
+      <c r="A199" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B199" s="10"/>
-      <c r="C199" s="14" t="s">
+      <c r="B199" s="13"/>
+      <c r="C199" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="12"/>
+      <c r="F199" s="15"/>
       <c r="G199" s="4"/>
-    </row>
-    <row r="200" spans="1:7" ht="12.75">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="13" t="s">
+      <c r="H199" s="16"/>
+    </row>
+    <row r="200" spans="1:8" ht="12.75">
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D200" s="13"/>
-      <c r="E200" s="13"/>
-      <c r="F200" s="13">
+      <c r="D200" s="17"/>
+      <c r="E200" s="17"/>
+      <c r="F200" s="17">
         <f>(F194+F196+F198)*1%</f>
         <v>220.32149999999999</v>
       </c>
-      <c r="G200" s="13" t="s">
+      <c r="G200" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="12.75">
-      <c r="A201" s="9" t="s">
+      <c r="H200" s="16"/>
+    </row>
+    <row r="201" spans="1:8" ht="12.75">
+      <c r="A201" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="8">
+      <c r="D201" s="10">
         <v>50</v>
       </c>
-      <c r="E201" s="8" t="s">
+      <c r="E201" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F201" s="8">
+      <c r="F201" s="10">
         <f>F194+F196+F198+F200</f>
         <v>22252.4715</v>
       </c>
-      <c r="G201" s="8"/>
-    </row>
-    <row r="202" spans="1:7" ht="12.75">
-      <c r="A202" s="9" t="s">
+      <c r="G201" s="10"/>
+      <c r="H201" s="11"/>
+    </row>
+    <row r="202" spans="1:8" ht="12.75">
+      <c r="A202" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="8">
+      <c r="D202" s="10">
         <v>1</v>
       </c>
-      <c r="E202" s="8" t="s">
+      <c r="E202" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F202" s="8">
+      <c r="F202" s="10">
         <f>F201/D201</f>
         <v>445.04942999999997</v>
       </c>
-      <c r="G202" s="8"/>
-    </row>
-    <row r="203" spans="1:7" ht="12.75">
-      <c r="A203" s="9" t="s">
+      <c r="G202" s="10"/>
+      <c r="H202" s="11"/>
+    </row>
+    <row r="203" spans="1:8" ht="12.75">
+      <c r="A203" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="4"/>
-      <c r="E203" s="15">
+      <c r="E203" s="19">
         <f>F194*105%*101%/D201</f>
         <v>349.60442999999998</v>
       </c>
-      <c r="F203" s="8">
+      <c r="F203" s="10">
         <f>E203*1%</f>
         <v>3.4960442999999999</v>
       </c>
-      <c r="G203" s="8"/>
-    </row>
-    <row r="204" spans="1:7" ht="12.75">
-      <c r="A204" s="9" t="s">
+      <c r="G203" s="10"/>
+      <c r="H203" s="11"/>
+    </row>
+    <row r="204" spans="1:8" ht="12.75">
+      <c r="A204" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="4"/>
-      <c r="E204" s="8"/>
-      <c r="F204" s="8">
+      <c r="E204" s="10"/>
+      <c r="F204" s="10">
         <f>F202+F203</f>
         <v>448.54547430000002</v>
       </c>
-      <c r="G204" s="8"/>
-    </row>
-    <row r="205" spans="1:7" ht="12.75">
-      <c r="A205" s="9" t="s">
+      <c r="G204" s="10"/>
+      <c r="H204" s="11"/>
+    </row>
+    <row r="205" spans="1:8" ht="12.75">
+      <c r="A205" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="4"/>
-      <c r="E205" s="8">
+      <c r="E205" s="10">
         <f>F204</f>
         <v>448.54547430000002</v>
       </c>
-      <c r="F205" s="8">
+      <c r="F205" s="10">
         <f>E205*15%</f>
         <v>67.281821149999999</v>
       </c>
-      <c r="G205" s="8"/>
-    </row>
-    <row r="206" spans="1:7" ht="12.75">
-      <c r="A206" s="16" t="s">
+      <c r="G205" s="10"/>
+      <c r="H205" s="11"/>
+    </row>
+    <row r="206" spans="1:8" ht="12.75">
+      <c r="A206" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="4"/>
-      <c r="E206" s="8"/>
-      <c r="F206" s="17">
+      <c r="E206" s="10"/>
+      <c r="F206" s="21">
         <f>ROUND(F204+F205,2)</f>
         <v>515.83</v>
       </c>
-      <c r="G206" s="8"/>
-    </row>
-    <row r="207" spans="1:7" ht="12.75">
-      <c r="A207" s="11">
+      <c r="G206" s="10"/>
+      <c r="H206" s="11"/>
+    </row>
+    <row r="207" spans="1:8" ht="12.75">
+      <c r="A207" s="14">
         <v>1001</v>
       </c>
-      <c r="B207" s="10"/>
-      <c r="C207" s="12" t="s">
+      <c r="B207" s="13"/>
+      <c r="C207" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="12"/>
+      <c r="F207" s="15"/>
       <c r="G207" s="4"/>
-    </row>
-    <row r="208" spans="1:7" ht="12.75">
-      <c r="A208" s="5"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="13" t="s">
+      <c r="H207" s="16"/>
+    </row>
+    <row r="208" spans="1:8" ht="12.75">
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D208" s="13">
+      <c r="D208" s="17">
         <v>1</v>
       </c>
-      <c r="E208" s="13">
+      <c r="E208" s="17">
         <v>806</v>
       </c>
-      <c r="F208" s="13">
+      <c r="F208" s="17">
         <f>E208*D208</f>
         <v>806</v>
       </c>
-      <c r="G208" s="13" t="s">
+      <c r="G208" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="12.75">
-      <c r="A209" s="11" t="s">
+      <c r="H208" s="16"/>
+    </row>
+    <row r="209" spans="1:8" ht="12.75">
+      <c r="A209" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B209" s="10"/>
-      <c r="C209" s="14" t="s">
+      <c r="B209" s="13"/>
+      <c r="C209" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D209" s="3"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="12"/>
+      <c r="F209" s="15"/>
       <c r="G209" s="4"/>
-    </row>
-    <row r="210" spans="1:7" ht="12.75">
-      <c r="A210" s="5"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="13" t="s">
+      <c r="H209" s="16"/>
+    </row>
+    <row r="210" spans="1:8" ht="12.75">
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D210" s="13"/>
-      <c r="E210" s="13"/>
-      <c r="F210" s="13">
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="17">
         <f>F208*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G210" s="13" t="s">
+      <c r="G210" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" ht="12.75">
-      <c r="A211" s="13">
+      <c r="H210" s="16">
+        <f>F210+F200</f>
+        <v>228.38149999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="12.75">
+      <c r="A211" s="17">
         <v>14.40</v>
       </c>
-      <c r="B211" s="13"/>
-      <c r="C211" s="12" t="s">
+      <c r="B211" s="17"/>
+      <c r="C211" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="13"/>
-      <c r="G211" s="13"/>
-    </row>
-    <row r="212" spans="1:7" ht="12.75">
-      <c r="A212" s="13"/>
-      <c r="B212" s="13"/>
-      <c r="C212" s="13" t="s">
+      <c r="F211" s="17"/>
+      <c r="G211" s="17"/>
+      <c r="H211" s="16"/>
+    </row>
+    <row r="212" spans="1:8" ht="12.75">
+      <c r="A212" s="17"/>
+      <c r="B212" s="17"/>
+      <c r="C212" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D212" s="13">
+      <c r="D212" s="17">
         <v>13.13</v>
       </c>
-      <c r="E212" s="13">
+      <c r="E212" s="17">
         <v>498.87</v>
       </c>
-      <c r="F212" s="13">
+      <c r="F212" s="17">
         <f>D212*E212</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G212" s="13" t="s">
+      <c r="G212" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="12.75">
-      <c r="A213" s="9" t="s">
+      <c r="H212" s="16"/>
+    </row>
+    <row r="213" spans="1:8" ht="12.75">
+      <c r="A213" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="8">
+      <c r="D213" s="10">
         <v>50</v>
       </c>
-      <c r="E213" s="8" t="s">
+      <c r="E213" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F213" s="8">
+      <c r="F213" s="10">
         <f>F208+F210+F212</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G213" s="8"/>
-    </row>
-    <row r="214" spans="1:7" ht="12.75">
-      <c r="A214" s="9" t="s">
+      <c r="G213" s="10"/>
+      <c r="H213" s="11"/>
+    </row>
+    <row r="214" spans="1:8" ht="12.75">
+      <c r="A214" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="4"/>
-      <c r="D214" s="8">
+      <c r="D214" s="10">
         <v>1</v>
       </c>
-      <c r="E214" s="8" t="s">
+      <c r="E214" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F214" s="8">
+      <c r="F214" s="10">
         <f>F213/D213</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G214" s="8"/>
-    </row>
-    <row r="215" spans="1:7" ht="12.75">
-      <c r="A215" s="9" t="s">
+      <c r="G214" s="10"/>
+      <c r="H214" s="11"/>
+    </row>
+    <row r="215" spans="1:8" ht="12.75">
+      <c r="A215" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="4"/>
-      <c r="E215" s="8">
+      <c r="E215" s="10">
         <f>F214</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F215" s="8">
+      <c r="F215" s="10">
         <f>E215*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G215" s="8"/>
-    </row>
-    <row r="216" spans="1:7" ht="12.75">
-      <c r="A216" s="16" t="s">
+      <c r="G215" s="10"/>
+      <c r="H215" s="11">
+        <f>E215+E205</f>
+        <v>595.82993629999999</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="12.75">
+      <c r="A216" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="4"/>
-      <c r="E216" s="8"/>
-      <c r="F216" s="17">
+      <c r="E216" s="10"/>
+      <c r="F216" s="21">
         <f>ROUND(F214+F215,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G216" s="8"/>
-    </row>
-    <row r="217" spans="1:7" ht="12.75">
-      <c r="A217" s="18" t="s">
+      <c r="G216" s="10"/>
+      <c r="H216" s="11">
+        <f>F216+F206</f>
+        <v>685.21</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="12.75">
+      <c r="A217" s="22" t="s">
         <v>65</v>
       </c>
       <c r="B217" s="3"/>
@@ -4236,11 +4575,12 @@
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
       <c r="F217" s="4"/>
-      <c r="G217" s="17" t="s">
+      <c r="G217" s="21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" ht="12.75">
+      <c r="H217" s="23"/>
+    </row>
+    <row r="218" spans="1:8" ht="12.75">
       <c r="A218" s="1" t="s">
         <v>0</v>
       </c>
@@ -4256,28 +4596,30 @@
         <v>3</v>
       </c>
       <c r="G218" s="4"/>
-    </row>
-    <row r="219" spans="1:7" ht="12.75">
-      <c r="A219" s="5"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="6" t="s">
+      <c r="H218" s="5"/>
+    </row>
+    <row r="219" spans="1:8" ht="12.75">
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="6" t="s">
+      <c r="D219" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E219" s="6" t="s">
+      <c r="E219" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F219" s="6" t="s">
+      <c r="F219" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G219" s="6" t="s">
+      <c r="G219" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" ht="12.75">
-      <c r="A220" s="7" t="s">
+      <c r="H219" s="5"/>
+    </row>
+    <row r="220" spans="1:8" ht="12.75">
+      <c r="A220" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B220" s="3"/>
@@ -4286,29 +4628,31 @@
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="4"/>
-    </row>
-    <row r="221" spans="1:7" ht="12.75">
-      <c r="A221" s="8"/>
-      <c r="B221" s="8" t="s">
+      <c r="H220" s="9"/>
+    </row>
+    <row r="221" spans="1:8" ht="12.75">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C221" s="8" t="s">
+      <c r="C221" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D221" s="8" t="s">
+      <c r="D221" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E221" s="8">
+      <c r="E221" s="10">
         <v>50</v>
       </c>
-      <c r="F221" s="8"/>
-      <c r="G221" s="8"/>
-    </row>
-    <row r="222" spans="1:7" ht="12.75">
-      <c r="A222" s="8" t="s">
+      <c r="F221" s="10"/>
+      <c r="G221" s="10"/>
+      <c r="H221" s="11"/>
+    </row>
+    <row r="222" spans="1:8" ht="12.75">
+      <c r="A222" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B222" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C222" s="3"/>
@@ -4316,9 +4660,10 @@
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="4"/>
-    </row>
-    <row r="223" spans="1:7" ht="12.75">
-      <c r="A223" s="9" t="s">
+      <c r="H222" s="11"/>
+    </row>
+    <row r="223" spans="1:8" ht="12.75">
+      <c r="A223" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B223" s="3"/>
@@ -4327,406 +4672,966 @@
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="4"/>
-    </row>
-    <row r="224" spans="1:7" ht="12.75">
-      <c r="A224" s="10"/>
-      <c r="B224" s="11" t="s">
+      <c r="H223" s="11"/>
+    </row>
+    <row r="224" spans="1:8" ht="12.75">
+      <c r="A224" s="13"/>
+      <c r="B224" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C224" s="12" t="s">
+      <c r="C224" s="15" t="s">
         <v>68</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="12"/>
+      <c r="F224" s="15"/>
       <c r="G224" s="4"/>
-    </row>
-    <row r="225" spans="1:7" ht="12.75">
-      <c r="A225" s="5"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="13" t="s">
+      <c r="H224" s="16"/>
+    </row>
+    <row r="225" spans="1:8" ht="12.75">
+      <c r="A225" s="6"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D225" s="13">
+      <c r="D225" s="17">
         <v>50</v>
       </c>
-      <c r="E225" s="13">
+      <c r="E225" s="17">
         <v>466.95</v>
       </c>
-      <c r="F225" s="13">
+      <c r="F225" s="17">
         <f>D225*E225</f>
         <v>23347.50</v>
       </c>
-      <c r="G225" s="13" t="s">
+      <c r="G225" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" ht="12.75">
-      <c r="A226" s="11" t="s">
+      <c r="H225" s="16"/>
+    </row>
+    <row r="226" spans="1:8" ht="12.75">
+      <c r="A226" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B226" s="10"/>
-      <c r="C226" s="12" t="s">
+      <c r="B226" s="13"/>
+      <c r="C226" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="12"/>
+      <c r="F226" s="15"/>
       <c r="G226" s="4"/>
-    </row>
-    <row r="227" spans="1:7" ht="12.75">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="13" t="s">
+      <c r="H226" s="16"/>
+    </row>
+    <row r="227" spans="1:8" ht="12.75">
+      <c r="A227" s="6"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D227" s="13"/>
-      <c r="E227" s="13"/>
-      <c r="F227" s="13">
+      <c r="D227" s="17"/>
+      <c r="E227" s="17"/>
+      <c r="F227" s="17">
         <f>F225*5%</f>
         <v>1167.375</v>
       </c>
-      <c r="G227" s="13" t="s">
+      <c r="G227" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" ht="12.75">
-      <c r="A228" s="10"/>
-      <c r="B228" s="11" t="s">
+      <c r="H227" s="16"/>
+    </row>
+    <row r="228" spans="1:8" ht="12.75">
+      <c r="A228" s="13"/>
+      <c r="B228" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C228" s="12" t="s">
+      <c r="C228" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="12"/>
+      <c r="F228" s="15"/>
       <c r="G228" s="4"/>
-    </row>
-    <row r="229" spans="1:7" ht="12.75">
-      <c r="A229" s="5"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="13" t="s">
+      <c r="H228" s="16"/>
+    </row>
+    <row r="229" spans="1:8" ht="12.75">
+      <c r="A229" s="6"/>
+      <c r="B229" s="6"/>
+      <c r="C229" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D229" s="13">
+      <c r="D229" s="17">
         <v>7</v>
       </c>
-      <c r="E229" s="13">
+      <c r="E229" s="17">
         <v>675</v>
       </c>
-      <c r="F229" s="13">
+      <c r="F229" s="17">
         <f>D229*E229</f>
         <v>4725</v>
       </c>
-      <c r="G229" s="13" t="s">
+      <c r="G229" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" ht="12.75">
-      <c r="A230" s="11" t="s">
+      <c r="H229" s="16"/>
+    </row>
+    <row r="230" spans="1:8" ht="12.75">
+      <c r="A230" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B230" s="10"/>
-      <c r="C230" s="14" t="s">
+      <c r="B230" s="13"/>
+      <c r="C230" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="12"/>
+      <c r="F230" s="15"/>
       <c r="G230" s="4"/>
-    </row>
-    <row r="231" spans="1:7" ht="12.75">
-      <c r="A231" s="5"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="13" t="s">
+      <c r="H230" s="16"/>
+    </row>
+    <row r="231" spans="1:8" ht="12.75">
+      <c r="A231" s="6"/>
+      <c r="B231" s="6"/>
+      <c r="C231" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D231" s="13"/>
-      <c r="E231" s="13"/>
-      <c r="F231" s="13">
+      <c r="D231" s="17"/>
+      <c r="E231" s="17"/>
+      <c r="F231" s="17">
         <f>(F225+F227+F229)*1%</f>
         <v>292.39875</v>
       </c>
-      <c r="G231" s="13" t="s">
+      <c r="G231" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" ht="12.75">
-      <c r="A232" s="9" t="s">
+      <c r="H231" s="16"/>
+    </row>
+    <row r="232" spans="1:8" ht="12.75">
+      <c r="A232" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B232" s="3"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="8">
+      <c r="D232" s="10">
         <v>50</v>
       </c>
-      <c r="E232" s="8" t="s">
+      <c r="E232" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F232" s="8">
+      <c r="F232" s="10">
         <f>F225+F227+F229+F231</f>
         <v>29532.27375</v>
       </c>
-      <c r="G232" s="8"/>
-    </row>
-    <row r="233" spans="1:7" ht="12.75">
-      <c r="A233" s="9" t="s">
+      <c r="G232" s="10"/>
+      <c r="H232" s="11"/>
+    </row>
+    <row r="233" spans="1:8" ht="12.75">
+      <c r="A233" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B233" s="3"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="8">
+      <c r="D233" s="10">
         <v>1</v>
       </c>
-      <c r="E233" s="8" t="s">
+      <c r="E233" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F233" s="8">
+      <c r="F233" s="10">
         <f>F232/D232</f>
         <v>590.64547500000003</v>
       </c>
-      <c r="G233" s="8"/>
-    </row>
-    <row r="234" spans="1:7" ht="12.75">
-      <c r="A234" s="9" t="s">
+      <c r="G233" s="10"/>
+      <c r="H233" s="11"/>
+    </row>
+    <row r="234" spans="1:8" ht="12.75">
+      <c r="A234" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="4"/>
-      <c r="E234" s="15">
+      <c r="E234" s="19">
         <f>F225*105%*101%/D232</f>
         <v>495.20047499999998</v>
       </c>
-      <c r="F234" s="8">
+      <c r="F234" s="10">
         <f>E234*1%</f>
         <v>4.9520047500000004</v>
       </c>
-      <c r="G234" s="8"/>
-    </row>
-    <row r="235" spans="1:7" ht="12.75">
-      <c r="A235" s="9" t="s">
+      <c r="G234" s="10"/>
+      <c r="H234" s="11"/>
+    </row>
+    <row r="235" spans="1:8" ht="12.75">
+      <c r="A235" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="4"/>
-      <c r="E235" s="8"/>
-      <c r="F235" s="8">
+      <c r="E235" s="10"/>
+      <c r="F235" s="10">
         <f>F233+F234</f>
         <v>595.59747979999997</v>
       </c>
-      <c r="G235" s="8"/>
-    </row>
-    <row r="236" spans="1:7" ht="12.75">
-      <c r="A236" s="9" t="s">
+      <c r="G235" s="10"/>
+      <c r="H235" s="11"/>
+    </row>
+    <row r="236" spans="1:8" ht="12.75">
+      <c r="A236" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="4"/>
-      <c r="E236" s="8">
+      <c r="E236" s="10">
         <f>F235</f>
         <v>595.59747979999997</v>
       </c>
-      <c r="F236" s="8">
+      <c r="F236" s="10">
         <f>E236*15%</f>
         <v>89.339621960000002</v>
       </c>
-      <c r="G236" s="8"/>
-    </row>
-    <row r="237" spans="1:7" ht="12.75">
-      <c r="A237" s="16" t="s">
+      <c r="G236" s="10"/>
+      <c r="H236" s="11"/>
+    </row>
+    <row r="237" spans="1:8" ht="12.75">
+      <c r="A237" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="4"/>
-      <c r="E237" s="8"/>
-      <c r="F237" s="17">
+      <c r="E237" s="10"/>
+      <c r="F237" s="21">
         <f>ROUND(F235+F236,2)</f>
         <v>684.94</v>
       </c>
-      <c r="G237" s="8"/>
-    </row>
-    <row r="238" spans="1:7" ht="12.75">
-      <c r="A238" s="11">
+      <c r="G237" s="10"/>
+      <c r="H237" s="11"/>
+    </row>
+    <row r="238" spans="1:8" ht="12.75">
+      <c r="A238" s="14">
         <v>1001</v>
       </c>
-      <c r="B238" s="10"/>
-      <c r="C238" s="12" t="s">
+      <c r="B238" s="13"/>
+      <c r="C238" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="12"/>
+      <c r="F238" s="15"/>
       <c r="G238" s="4"/>
-    </row>
-    <row r="239" spans="1:7" ht="12.75">
-      <c r="A239" s="5"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="13" t="s">
+      <c r="H238" s="16"/>
+    </row>
+    <row r="239" spans="1:8" ht="12.75">
+      <c r="A239" s="6"/>
+      <c r="B239" s="6"/>
+      <c r="C239" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D239" s="13">
+      <c r="D239" s="17">
         <v>1</v>
       </c>
-      <c r="E239" s="13">
+      <c r="E239" s="17">
         <v>806</v>
       </c>
-      <c r="F239" s="13">
+      <c r="F239" s="17">
         <f>E239*D239</f>
         <v>806</v>
       </c>
-      <c r="G239" s="13" t="s">
+      <c r="G239" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" ht="12.75">
-      <c r="A240" s="11" t="s">
+      <c r="H239" s="16"/>
+    </row>
+    <row r="240" spans="1:8" ht="12.75">
+      <c r="A240" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B240" s="10"/>
-      <c r="C240" s="14" t="s">
+      <c r="B240" s="13"/>
+      <c r="C240" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="12"/>
+      <c r="F240" s="15"/>
       <c r="G240" s="4"/>
-    </row>
-    <row r="241" spans="1:7" ht="12.75">
-      <c r="A241" s="5"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="13" t="s">
+      <c r="H240" s="16"/>
+    </row>
+    <row r="241" spans="1:8" ht="12.75">
+      <c r="A241" s="6"/>
+      <c r="B241" s="6"/>
+      <c r="C241" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D241" s="13"/>
-      <c r="E241" s="13"/>
-      <c r="F241" s="13">
+      <c r="D241" s="17"/>
+      <c r="E241" s="17"/>
+      <c r="F241" s="17">
         <f>F239*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G241" s="13" t="s">
+      <c r="G241" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" ht="12.75">
-      <c r="A242" s="13">
+      <c r="H241" s="16">
+        <f>F241+F231</f>
+        <v>300.45875</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="12.75">
+      <c r="A242" s="17">
         <v>14.40</v>
       </c>
-      <c r="B242" s="13"/>
-      <c r="C242" s="12" t="s">
+      <c r="B242" s="17"/>
+      <c r="C242" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="13"/>
-      <c r="G242" s="13"/>
-    </row>
-    <row r="243" spans="1:7" ht="12.75">
-      <c r="A243" s="13"/>
-      <c r="B243" s="13"/>
-      <c r="C243" s="13" t="s">
+      <c r="F242" s="17"/>
+      <c r="G242" s="17"/>
+      <c r="H242" s="16"/>
+    </row>
+    <row r="243" spans="1:8" ht="12.75">
+      <c r="A243" s="17"/>
+      <c r="B243" s="17"/>
+      <c r="C243" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D243" s="13">
+      <c r="D243" s="17">
         <v>13.13</v>
       </c>
-      <c r="E243" s="13">
+      <c r="E243" s="17">
         <v>498.87</v>
       </c>
-      <c r="F243" s="13">
+      <c r="F243" s="17">
         <f>D243*E243</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G243" s="13" t="s">
+      <c r="G243" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" ht="12.75">
-      <c r="A244" s="9" t="s">
+      <c r="H243" s="16"/>
+    </row>
+    <row r="244" spans="1:8" ht="12.75">
+      <c r="A244" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="4"/>
-      <c r="D244" s="8">
+      <c r="D244" s="10">
         <v>50</v>
       </c>
-      <c r="E244" s="8" t="s">
+      <c r="E244" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F244" s="8">
+      <c r="F244" s="10">
         <f>F239+F241+F243</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G244" s="8"/>
-    </row>
-    <row r="245" spans="1:7" ht="12.75">
-      <c r="A245" s="9" t="s">
+      <c r="G244" s="10"/>
+      <c r="H244" s="11"/>
+    </row>
+    <row r="245" spans="1:8" ht="12.75">
+      <c r="A245" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="4"/>
-      <c r="D245" s="8">
+      <c r="D245" s="10">
         <v>1</v>
       </c>
-      <c r="E245" s="8" t="s">
+      <c r="E245" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F245" s="8">
+      <c r="F245" s="10">
         <f>F244/D244</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G245" s="8"/>
-    </row>
-    <row r="246" spans="1:7" ht="12.75">
-      <c r="A246" s="9" t="s">
+      <c r="G245" s="10"/>
+      <c r="H245" s="11"/>
+    </row>
+    <row r="246" spans="1:8" ht="12.75">
+      <c r="A246" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
       <c r="D246" s="4"/>
-      <c r="E246" s="8">
+      <c r="E246" s="10">
         <f>F245</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F246" s="8">
+      <c r="F246" s="10">
         <f>E246*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G246" s="8"/>
-    </row>
-    <row r="247" spans="1:7" ht="12.75">
-      <c r="A247" s="16" t="s">
+      <c r="G246" s="10"/>
+      <c r="H246" s="11">
+        <f>E246+E236</f>
+        <v>742.88194180000005</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="12.75">
+      <c r="A247" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
       <c r="D247" s="4"/>
-      <c r="E247" s="8"/>
-      <c r="F247" s="17">
+      <c r="E247" s="10"/>
+      <c r="F247" s="21">
         <f>ROUND(F245+F246,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G247" s="8"/>
-    </row>
-    <row r="248" spans="1:7" ht="12.75">
-      <c r="A248" s="18" t="s">
+      <c r="G247" s="10"/>
+      <c r="H247" s="11">
+        <f>F247+F237</f>
+        <v>854.32</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="12.75">
+      <c r="A248" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B248" s="3"/>
-      <c r="C248" s="3"/>
-      <c r="D248" s="3"/>
-      <c r="E248" s="3"/>
-      <c r="F248" s="4"/>
-      <c r="G248" s="17" t="s">
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+      <c r="D248" s="25"/>
+      <c r="E248" s="25"/>
+      <c r="F248" s="26"/>
+      <c r="G248" s="27" t="s">
         <v>41</v>
       </c>
+      <c r="H248" s="23"/>
+    </row>
+    <row r="249" spans="1:8" ht="12.75">
+      <c r="A249" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D249" s="3"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G249" s="4"/>
+      <c r="H249" s="5"/>
+    </row>
+    <row r="250" spans="1:8" ht="12.75">
+      <c r="A250" s="6"/>
+      <c r="B250" s="6"/>
+      <c r="C250" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H250" s="5"/>
+    </row>
+    <row r="251" spans="1:8" ht="12.75">
+      <c r="A251" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
+      <c r="E251" s="3"/>
+      <c r="F251" s="3"/>
+      <c r="G251" s="4"/>
+      <c r="H251" s="9"/>
+    </row>
+    <row r="252" spans="1:8" ht="12.75">
+      <c r="A252" s="10"/>
+      <c r="B252" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252" s="10">
+        <v>50</v>
+      </c>
+      <c r="F252" s="10"/>
+      <c r="G252" s="10"/>
+      <c r="H252" s="11"/>
+    </row>
+    <row r="253" spans="1:8" ht="12.75">
+      <c r="A253" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" s="3"/>
+      <c r="D253" s="3"/>
+      <c r="E253" s="3"/>
+      <c r="F253" s="3"/>
+      <c r="G253" s="4"/>
+      <c r="H253" s="11"/>
+    </row>
+    <row r="254" spans="1:8" ht="12.75">
+      <c r="A254" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="3"/>
+      <c r="F254" s="3"/>
+      <c r="G254" s="4"/>
+      <c r="H254" s="11"/>
+    </row>
+    <row r="255" spans="1:8" ht="12.75">
+      <c r="A255" s="13"/>
+      <c r="B255" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C255" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D255" s="3"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="15"/>
+      <c r="G255" s="4"/>
+      <c r="H255" s="16"/>
+    </row>
+    <row r="256" spans="1:8" ht="12.75">
+      <c r="A256" s="6"/>
+      <c r="B256" s="6"/>
+      <c r="C256" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D256" s="17">
+        <v>50</v>
+      </c>
+      <c r="E256" s="17">
+        <v>425.42</v>
+      </c>
+      <c r="F256" s="17">
+        <f>D256*E256</f>
+        <v>21271</v>
+      </c>
+      <c r="G256" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H256" s="16"/>
+    </row>
+    <row r="257" spans="1:8" ht="12.75">
+      <c r="A257" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B257" s="13"/>
+      <c r="C257" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D257" s="3"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="15"/>
+      <c r="G257" s="4"/>
+      <c r="H257" s="16"/>
+    </row>
+    <row r="258" spans="1:8" ht="12.75">
+      <c r="A258" s="6"/>
+      <c r="B258" s="6"/>
+      <c r="C258" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D258" s="17"/>
+      <c r="E258" s="17"/>
+      <c r="F258" s="17">
+        <f>F256*5%</f>
+        <v>1063.55</v>
+      </c>
+      <c r="G258" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H258" s="16"/>
+    </row>
+    <row r="259" spans="1:8" ht="12.75">
+      <c r="A259" s="13"/>
+      <c r="B259" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C259" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D259" s="3"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="15"/>
+      <c r="G259" s="4"/>
+      <c r="H259" s="16"/>
+    </row>
+    <row r="260" spans="1:8" ht="12.75">
+      <c r="A260" s="6"/>
+      <c r="B260" s="6"/>
+      <c r="C260" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D260" s="17">
+        <v>7</v>
+      </c>
+      <c r="E260" s="17">
+        <v>675</v>
+      </c>
+      <c r="F260" s="17">
+        <f>D260*E260</f>
+        <v>4725</v>
+      </c>
+      <c r="G260" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H260" s="16"/>
+    </row>
+    <row r="261" spans="1:8" ht="12.75">
+      <c r="A261" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B261" s="13"/>
+      <c r="C261" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D261" s="3"/>
+      <c r="E261" s="4"/>
+      <c r="F261" s="15"/>
+      <c r="G261" s="4"/>
+      <c r="H261" s="16"/>
+    </row>
+    <row r="262" spans="1:8" ht="12.75">
+      <c r="A262" s="6"/>
+      <c r="B262" s="6"/>
+      <c r="C262" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D262" s="17"/>
+      <c r="E262" s="17"/>
+      <c r="F262" s="17">
+        <f>(F256+F258+F260)*1%</f>
+        <v>270.59550000000002</v>
+      </c>
+      <c r="G262" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H262" s="16"/>
+    </row>
+    <row r="263" spans="1:8" ht="12.75">
+      <c r="A263" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B263" s="3"/>
+      <c r="C263" s="4"/>
+      <c r="D263" s="10">
+        <v>50</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F263" s="10">
+        <f>F256+F258+F260+F262</f>
+        <v>27330.145499999999</v>
+      </c>
+      <c r="G263" s="10"/>
+      <c r="H263" s="11"/>
+    </row>
+    <row r="264" spans="1:8" ht="12.75">
+      <c r="A264" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B264" s="3"/>
+      <c r="C264" s="4"/>
+      <c r="D264" s="10">
+        <v>1</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F264" s="10">
+        <f>F263/D263</f>
+        <v>546.60290999999995</v>
+      </c>
+      <c r="G264" s="10"/>
+      <c r="H264" s="11"/>
+    </row>
+    <row r="265" spans="1:8" ht="12.75">
+      <c r="A265" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="4"/>
+      <c r="E265" s="19">
+        <f>F256*105%*101%/D263</f>
+        <v>451.15791000000002</v>
+      </c>
+      <c r="F265" s="10">
+        <f>E265*1%</f>
+        <v>4.5115790999999996</v>
+      </c>
+      <c r="G265" s="10"/>
+      <c r="H265" s="11"/>
+    </row>
+    <row r="266" spans="1:8" ht="12.75">
+      <c r="A266" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="4"/>
+      <c r="E266" s="10"/>
+      <c r="F266" s="10">
+        <f>F264+F265</f>
+        <v>551.11448910000001</v>
+      </c>
+      <c r="G266" s="10"/>
+      <c r="H266" s="11"/>
+    </row>
+    <row r="267" spans="1:8" ht="12.75">
+      <c r="A267" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B267" s="3"/>
+      <c r="C267" s="3"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="10">
+        <f>F266</f>
+        <v>551.11448910000001</v>
+      </c>
+      <c r="F267" s="10">
+        <f>E267*15%</f>
+        <v>82.66717337</v>
+      </c>
+      <c r="G267" s="10"/>
+      <c r="H267" s="11"/>
+    </row>
+    <row r="268" spans="1:8" ht="12.75">
+      <c r="A268" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B268" s="3"/>
+      <c r="C268" s="3"/>
+      <c r="D268" s="4"/>
+      <c r="E268" s="10"/>
+      <c r="F268" s="21">
+        <f>ROUND(F266+F267,2)</f>
+        <v>633.78</v>
+      </c>
+      <c r="G268" s="10"/>
+      <c r="H268" s="11"/>
+    </row>
+    <row r="269" spans="1:8" ht="12.75">
+      <c r="A269" s="14">
+        <v>1001</v>
+      </c>
+      <c r="B269" s="13"/>
+      <c r="C269" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D269" s="3"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="15"/>
+      <c r="G269" s="4"/>
+      <c r="H269" s="16"/>
+    </row>
+    <row r="270" spans="1:8" ht="12.75">
+      <c r="A270" s="6"/>
+      <c r="B270" s="6"/>
+      <c r="C270" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D270" s="17">
+        <v>1</v>
+      </c>
+      <c r="E270" s="17">
+        <v>806</v>
+      </c>
+      <c r="F270" s="17">
+        <f>E270*D270</f>
+        <v>806</v>
+      </c>
+      <c r="G270" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H270" s="16"/>
+    </row>
+    <row r="271" spans="1:8" ht="12.75">
+      <c r="A271" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B271" s="13"/>
+      <c r="C271" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D271" s="3"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="15"/>
+      <c r="G271" s="4"/>
+      <c r="H271" s="16"/>
+    </row>
+    <row r="272" spans="1:8" ht="12.75">
+      <c r="A272" s="6"/>
+      <c r="B272" s="6"/>
+      <c r="C272" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D272" s="17"/>
+      <c r="E272" s="17"/>
+      <c r="F272" s="17">
+        <f>F270*1%</f>
+        <v>8.06</v>
+      </c>
+      <c r="G272" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H272" s="16">
+        <f>F272+F262</f>
+        <v>278.65550000000002</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="12.75">
+      <c r="A273" s="17">
+        <v>14.40</v>
+      </c>
+      <c r="B273" s="17"/>
+      <c r="C273" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D273" s="3"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="17"/>
+      <c r="G273" s="17"/>
+      <c r="H273" s="16"/>
+    </row>
+    <row r="274" spans="1:8" ht="12.75">
+      <c r="A274" s="17"/>
+      <c r="B274" s="17"/>
+      <c r="C274" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D274" s="17">
+        <v>13.13</v>
+      </c>
+      <c r="E274" s="17">
+        <v>498.87</v>
+      </c>
+      <c r="F274" s="17">
+        <f>D274*E274</f>
+        <v>6550.1630999999998</v>
+      </c>
+      <c r="G274" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H274" s="16"/>
+    </row>
+    <row r="275" spans="1:8" ht="12.75">
+      <c r="A275" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B275" s="3"/>
+      <c r="C275" s="4"/>
+      <c r="D275" s="10">
+        <v>50</v>
+      </c>
+      <c r="E275" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F275" s="10">
+        <f>F270+F272+F274</f>
+        <v>7364.2231000000002</v>
+      </c>
+      <c r="G275" s="10"/>
+      <c r="H275" s="11"/>
+    </row>
+    <row r="276" spans="1:8" ht="12.75">
+      <c r="A276" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B276" s="3"/>
+      <c r="C276" s="4"/>
+      <c r="D276" s="10">
+        <v>1</v>
+      </c>
+      <c r="E276" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F276" s="10">
+        <f>F275/D275</f>
+        <v>147.28446199999999</v>
+      </c>
+      <c r="G276" s="10"/>
+      <c r="H276" s="11"/>
+    </row>
+    <row r="277" spans="1:8" ht="12.75">
+      <c r="A277" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B277" s="3"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="4"/>
+      <c r="E277" s="10">
+        <f>F276</f>
+        <v>147.28446199999999</v>
+      </c>
+      <c r="F277" s="10">
+        <f>E277*15%</f>
+        <v>22.092669300000001</v>
+      </c>
+      <c r="G277" s="10"/>
+      <c r="H277" s="11">
+        <f>E277+E267</f>
+        <v>698.39895109999998</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="12.75">
+      <c r="A278" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B278" s="3"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="4"/>
+      <c r="E278" s="10"/>
+      <c r="F278" s="21">
+        <f>ROUND(F276+F277,2)</f>
+        <v>169.38</v>
+      </c>
+      <c r="G278" s="10"/>
+      <c r="H278" s="11">
+        <f>F278+F268</f>
+        <v>803.16</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="12.75">
+      <c r="A279" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="3"/>
+      <c r="E279" s="3"/>
+      <c r="F279" s="4"/>
+      <c r="G279" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H279" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="344">
+  <mergeCells count="387">
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A93:F93"/>
@@ -4790,6 +5695,172 @@
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A110:D110"/>
     <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A266:D266"/>
+    <mergeCell ref="A267:D267"/>
+    <mergeCell ref="A268:D268"/>
+    <mergeCell ref="A269:A270"/>
+    <mergeCell ref="B269:B270"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="F269:G269"/>
+    <mergeCell ref="A271:A272"/>
+    <mergeCell ref="B271:B272"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="F271:G271"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="A275:C275"/>
+    <mergeCell ref="A276:C276"/>
+    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A237:D237"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="F238:G238"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="A244:C244"/>
+    <mergeCell ref="A245:C245"/>
+    <mergeCell ref="A246:D246"/>
+    <mergeCell ref="A247:D247"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="F255:G255"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="F257:G257"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="F259:G259"/>
+    <mergeCell ref="A248:F248"/>
+    <mergeCell ref="B249:B250"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="F249:G249"/>
+    <mergeCell ref="A251:G251"/>
+    <mergeCell ref="B253:G253"/>
+    <mergeCell ref="A254:G254"/>
+    <mergeCell ref="A249:A250"/>
+    <mergeCell ref="A255:A256"/>
+    <mergeCell ref="B255:B256"/>
+    <mergeCell ref="A257:A258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="A261:A262"/>
+    <mergeCell ref="B261:B262"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="F261:G261"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A264:C264"/>
+    <mergeCell ref="A265:D265"/>
+    <mergeCell ref="A277:D277"/>
+    <mergeCell ref="A278:D278"/>
+    <mergeCell ref="A279:F279"/>
     <mergeCell ref="A153:D153"/>
     <mergeCell ref="A154:D154"/>
     <mergeCell ref="A155:F155"/>
@@ -4899,22 +5970,6 @@
     <mergeCell ref="B228:B229"/>
     <mergeCell ref="C228:E228"/>
     <mergeCell ref="F228:G228"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="A244:C244"/>
-    <mergeCell ref="A245:C245"/>
-    <mergeCell ref="A246:D246"/>
-    <mergeCell ref="A247:D247"/>
-    <mergeCell ref="A248:F248"/>
-    <mergeCell ref="A236:D236"/>
-    <mergeCell ref="A237:D237"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="F238:G238"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="F240:G240"/>
     <mergeCell ref="A174:D174"/>
     <mergeCell ref="A175:D175"/>
     <mergeCell ref="A176:A177"/>
@@ -4964,113 +6019,6 @@
     <mergeCell ref="A233:C233"/>
     <mergeCell ref="A234:D234"/>
     <mergeCell ref="A235:D235"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="A142:D142"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A152:C152"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
+++ b/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
@@ -907,7 +907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1250D54E-3823-45FF-A7AC-1C0D06A4BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA0B4AC-04D2-45AF-BAA9-5217D323BAA6}">
   <dimension ref="A1:H279"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
+++ b/Side Bar Files/GWD Data/UG Cable PRICE.xlsx
@@ -246,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="177" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -268,13 +268,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
@@ -283,12 +276,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
@@ -440,12 +427,12 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
@@ -454,49 +441,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -507,9 +482,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -907,11 +879,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA0B4AC-04D2-45AF-BAA9-5217D323BAA6}">
-  <dimension ref="A1:H279"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8576867E-5075-4CB5-B948-9FFA08B8BAA6}">
+  <dimension ref="A1:G279"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="12.75">
+    <row r="1" spans="1:7" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,30 +899,28 @@
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" ht="12.75">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="12.75">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" ht="12.75">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="12.75">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3"/>
@@ -959,31 +929,29 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:8" ht="12.75">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="12.75">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>50</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:8" ht="12.75">
-      <c r="A5" s="10" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" ht="12.75">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="3"/>
@@ -991,10 +959,9 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:8" ht="12.75">
-      <c r="A6" s="12" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="12.75">
+      <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="3"/>
@@ -1003,424 +970,393 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" ht="12.75">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="12.75">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="15"/>
+      <c r="F7" s="12"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="12.75">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="17" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="12.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="13">
         <v>50</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="13">
         <v>118.64</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="13">
         <f>D8*E8</f>
         <v>5932</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="12.75">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="12.75">
+      <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="12"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="12.75">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="17" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="12.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13">
         <f>F8*5%</f>
         <v>296.60</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="12.75">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="12.75">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="15"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="12.75">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="17" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="12.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="13">
         <v>7</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="13">
         <v>675</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="13">
         <f>D12*E12</f>
         <v>4725</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:8" ht="12.75">
-      <c r="A13" s="14" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="12.75">
+      <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="18" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="15"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="12.75">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="17" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="12.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13">
         <f>(F8+F10+F12)*1%</f>
         <v>109.536</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8" ht="12.75">
-      <c r="A15" s="12" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="12.75">
+      <c r="A15" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="10">
+      <c r="D15" s="8">
         <v>50</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="8">
         <f>F8+F10+F12+F14</f>
         <v>11063.136</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" ht="12.75">
-      <c r="A16" s="12" t="s">
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="1:7" ht="12.75">
+      <c r="A16" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>1</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="8">
         <f>F15/D15</f>
         <v>221.26272</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" ht="12.75">
-      <c r="A17" s="12" t="s">
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:7" ht="12.75">
+      <c r="A17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="19">
+      <c r="E17" s="15">
         <f>F8*105%*101%/D15</f>
         <v>125.81771999999999</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="8">
         <f>E17*1%</f>
         <v>1.2581772</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:8" ht="12.75">
-      <c r="A18" s="12" t="s">
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" ht="12.75">
+      <c r="A18" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10">
+      <c r="E18" s="8"/>
+      <c r="F18" s="8">
         <f>F16+F17</f>
         <v>222.52089720000001</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" spans="1:8" ht="12.75">
-      <c r="A19" s="12" t="s">
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7" ht="12.75">
+      <c r="A19" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <f>F18</f>
         <v>222.52089720000001</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="8">
         <f>E19*15%</f>
         <v>33.378134580000001</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" ht="12.75">
-      <c r="A20" s="20" t="s">
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" ht="12.75">
+      <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="21">
+      <c r="E20" s="8"/>
+      <c r="F20" s="17">
         <f>ROUND(F18+F19,2)</f>
         <v>255.90</v>
       </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="1:8" ht="12.75">
-      <c r="A21" s="14">
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" ht="12.75">
+      <c r="A21" s="11">
         <v>1001</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" spans="1:8" ht="12.75">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="17" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="12.75">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="13">
         <v>1</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="13">
         <v>806</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="13">
         <f>E22*D22</f>
         <v>806</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" spans="1:8" ht="12.75">
-      <c r="A23" s="14" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="12.75">
+      <c r="A23" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="18" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="15"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" spans="1:8" ht="12.75">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="17" t="s">
+    </row>
+    <row r="24" spans="1:7" ht="12.75">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13">
         <f>F22*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="16">
-        <f>F24+F14</f>
-        <v>117.596</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="12.75">
-      <c r="A25" s="17">
+    </row>
+    <row r="25" spans="1:7" ht="12.75">
+      <c r="A25" s="13">
         <v>14.40</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="15" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" spans="1:8" ht="12.75">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17" t="s">
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="26" spans="1:7" ht="12.75">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="13">
         <v>13.13</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="13">
         <v>498.87</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="13">
         <f>D26*E26</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="1:8" ht="12.75">
-      <c r="A27" s="12" t="s">
+    </row>
+    <row r="27" spans="1:7" ht="12.75">
+      <c r="A27" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <v>50</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="8">
         <f>F22+F24+F26</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="12.75">
-      <c r="A28" s="12" t="s">
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" spans="1:7" ht="12.75">
+      <c r="A28" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="10">
+      <c r="D28" s="8">
         <v>1</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="8">
         <f>F27/D27</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" spans="1:8" ht="12.75">
-      <c r="A29" s="12" t="s">
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="1:7" ht="12.75">
+      <c r="A29" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="10">
+      <c r="E29" s="8">
         <f>F28</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="8">
         <f>E29*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="1:8" ht="12.75">
-      <c r="A30" s="20" t="s">
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="1:7" ht="12.75">
+      <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="21">
+      <c r="E30" s="8"/>
+      <c r="F30" s="17">
         <f>ROUND(F28+F29,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="11">
-        <f>F30+F20</f>
-        <v>425.28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="12.75">
-      <c r="A31" s="22" t="s">
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" ht="12.75">
+      <c r="A31" s="18" t="s">
         <v>40</v>
       </c>
       <c r="B31" s="3"/>
@@ -1428,12 +1364,11 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="21" t="s">
+      <c r="G31" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H31" s="23"/>
-    </row>
-    <row r="32" spans="1:8" ht="12.75">
+    </row>
+    <row r="32" spans="1:7" ht="12.75">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,30 +1384,28 @@
         <v>3</v>
       </c>
       <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:8" ht="12.75">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7" t="s">
+    </row>
+    <row r="33" spans="1:7" ht="12.75">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="1:8" ht="12.75">
-      <c r="A34" s="8" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="12.75">
+      <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="3"/>
@@ -1481,31 +1414,29 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" ht="12.75">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10" t="s">
+    </row>
+    <row r="35" spans="1:7" ht="12.75">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="8">
         <v>50</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" ht="12.75">
-      <c r="A36" s="10" t="s">
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" spans="1:7" ht="12.75">
+      <c r="A36" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="3"/>
@@ -1513,10 +1444,9 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" spans="1:8" ht="12.75">
-      <c r="A37" s="12" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="12.75">
+      <c r="A37" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="3"/>
@@ -1525,424 +1455,393 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" spans="1:8" ht="12.75">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="12.75">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="12" t="s">
         <v>44</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="15"/>
+      <c r="F38" s="12"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" ht="12.75">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="17" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="12.75">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="13">
         <v>50</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="13">
         <v>159.32</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="13">
         <f>D39*E39</f>
         <v>7966</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:8" ht="12.75">
-      <c r="A40" s="14" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="12.75">
+      <c r="A40" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="15"/>
+      <c r="F40" s="12"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" spans="1:8" ht="12.75">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="17" t="s">
+    </row>
+    <row r="41" spans="1:7" ht="12.75">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17">
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13">
         <f>F39*5%</f>
         <v>398.30</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G41" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" spans="1:8" ht="12.75">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14" t="s">
+    </row>
+    <row r="42" spans="1:7" ht="12.75">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="15"/>
+      <c r="F42" s="12"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" spans="1:8" ht="12.75">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="17" t="s">
+    </row>
+    <row r="43" spans="1:7" ht="12.75">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="13">
         <v>7</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="13">
         <v>675</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="13">
         <f>D43*E43</f>
         <v>4725</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" spans="1:8" ht="12.75">
-      <c r="A44" s="14" t="s">
+    </row>
+    <row r="44" spans="1:7" ht="12.75">
+      <c r="A44" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="18" t="s">
+      <c r="B44" s="10"/>
+      <c r="C44" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="15"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" spans="1:8" ht="12.75">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="17" t="s">
+    </row>
+    <row r="45" spans="1:7" ht="12.75">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17">
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13">
         <f>(F39+F41+F43)*1%</f>
         <v>130.893</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G45" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H45" s="16"/>
-    </row>
-    <row r="46" spans="1:8" ht="12.75">
-      <c r="A46" s="12" t="s">
+    </row>
+    <row r="46" spans="1:7" ht="12.75">
+      <c r="A46" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="10">
+      <c r="D46" s="8">
         <v>50</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="8">
         <f>F39+F41+F43+F45</f>
         <v>13220.192999999999</v>
       </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" spans="1:8" ht="12.75">
-      <c r="A47" s="12" t="s">
+      <c r="G46" s="8"/>
+    </row>
+    <row r="47" spans="1:7" ht="12.75">
+      <c r="A47" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="10">
+      <c r="D47" s="8">
         <v>1</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="8">
         <f>F46/D46</f>
         <v>264.40386000000001</v>
       </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" spans="1:8" ht="12.75">
-      <c r="A48" s="12" t="s">
+      <c r="G47" s="8"/>
+    </row>
+    <row r="48" spans="1:7" ht="12.75">
+      <c r="A48" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="19">
+      <c r="E48" s="15">
         <f>F39*105%*101%/D46</f>
         <v>168.95885999999999</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="8">
         <f>E48*1%</f>
         <v>1.6895886</v>
       </c>
-      <c r="G48" s="10"/>
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" spans="1:8" ht="12.75">
-      <c r="A49" s="12" t="s">
+      <c r="G48" s="8"/>
+    </row>
+    <row r="49" spans="1:7" ht="12.75">
+      <c r="A49" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10">
+      <c r="E49" s="8"/>
+      <c r="F49" s="8">
         <f>F47+F48</f>
         <v>266.09344859999999</v>
       </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" spans="1:8" ht="12.75">
-      <c r="A50" s="12" t="s">
+      <c r="G49" s="8"/>
+    </row>
+    <row r="50" spans="1:7" ht="12.75">
+      <c r="A50" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="10">
+      <c r="E50" s="8">
         <f>F49</f>
         <v>266.09344859999999</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="8">
         <f>E50*15%</f>
         <v>39.914017289999997</v>
       </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" spans="1:8" ht="12.75">
-      <c r="A51" s="20" t="s">
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51" spans="1:7" ht="12.75">
+      <c r="A51" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="21">
+      <c r="E51" s="8"/>
+      <c r="F51" s="17">
         <f>ROUND(F49+F50,2)</f>
         <v>306.01</v>
       </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" spans="1:8" ht="12.75">
-      <c r="A52" s="14">
+      <c r="G51" s="8"/>
+    </row>
+    <row r="52" spans="1:7" ht="12.75">
+      <c r="A52" s="11">
         <v>1001</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="10"/>
+      <c r="C52" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="15"/>
+      <c r="F52" s="12"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" spans="1:8" ht="12.75">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="17" t="s">
+    </row>
+    <row r="53" spans="1:7" ht="12.75">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="13">
         <v>1</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="13">
         <v>806</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="13">
         <f>E53*D53</f>
         <v>806</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="16"/>
-    </row>
-    <row r="54" spans="1:8" ht="12.75">
-      <c r="A54" s="14" t="s">
+    </row>
+    <row r="54" spans="1:7" ht="12.75">
+      <c r="A54" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="18" t="s">
+      <c r="B54" s="10"/>
+      <c r="C54" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="15"/>
+      <c r="F54" s="12"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" spans="1:8" ht="12.75">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="17" t="s">
+    </row>
+    <row r="55" spans="1:7" ht="12.75">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13">
         <f>F53*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G55" s="17" t="s">
+      <c r="G55" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H55" s="16">
-        <f>F55+F45</f>
-        <v>138.953</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="12.75">
-      <c r="A56" s="17">
+    </row>
+    <row r="56" spans="1:7" ht="12.75">
+      <c r="A56" s="13">
         <v>14.40</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="15" t="s">
+      <c r="B56" s="13"/>
+      <c r="C56" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" spans="1:8" ht="12.75">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17" t="s">
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" spans="1:7" ht="12.75">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="13">
         <v>13.13</v>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="13">
         <v>498.87</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="13">
         <f>D57*E57</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G57" s="17" t="s">
+      <c r="G57" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H57" s="16"/>
-    </row>
-    <row r="58" spans="1:8" ht="12.75">
-      <c r="A58" s="12" t="s">
+    </row>
+    <row r="58" spans="1:7" ht="12.75">
+      <c r="A58" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="10">
+      <c r="D58" s="8">
         <v>50</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="8">
         <f>F53+F55+F57</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G58" s="10"/>
-      <c r="H58" s="11"/>
-    </row>
-    <row r="59" spans="1:8" ht="12.75">
-      <c r="A59" s="12" t="s">
+      <c r="G58" s="8"/>
+    </row>
+    <row r="59" spans="1:7" ht="12.75">
+      <c r="A59" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="10">
+      <c r="D59" s="8">
         <v>1</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="8">
         <f>F58/D58</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G59" s="10"/>
-      <c r="H59" s="11"/>
-    </row>
-    <row r="60" spans="1:8" ht="12.75">
-      <c r="A60" s="12" t="s">
+      <c r="G59" s="8"/>
+    </row>
+    <row r="60" spans="1:7" ht="12.75">
+      <c r="A60" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="10">
+      <c r="E60" s="8">
         <f>F59</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="8">
         <f>E60*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G60" s="10"/>
-      <c r="H60" s="11"/>
-    </row>
-    <row r="61" spans="1:8" ht="12.75">
-      <c r="A61" s="20" t="s">
+      <c r="G60" s="8"/>
+    </row>
+    <row r="61" spans="1:7" ht="12.75">
+      <c r="A61" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="21">
+      <c r="E61" s="8"/>
+      <c r="F61" s="17">
         <f>ROUND(F59+F60,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G61" s="10"/>
-      <c r="H61" s="11">
-        <f>F61+F51</f>
-        <v>475.39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="12.75">
-      <c r="A62" s="22" t="s">
+      <c r="G61" s="8"/>
+    </row>
+    <row r="62" spans="1:7" ht="12.75">
+      <c r="A62" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="3"/>
@@ -1950,12 +1849,11 @@
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="21" t="s">
+      <c r="G62" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H62" s="23"/>
-    </row>
-    <row r="63" spans="1:8" ht="12.75">
+    </row>
+    <row r="63" spans="1:7" ht="12.75">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
@@ -1971,30 +1869,28 @@
         <v>3</v>
       </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" spans="1:8" ht="12.75">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="7" t="s">
+    </row>
+    <row r="64" spans="1:7" ht="12.75">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H64" s="5"/>
-    </row>
-    <row r="65" spans="1:8" ht="12.75">
-      <c r="A65" s="8" t="s">
+    </row>
+    <row r="65" spans="1:7" ht="12.75">
+      <c r="A65" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B65" s="3"/>
@@ -2003,31 +1899,29 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="1:8" ht="12.75">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10" t="s">
+    </row>
+    <row r="66" spans="1:7" ht="12.75">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="10">
+      <c r="E66" s="8">
         <v>50</v>
       </c>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="11"/>
-    </row>
-    <row r="67" spans="1:8" ht="12.75">
-      <c r="A67" s="10" t="s">
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+    </row>
+    <row r="67" spans="1:7" ht="12.75">
+      <c r="A67" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="3"/>
@@ -2035,10 +1929,9 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="11"/>
-    </row>
-    <row r="68" spans="1:8" ht="12.75">
-      <c r="A68" s="12" t="s">
+    </row>
+    <row r="68" spans="1:7" ht="12.75">
+      <c r="A68" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B68" s="3"/>
@@ -2047,430 +1940,393 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="4"/>
-      <c r="H68" s="11"/>
-    </row>
-    <row r="69" spans="1:8" ht="12.75">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14" t="s">
+    </row>
+    <row r="69" spans="1:7" ht="12.75">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="12" t="s">
         <v>48</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="15"/>
+      <c r="F69" s="12"/>
       <c r="G69" s="4"/>
-      <c r="H69" s="16"/>
-    </row>
-    <row r="70" spans="1:8" ht="12.75">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="17" t="s">
+    </row>
+    <row r="70" spans="1:7" ht="12.75">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="13">
         <v>50</v>
       </c>
-      <c r="E70" s="17">
+      <c r="E70" s="13">
         <v>241.53</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="13">
         <f>D70*E70</f>
         <v>12076.50</v>
       </c>
-      <c r="G70" s="17" t="s">
+      <c r="G70" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H70" s="16"/>
-    </row>
-    <row r="71" spans="1:8" ht="12.75">
-      <c r="A71" s="14" t="s">
+    </row>
+    <row r="71" spans="1:7" ht="12.75">
+      <c r="A71" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="15" t="s">
+      <c r="B71" s="10"/>
+      <c r="C71" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="15"/>
+      <c r="F71" s="12"/>
       <c r="G71" s="4"/>
-      <c r="H71" s="16"/>
-    </row>
-    <row r="72" spans="1:8" ht="12.75">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="17" t="s">
+    </row>
+    <row r="72" spans="1:7" ht="12.75">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17">
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13">
         <f>F70*5%</f>
         <v>603.825</v>
       </c>
-      <c r="G72" s="17" t="s">
+      <c r="G72" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="1:8" ht="12.75">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14" t="s">
+    </row>
+    <row r="73" spans="1:7" ht="12.75">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="15"/>
+      <c r="F73" s="12"/>
       <c r="G73" s="4"/>
-      <c r="H73" s="16"/>
-    </row>
-    <row r="74" spans="1:8" ht="12.75">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="17" t="s">
+    </row>
+    <row r="74" spans="1:7" ht="12.75">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="17">
+      <c r="D74" s="13">
         <v>7</v>
       </c>
-      <c r="E74" s="17">
+      <c r="E74" s="13">
         <v>675</v>
       </c>
-      <c r="F74" s="17">
+      <c r="F74" s="13">
         <f>D74*E74</f>
         <v>4725</v>
       </c>
-      <c r="G74" s="17" t="s">
+      <c r="G74" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H74" s="16"/>
-    </row>
-    <row r="75" spans="1:8" ht="12.75">
-      <c r="A75" s="14" t="s">
+    </row>
+    <row r="75" spans="1:7" ht="12.75">
+      <c r="A75" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="18" t="s">
+      <c r="B75" s="10"/>
+      <c r="C75" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="15"/>
+      <c r="F75" s="12"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="16"/>
-    </row>
-    <row r="76" spans="1:8" ht="12.75">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="17" t="s">
+    </row>
+    <row r="76" spans="1:7" ht="12.75">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="17">
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13">
         <f>(F70+F72+F74)*1%</f>
         <v>174.05324999999999</v>
       </c>
-      <c r="G76" s="17" t="s">
+      <c r="G76" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H76" s="16"/>
-    </row>
-    <row r="77" spans="1:8" ht="12.75">
-      <c r="A77" s="12" t="s">
+    </row>
+    <row r="77" spans="1:7" ht="12.75">
+      <c r="A77" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="10">
+      <c r="D77" s="8">
         <v>50</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="10">
+      <c r="F77" s="8">
         <f>F70+F72+F74+F76</f>
         <v>17579.378250000002</v>
       </c>
-      <c r="G77" s="10"/>
-      <c r="H77" s="11"/>
-    </row>
-    <row r="78" spans="1:8" ht="12.75">
-      <c r="A78" s="12" t="s">
+      <c r="G77" s="8"/>
+    </row>
+    <row r="78" spans="1:7" ht="12.75">
+      <c r="A78" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="10">
+      <c r="D78" s="8">
         <v>1</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78" s="8">
         <f>F77/D77</f>
         <v>351.58756499999998</v>
       </c>
-      <c r="G78" s="10"/>
-      <c r="H78" s="11"/>
-    </row>
-    <row r="79" spans="1:8" ht="12.75">
-      <c r="A79" s="12" t="s">
+      <c r="G78" s="8"/>
+    </row>
+    <row r="79" spans="1:7" ht="12.75">
+      <c r="A79" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="19">
+      <c r="E79" s="15">
         <f>F70*105%*101%/D77</f>
         <v>256.14256499999999</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79" s="8">
         <f>E79*1%</f>
         <v>2.5614256499999999</v>
       </c>
-      <c r="G79" s="10"/>
-      <c r="H79" s="11"/>
-    </row>
-    <row r="80" spans="1:8" ht="12.75">
-      <c r="A80" s="12" t="s">
+      <c r="G79" s="8"/>
+    </row>
+    <row r="80" spans="1:7" ht="12.75">
+      <c r="A80" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10">
+      <c r="E80" s="8"/>
+      <c r="F80" s="8">
         <f>F78+F79</f>
         <v>354.14899070000001</v>
       </c>
-      <c r="G80" s="10"/>
-      <c r="H80" s="11"/>
-    </row>
-    <row r="81" spans="1:8" ht="12.75">
-      <c r="A81" s="12" t="s">
+      <c r="G80" s="8"/>
+    </row>
+    <row r="81" spans="1:7" ht="12.75">
+      <c r="A81" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="10">
+      <c r="E81" s="8">
         <f>F80</f>
         <v>354.14899070000001</v>
       </c>
-      <c r="F81" s="10">
+      <c r="F81" s="8">
         <f>E81*15%</f>
         <v>53.122348600000002</v>
       </c>
-      <c r="G81" s="10"/>
-      <c r="H81" s="11"/>
-    </row>
-    <row r="82" spans="1:8" ht="12.75">
-      <c r="A82" s="20" t="s">
+      <c r="G81" s="8"/>
+    </row>
+    <row r="82" spans="1:7" ht="12.75">
+      <c r="A82" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="21">
+      <c r="E82" s="8"/>
+      <c r="F82" s="17">
         <f>ROUND(F80+F81,2)</f>
         <v>407.27</v>
       </c>
-      <c r="G82" s="10"/>
-      <c r="H82" s="11"/>
-    </row>
-    <row r="83" spans="1:8" ht="12.75">
-      <c r="A83" s="14">
+      <c r="G82" s="8"/>
+    </row>
+    <row r="83" spans="1:7" ht="12.75">
+      <c r="A83" s="11">
         <v>1001</v>
       </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="15" t="s">
+      <c r="B83" s="10"/>
+      <c r="C83" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="15"/>
+      <c r="F83" s="12"/>
       <c r="G83" s="4"/>
-      <c r="H83" s="16"/>
-    </row>
-    <row r="84" spans="1:8" ht="12.75">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="17" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="12.75">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D84" s="17">
+      <c r="D84" s="13">
         <v>1</v>
       </c>
-      <c r="E84" s="17">
+      <c r="E84" s="13">
         <v>806</v>
       </c>
-      <c r="F84" s="17">
+      <c r="F84" s="13">
         <f>E84*D84</f>
         <v>806</v>
       </c>
-      <c r="G84" s="17" t="s">
+      <c r="G84" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="16"/>
-    </row>
-    <row r="85" spans="1:8" ht="12.75">
-      <c r="A85" s="14" t="s">
+    </row>
+    <row r="85" spans="1:7" ht="12.75">
+      <c r="A85" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="18" t="s">
+      <c r="B85" s="10"/>
+      <c r="C85" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="15"/>
+      <c r="F85" s="12"/>
       <c r="G85" s="4"/>
-      <c r="H85" s="16"/>
-    </row>
-    <row r="86" spans="1:8" ht="12.75">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="17" t="s">
+    </row>
+    <row r="86" spans="1:7" ht="12.75">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17">
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13">
         <f>F84*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="G86" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H86" s="16">
-        <f>F86+F76</f>
-        <v>182.11324999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="12.75">
-      <c r="A87" s="17">
+    </row>
+    <row r="87" spans="1:7" ht="12.75">
+      <c r="A87" s="13">
         <v>14.40</v>
       </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="15" t="s">
+      <c r="B87" s="13"/>
+      <c r="C87" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="16"/>
-    </row>
-    <row r="88" spans="1:8" ht="12.75">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17" t="s">
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+    </row>
+    <row r="88" spans="1:7" ht="12.75">
+      <c r="A88" s="13"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="17">
+      <c r="D88" s="13">
         <v>13.13</v>
       </c>
-      <c r="E88" s="17">
+      <c r="E88" s="13">
         <v>498.87</v>
       </c>
-      <c r="F88" s="17">
+      <c r="F88" s="13">
         <f>D88*E88</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G88" s="17" t="s">
+      <c r="G88" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H88" s="16"/>
-    </row>
-    <row r="89" spans="1:8" ht="12.75">
-      <c r="A89" s="12" t="s">
+    </row>
+    <row r="89" spans="1:7" ht="12.75">
+      <c r="A89" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="10">
+      <c r="D89" s="8">
         <v>50</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="10">
+      <c r="F89" s="8">
         <f>F84+F86+F88</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G89" s="10"/>
-      <c r="H89" s="11"/>
-    </row>
-    <row r="90" spans="1:8" ht="12.75">
-      <c r="A90" s="12" t="s">
+      <c r="G89" s="8"/>
+    </row>
+    <row r="90" spans="1:7" ht="12.75">
+      <c r="A90" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="10">
+      <c r="D90" s="8">
         <v>1</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F90" s="10">
+      <c r="F90" s="8">
         <f>F89/D89</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G90" s="10"/>
-      <c r="H90" s="11">
-        <f>F90+F80</f>
-        <v>501.43345269999998</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="12.75">
-      <c r="A91" s="12" t="s">
+      <c r="G90" s="8"/>
+    </row>
+    <row r="91" spans="1:7" ht="12.75">
+      <c r="A91" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="10">
+      <c r="E91" s="8">
         <f>F90</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F91" s="10">
+      <c r="F91" s="8">
         <f>E91*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G91" s="10"/>
-      <c r="H91" s="11">
-        <f>F91+F81</f>
-        <v>75.215017900000007</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="12.75">
-      <c r="A92" s="20" t="s">
+      <c r="G91" s="8"/>
+    </row>
+    <row r="92" spans="1:7" ht="12.75">
+      <c r="A92" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="21">
+      <c r="E92" s="8"/>
+      <c r="F92" s="17">
         <f>ROUND(F90+F91,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G92" s="10"/>
-      <c r="H92" s="11">
-        <f>F92+F82</f>
-        <v>576.65</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="12.75">
-      <c r="A93" s="22" t="s">
+      <c r="G92" s="8"/>
+    </row>
+    <row r="93" spans="1:7" ht="12.75">
+      <c r="A93" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B93" s="3"/>
@@ -2478,12 +2334,11 @@
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="21" t="s">
+      <c r="G93" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H93" s="23"/>
-    </row>
-    <row r="94" spans="1:8" ht="12.75">
+    </row>
+    <row r="94" spans="1:7" ht="12.75">
       <c r="A94" s="1" t="s">
         <v>0</v>
       </c>
@@ -2499,30 +2354,28 @@
         <v>3</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="5"/>
-    </row>
-    <row r="95" spans="1:8" ht="12.75">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="7" t="s">
+    </row>
+    <row r="95" spans="1:7" ht="12.75">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="F95" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G95" s="7" t="s">
+      <c r="G95" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H95" s="5"/>
-    </row>
-    <row r="96" spans="1:8" ht="12.75">
-      <c r="A96" s="8" t="s">
+    </row>
+    <row r="96" spans="1:7" ht="12.75">
+      <c r="A96" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B96" s="3"/>
@@ -2531,31 +2384,29 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="9"/>
-    </row>
-    <row r="97" spans="1:8" ht="12.75">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10" t="s">
+    </row>
+    <row r="97" spans="1:7" ht="12.75">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="10">
+      <c r="E97" s="8">
         <v>50</v>
       </c>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="11"/>
-    </row>
-    <row r="98" spans="1:8" ht="12.75">
-      <c r="A98" s="10" t="s">
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+    </row>
+    <row r="98" spans="1:7" ht="12.75">
+      <c r="A98" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C98" s="3"/>
@@ -2563,10 +2414,9 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="11"/>
-    </row>
-    <row r="99" spans="1:8" ht="12.75">
-      <c r="A99" s="12" t="s">
+    </row>
+    <row r="99" spans="1:7" ht="12.75">
+      <c r="A99" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B99" s="3"/>
@@ -2575,424 +2425,393 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="11"/>
-    </row>
-    <row r="100" spans="1:8" ht="12.75">
-      <c r="A100" s="13"/>
-      <c r="B100" s="14" t="s">
+    </row>
+    <row r="100" spans="1:7" ht="12.75">
+      <c r="A100" s="10"/>
+      <c r="B100" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="15"/>
+      <c r="F100" s="12"/>
       <c r="G100" s="4"/>
-      <c r="H100" s="16"/>
-    </row>
-    <row r="101" spans="1:8" ht="12.75">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="17" t="s">
+    </row>
+    <row r="101" spans="1:7" ht="12.75">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D101" s="17">
+      <c r="D101" s="13">
         <v>50</v>
       </c>
-      <c r="E101" s="17">
+      <c r="E101" s="13">
         <v>343.22</v>
       </c>
-      <c r="F101" s="17">
+      <c r="F101" s="13">
         <f>D101*E101</f>
         <v>17161</v>
       </c>
-      <c r="G101" s="17" t="s">
+      <c r="G101" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H101" s="16"/>
-    </row>
-    <row r="102" spans="1:8" ht="12.75">
-      <c r="A102" s="14" t="s">
+    </row>
+    <row r="102" spans="1:7" ht="12.75">
+      <c r="A102" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="15" t="s">
+      <c r="B102" s="10"/>
+      <c r="C102" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="4"/>
-      <c r="F102" s="15"/>
+      <c r="F102" s="12"/>
       <c r="G102" s="4"/>
-      <c r="H102" s="16"/>
-    </row>
-    <row r="103" spans="1:8" ht="12.75">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="17" t="s">
+    </row>
+    <row r="103" spans="1:7" ht="12.75">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D103" s="17"/>
-      <c r="E103" s="17"/>
-      <c r="F103" s="17">
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13">
         <f>F101*5%</f>
         <v>858.05</v>
       </c>
-      <c r="G103" s="17" t="s">
+      <c r="G103" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H103" s="16"/>
-    </row>
-    <row r="104" spans="1:8" ht="12.75">
-      <c r="A104" s="13"/>
-      <c r="B104" s="14" t="s">
+    </row>
+    <row r="104" spans="1:7" ht="12.75">
+      <c r="A104" s="10"/>
+      <c r="B104" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
-      <c r="F104" s="15"/>
+      <c r="F104" s="12"/>
       <c r="G104" s="4"/>
-      <c r="H104" s="16"/>
-    </row>
-    <row r="105" spans="1:8" ht="12.75">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="17" t="s">
+    </row>
+    <row r="105" spans="1:7" ht="12.75">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D105" s="17">
+      <c r="D105" s="13">
         <v>7</v>
       </c>
-      <c r="E105" s="17">
+      <c r="E105" s="13">
         <v>675</v>
       </c>
-      <c r="F105" s="17">
+      <c r="F105" s="13">
         <f>D105*E105</f>
         <v>4725</v>
       </c>
-      <c r="G105" s="17" t="s">
+      <c r="G105" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H105" s="16"/>
-    </row>
-    <row r="106" spans="1:8" ht="12.75">
-      <c r="A106" s="14" t="s">
+    </row>
+    <row r="106" spans="1:7" ht="12.75">
+      <c r="A106" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B106" s="13"/>
-      <c r="C106" s="18" t="s">
+      <c r="B106" s="10"/>
+      <c r="C106" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="4"/>
-      <c r="F106" s="15"/>
+      <c r="F106" s="12"/>
       <c r="G106" s="4"/>
-      <c r="H106" s="16"/>
-    </row>
-    <row r="107" spans="1:8" ht="12.75">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="17" t="s">
+    </row>
+    <row r="107" spans="1:7" ht="12.75">
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D107" s="17"/>
-      <c r="E107" s="17"/>
-      <c r="F107" s="17">
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13">
         <f>(F101+F103+F105)*1%</f>
         <v>227.44049999999999</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H107" s="16"/>
-    </row>
-    <row r="108" spans="1:8" ht="12.75">
-      <c r="A108" s="12" t="s">
+    </row>
+    <row r="108" spans="1:7" ht="12.75">
+      <c r="A108" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
-      <c r="D108" s="10">
+      <c r="D108" s="8">
         <v>50</v>
       </c>
-      <c r="E108" s="10" t="s">
+      <c r="E108" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="10">
+      <c r="F108" s="8">
         <f>F101+F103+F105+F107</f>
         <v>22971.4905</v>
       </c>
-      <c r="G108" s="10"/>
-      <c r="H108" s="11"/>
-    </row>
-    <row r="109" spans="1:8" ht="12.75">
-      <c r="A109" s="12" t="s">
+      <c r="G108" s="8"/>
+    </row>
+    <row r="109" spans="1:7" ht="12.75">
+      <c r="A109" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
-      <c r="D109" s="10">
+      <c r="D109" s="8">
         <v>1</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F109" s="10">
+      <c r="F109" s="8">
         <f>F108/D108</f>
         <v>459.42980999999997</v>
       </c>
-      <c r="G109" s="10"/>
-      <c r="H109" s="11"/>
-    </row>
-    <row r="110" spans="1:8" ht="12.75">
-      <c r="A110" s="12" t="s">
+      <c r="G109" s="8"/>
+    </row>
+    <row r="110" spans="1:7" ht="12.75">
+      <c r="A110" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="4"/>
-      <c r="E110" s="19">
+      <c r="E110" s="15">
         <f>F101*105%*101%/D108</f>
         <v>363.98480999999998</v>
       </c>
-      <c r="F110" s="10">
+      <c r="F110" s="8">
         <f>E110*1%</f>
         <v>3.6398481</v>
       </c>
-      <c r="G110" s="10"/>
-      <c r="H110" s="11"/>
-    </row>
-    <row r="111" spans="1:8" ht="12.75">
-      <c r="A111" s="12" t="s">
+      <c r="G110" s="8"/>
+    </row>
+    <row r="111" spans="1:7" ht="12.75">
+      <c r="A111" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="4"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10">
+      <c r="E111" s="8"/>
+      <c r="F111" s="8">
         <f>F109+F110</f>
         <v>463.06965810000003</v>
       </c>
-      <c r="G111" s="10"/>
-      <c r="H111" s="11"/>
-    </row>
-    <row r="112" spans="1:8" ht="12.75">
-      <c r="A112" s="12" t="s">
+      <c r="G111" s="8"/>
+    </row>
+    <row r="112" spans="1:7" ht="12.75">
+      <c r="A112" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="4"/>
-      <c r="E112" s="10">
+      <c r="E112" s="8">
         <f>F111</f>
         <v>463.06965810000003</v>
       </c>
-      <c r="F112" s="10">
+      <c r="F112" s="8">
         <f>E112*15%</f>
         <v>69.460448720000002</v>
       </c>
-      <c r="G112" s="10"/>
-      <c r="H112" s="11"/>
-    </row>
-    <row r="113" spans="1:8" ht="12.75">
-      <c r="A113" s="20" t="s">
+      <c r="G112" s="8"/>
+    </row>
+    <row r="113" spans="1:7" ht="12.75">
+      <c r="A113" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="4"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="21">
+      <c r="E113" s="8"/>
+      <c r="F113" s="17">
         <f>ROUND(F111+F112,2)</f>
         <v>532.53</v>
       </c>
-      <c r="G113" s="10"/>
-      <c r="H113" s="11"/>
-    </row>
-    <row r="114" spans="1:8" ht="12.75">
-      <c r="A114" s="14">
+      <c r="G113" s="8"/>
+    </row>
+    <row r="114" spans="1:7" ht="12.75">
+      <c r="A114" s="11">
         <v>1001</v>
       </c>
-      <c r="B114" s="13"/>
-      <c r="C114" s="15" t="s">
+      <c r="B114" s="10"/>
+      <c r="C114" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="4"/>
-      <c r="F114" s="15"/>
+      <c r="F114" s="12"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="16"/>
-    </row>
-    <row r="115" spans="1:8" ht="12.75">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="17" t="s">
+    </row>
+    <row r="115" spans="1:7" ht="12.75">
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D115" s="17">
+      <c r="D115" s="13">
         <v>1</v>
       </c>
-      <c r="E115" s="17">
+      <c r="E115" s="13">
         <v>806</v>
       </c>
-      <c r="F115" s="17">
+      <c r="F115" s="13">
         <f>E115*D115</f>
         <v>806</v>
       </c>
-      <c r="G115" s="17" t="s">
+      <c r="G115" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H115" s="16"/>
-    </row>
-    <row r="116" spans="1:8" ht="12.75">
-      <c r="A116" s="14" t="s">
+    </row>
+    <row r="116" spans="1:7" ht="12.75">
+      <c r="A116" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="13"/>
-      <c r="C116" s="18" t="s">
+      <c r="B116" s="10"/>
+      <c r="C116" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="4"/>
-      <c r="F116" s="15"/>
+      <c r="F116" s="12"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="16"/>
-    </row>
-    <row r="117" spans="1:8" ht="12.75">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="17" t="s">
+    </row>
+    <row r="117" spans="1:7" ht="12.75">
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D117" s="17"/>
-      <c r="E117" s="17"/>
-      <c r="F117" s="17">
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="13">
         <f>F115*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G117" s="17" t="s">
+      <c r="G117" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H117" s="16">
-        <f>F117+F107</f>
-        <v>235.50049999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="12.75">
-      <c r="A118" s="17">
+    </row>
+    <row r="118" spans="1:7" ht="12.75">
+      <c r="A118" s="13">
         <v>14.40</v>
       </c>
-      <c r="B118" s="17"/>
-      <c r="C118" s="15" t="s">
+      <c r="B118" s="13"/>
+      <c r="C118" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="4"/>
-      <c r="F118" s="17"/>
-      <c r="G118" s="17"/>
-      <c r="H118" s="16"/>
-    </row>
-    <row r="119" spans="1:8" ht="12.75">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="17" t="s">
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+    </row>
+    <row r="119" spans="1:7" ht="12.75">
+      <c r="A119" s="13"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D119" s="17">
+      <c r="D119" s="13">
         <v>13.13</v>
       </c>
-      <c r="E119" s="17">
+      <c r="E119" s="13">
         <v>498.87</v>
       </c>
-      <c r="F119" s="17">
+      <c r="F119" s="13">
         <f>D119*E119</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G119" s="17" t="s">
+      <c r="G119" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H119" s="16"/>
-    </row>
-    <row r="120" spans="1:8" ht="12.75">
-      <c r="A120" s="12" t="s">
+    </row>
+    <row r="120" spans="1:7" ht="12.75">
+      <c r="A120" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="10">
+      <c r="D120" s="8">
         <v>50</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F120" s="10">
+      <c r="F120" s="8">
         <f>F115+F117+F119</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G120" s="10"/>
-      <c r="H120" s="11"/>
-    </row>
-    <row r="121" spans="1:8" ht="12.75">
-      <c r="A121" s="12" t="s">
+      <c r="G120" s="8"/>
+    </row>
+    <row r="121" spans="1:7" ht="12.75">
+      <c r="A121" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="10">
+      <c r="D121" s="8">
         <v>1</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F121" s="10">
+      <c r="F121" s="8">
         <f>F120/D120</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G121" s="10"/>
-      <c r="H121" s="11"/>
-    </row>
-    <row r="122" spans="1:8" ht="12.75">
-      <c r="A122" s="12" t="s">
+      <c r="G121" s="8"/>
+    </row>
+    <row r="122" spans="1:7" ht="12.75">
+      <c r="A122" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="4"/>
-      <c r="E122" s="10">
+      <c r="E122" s="8">
         <f>F121</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F122" s="10">
+      <c r="F122" s="8">
         <f>E122*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G122" s="10"/>
-      <c r="H122" s="11"/>
-    </row>
-    <row r="123" spans="1:8" ht="12.75">
-      <c r="A123" s="20" t="s">
+      <c r="G122" s="8"/>
+    </row>
+    <row r="123" spans="1:7" ht="12.75">
+      <c r="A123" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="4"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="21">
+      <c r="E123" s="8"/>
+      <c r="F123" s="17">
         <f>ROUND(F121+F122,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G123" s="10"/>
-      <c r="H123" s="11">
-        <f>F123+F113</f>
-        <v>701.91</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="12.75">
-      <c r="A124" s="22" t="s">
+      <c r="G123" s="8"/>
+    </row>
+    <row r="124" spans="1:7" ht="12.75">
+      <c r="A124" s="18" t="s">
         <v>53</v>
       </c>
       <c r="B124" s="3"/>
@@ -3000,12 +2819,11 @@
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="4"/>
-      <c r="G124" s="21" t="s">
+      <c r="G124" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="23"/>
-    </row>
-    <row r="125" spans="1:8" ht="12.75">
+    </row>
+    <row r="125" spans="1:7" ht="12.75">
       <c r="A125" s="1" t="s">
         <v>0</v>
       </c>
@@ -3021,30 +2839,28 @@
         <v>3</v>
       </c>
       <c r="G125" s="4"/>
-      <c r="H125" s="5"/>
-    </row>
-    <row r="126" spans="1:8" ht="12.75">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="7" t="s">
+    </row>
+    <row r="126" spans="1:7" ht="12.75">
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H126" s="5"/>
-    </row>
-    <row r="127" spans="1:8" ht="12.75">
-      <c r="A127" s="8" t="s">
+    </row>
+    <row r="127" spans="1:7" ht="12.75">
+      <c r="A127" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B127" s="3"/>
@@ -3053,31 +2869,29 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="4"/>
-      <c r="H127" s="9"/>
-    </row>
-    <row r="128" spans="1:8" ht="12.75">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10" t="s">
+    </row>
+    <row r="128" spans="1:7" ht="12.75">
+      <c r="A128" s="8"/>
+      <c r="B128" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="8">
         <v>50</v>
       </c>
-      <c r="F128" s="10"/>
-      <c r="G128" s="10"/>
-      <c r="H128" s="11"/>
-    </row>
-    <row r="129" spans="1:8" ht="12.75">
-      <c r="A129" s="10" t="s">
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+    </row>
+    <row r="129" spans="1:7" ht="12.75">
+      <c r="A129" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="3"/>
@@ -3085,10 +2899,9 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="11"/>
-    </row>
-    <row r="130" spans="1:8" ht="12.75">
-      <c r="A130" s="12" t="s">
+    </row>
+    <row r="130" spans="1:7" ht="12.75">
+      <c r="A130" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B130" s="3"/>
@@ -3097,427 +2910,393 @@
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="11"/>
-    </row>
-    <row r="131" spans="1:8" ht="12.75">
-      <c r="A131" s="13"/>
-      <c r="B131" s="14" t="s">
+    </row>
+    <row r="131" spans="1:7" ht="12.75">
+      <c r="A131" s="10"/>
+      <c r="B131" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="12" t="s">
         <v>56</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="4"/>
-      <c r="F131" s="15"/>
+      <c r="F131" s="12"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="16"/>
-    </row>
-    <row r="132" spans="1:8" ht="12.75">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="17" t="s">
+    </row>
+    <row r="132" spans="1:7" ht="12.75">
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="17">
+      <c r="D132" s="13">
         <v>50</v>
       </c>
-      <c r="E132" s="17">
+      <c r="E132" s="13">
         <v>153.39</v>
       </c>
-      <c r="F132" s="17">
+      <c r="F132" s="13">
         <f>D132*E132</f>
         <v>7669.50</v>
       </c>
-      <c r="G132" s="17" t="s">
+      <c r="G132" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H132" s="16"/>
-    </row>
-    <row r="133" spans="1:8" ht="12.75">
-      <c r="A133" s="14" t="s">
+    </row>
+    <row r="133" spans="1:7" ht="12.75">
+      <c r="A133" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B133" s="13"/>
-      <c r="C133" s="15" t="s">
+      <c r="B133" s="10"/>
+      <c r="C133" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="4"/>
-      <c r="F133" s="15"/>
+      <c r="F133" s="12"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="16"/>
-    </row>
-    <row r="134" spans="1:8" ht="12.75">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="17" t="s">
+    </row>
+    <row r="134" spans="1:7" ht="12.75">
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D134" s="17"/>
-      <c r="E134" s="17"/>
-      <c r="F134" s="17">
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13">
         <f>F132*5%</f>
         <v>383.475</v>
       </c>
-      <c r="G134" s="17" t="s">
+      <c r="G134" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H134" s="16"/>
-    </row>
-    <row r="135" spans="1:8" ht="12.75">
-      <c r="A135" s="13"/>
-      <c r="B135" s="14" t="s">
+    </row>
+    <row r="135" spans="1:7" ht="12.75">
+      <c r="A135" s="10"/>
+      <c r="B135" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="15" t="s">
+      <c r="C135" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="4"/>
-      <c r="F135" s="15"/>
+      <c r="F135" s="12"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="16"/>
-    </row>
-    <row r="136" spans="1:8" ht="12.75">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="17" t="s">
+    </row>
+    <row r="136" spans="1:7" ht="12.75">
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D136" s="17">
+      <c r="D136" s="13">
         <v>7</v>
       </c>
-      <c r="E136" s="17">
+      <c r="E136" s="13">
         <v>675</v>
       </c>
-      <c r="F136" s="17">
+      <c r="F136" s="13">
         <f>D136*E136</f>
         <v>4725</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G136" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H136" s="16"/>
-    </row>
-    <row r="137" spans="1:8" ht="12.75">
-      <c r="A137" s="14" t="s">
+    </row>
+    <row r="137" spans="1:7" ht="12.75">
+      <c r="A137" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B137" s="13"/>
-      <c r="C137" s="18" t="s">
+      <c r="B137" s="10"/>
+      <c r="C137" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="4"/>
-      <c r="F137" s="15"/>
+      <c r="F137" s="12"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="16"/>
-    </row>
-    <row r="138" spans="1:8" ht="12.75">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="17" t="s">
+    </row>
+    <row r="138" spans="1:7" ht="12.75">
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D138" s="17"/>
-      <c r="E138" s="17"/>
-      <c r="F138" s="17">
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="13">
         <f>(F132+F134+F136)*1%</f>
         <v>127.77975000000001</v>
       </c>
-      <c r="G138" s="17" t="s">
+      <c r="G138" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H138" s="16"/>
-    </row>
-    <row r="139" spans="1:8" ht="12.75">
-      <c r="A139" s="12" t="s">
+    </row>
+    <row r="139" spans="1:7" ht="12.75">
+      <c r="A139" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="4"/>
-      <c r="D139" s="10">
+      <c r="D139" s="8">
         <v>50</v>
       </c>
-      <c r="E139" s="10" t="s">
+      <c r="E139" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F139" s="10">
+      <c r="F139" s="8">
         <f>F132+F134+F136+F138</f>
         <v>12905.75475</v>
       </c>
-      <c r="G139" s="10"/>
-      <c r="H139" s="11"/>
-    </row>
-    <row r="140" spans="1:8" ht="12.75">
-      <c r="A140" s="12" t="s">
+      <c r="G139" s="8"/>
+    </row>
+    <row r="140" spans="1:7" ht="12.75">
+      <c r="A140" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="4"/>
-      <c r="D140" s="10">
+      <c r="D140" s="8">
         <v>1</v>
       </c>
-      <c r="E140" s="10" t="s">
+      <c r="E140" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F140" s="10">
+      <c r="F140" s="8">
         <f>F139/D139</f>
         <v>258.115095</v>
       </c>
-      <c r="G140" s="10"/>
-      <c r="H140" s="11"/>
-    </row>
-    <row r="141" spans="1:8" ht="12.75">
-      <c r="A141" s="12" t="s">
+      <c r="G140" s="8"/>
+    </row>
+    <row r="141" spans="1:7" ht="12.75">
+      <c r="A141" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="4"/>
-      <c r="E141" s="19">
+      <c r="E141" s="15">
         <f>F132*105%*101%/D139</f>
         <v>162.670095</v>
       </c>
-      <c r="F141" s="10">
+      <c r="F141" s="8">
         <f>E141*1%</f>
         <v>1.62670095</v>
       </c>
-      <c r="G141" s="10"/>
-      <c r="H141" s="11"/>
-    </row>
-    <row r="142" spans="1:8" ht="12.75">
-      <c r="A142" s="12" t="s">
+      <c r="G141" s="8"/>
+    </row>
+    <row r="142" spans="1:7" ht="12.75">
+      <c r="A142" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="4"/>
-      <c r="E142" s="10"/>
-      <c r="F142" s="10">
+      <c r="E142" s="8"/>
+      <c r="F142" s="8">
         <f>F140+F141</f>
         <v>259.74179600000002</v>
       </c>
-      <c r="G142" s="10"/>
-      <c r="H142" s="11"/>
-    </row>
-    <row r="143" spans="1:8" ht="12.75">
-      <c r="A143" s="12" t="s">
+      <c r="G142" s="8"/>
+    </row>
+    <row r="143" spans="1:7" ht="12.75">
+      <c r="A143" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="10">
+      <c r="E143" s="8">
         <f>F142</f>
         <v>259.74179600000002</v>
       </c>
-      <c r="F143" s="10">
+      <c r="F143" s="8">
         <f>E143*15%</f>
         <v>38.961269389999998</v>
       </c>
-      <c r="G143" s="10"/>
-      <c r="H143" s="11"/>
-    </row>
-    <row r="144" spans="1:8" ht="12.75">
-      <c r="A144" s="20" t="s">
+      <c r="G143" s="8"/>
+    </row>
+    <row r="144" spans="1:7" ht="12.75">
+      <c r="A144" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="4"/>
-      <c r="E144" s="10"/>
-      <c r="F144" s="21">
+      <c r="E144" s="8"/>
+      <c r="F144" s="17">
         <f>ROUND(F142+F143,2)</f>
         <v>298.70</v>
       </c>
-      <c r="G144" s="10"/>
-      <c r="H144" s="11"/>
-    </row>
-    <row r="145" spans="1:8" ht="12.75">
-      <c r="A145" s="14">
+      <c r="G144" s="8"/>
+    </row>
+    <row r="145" spans="1:7" ht="12.75">
+      <c r="A145" s="11">
         <v>1001</v>
       </c>
-      <c r="B145" s="13"/>
-      <c r="C145" s="15" t="s">
+      <c r="B145" s="10"/>
+      <c r="C145" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="4"/>
-      <c r="F145" s="15"/>
+      <c r="F145" s="12"/>
       <c r="G145" s="4"/>
-      <c r="H145" s="16"/>
-    </row>
-    <row r="146" spans="1:8" ht="12.75">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="17" t="s">
+    </row>
+    <row r="146" spans="1:7" ht="12.75">
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D146" s="17">
+      <c r="D146" s="13">
         <v>1</v>
       </c>
-      <c r="E146" s="17">
+      <c r="E146" s="13">
         <v>806</v>
       </c>
-      <c r="F146" s="17">
+      <c r="F146" s="13">
         <f>E146*D146</f>
         <v>806</v>
       </c>
-      <c r="G146" s="17" t="s">
+      <c r="G146" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H146" s="16"/>
-    </row>
-    <row r="147" spans="1:8" ht="12.75">
-      <c r="A147" s="14" t="s">
+    </row>
+    <row r="147" spans="1:7" ht="12.75">
+      <c r="A147" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B147" s="13"/>
-      <c r="C147" s="18" t="s">
+      <c r="B147" s="10"/>
+      <c r="C147" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="4"/>
-      <c r="F147" s="15"/>
+      <c r="F147" s="12"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="16"/>
-    </row>
-    <row r="148" spans="1:8" ht="12.75">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="17" t="s">
+    </row>
+    <row r="148" spans="1:7" ht="12.75">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D148" s="17"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="17">
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="13">
         <f>F146*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G148" s="17" t="s">
+      <c r="G148" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H148" s="16">
-        <f>F148+F138</f>
-        <v>135.83975000000001</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="12.75">
-      <c r="A149" s="17">
+    </row>
+    <row r="149" spans="1:7" ht="12.75">
+      <c r="A149" s="13">
         <v>14.40</v>
       </c>
-      <c r="B149" s="17"/>
-      <c r="C149" s="15" t="s">
+      <c r="B149" s="13"/>
+      <c r="C149" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="4"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="17"/>
-      <c r="H149" s="16"/>
-    </row>
-    <row r="150" spans="1:8" ht="12.75">
-      <c r="A150" s="17"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="17" t="s">
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+    </row>
+    <row r="150" spans="1:7" ht="12.75">
+      <c r="A150" s="13"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D150" s="17">
+      <c r="D150" s="13">
         <v>13.13</v>
       </c>
-      <c r="E150" s="17">
+      <c r="E150" s="13">
         <v>498.87</v>
       </c>
-      <c r="F150" s="17">
+      <c r="F150" s="13">
         <f>D150*E150</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G150" s="17" t="s">
+      <c r="G150" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H150" s="16"/>
-    </row>
-    <row r="151" spans="1:8" ht="12.75">
-      <c r="A151" s="12" t="s">
+    </row>
+    <row r="151" spans="1:7" ht="12.75">
+      <c r="A151" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="10">
+      <c r="D151" s="8">
         <v>50</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="E151" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="10">
+      <c r="F151" s="8">
         <f>F146+F148+F150</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G151" s="10"/>
-      <c r="H151" s="11"/>
-    </row>
-    <row r="152" spans="1:8" ht="12.75">
-      <c r="A152" s="12" t="s">
+      <c r="G151" s="8"/>
+    </row>
+    <row r="152" spans="1:7" ht="12.75">
+      <c r="A152" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="10">
+      <c r="D152" s="8">
         <v>1</v>
       </c>
-      <c r="E152" s="10" t="s">
+      <c r="E152" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F152" s="10">
+      <c r="F152" s="8">
         <f>F151/D151</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G152" s="10"/>
-      <c r="H152" s="11"/>
-    </row>
-    <row r="153" spans="1:8" ht="12.75">
-      <c r="A153" s="12" t="s">
+      <c r="G152" s="8"/>
+    </row>
+    <row r="153" spans="1:7" ht="12.75">
+      <c r="A153" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="10">
+      <c r="E153" s="8">
         <f>F152</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F153" s="10">
+      <c r="F153" s="8">
         <f>E153*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G153" s="10"/>
-      <c r="H153" s="11">
-        <f>E153+E143</f>
-        <v>407.02625799999998</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="12.75">
-      <c r="A154" s="20" t="s">
+      <c r="G153" s="8"/>
+    </row>
+    <row r="154" spans="1:7" ht="12.75">
+      <c r="A154" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="10"/>
-      <c r="F154" s="21">
+      <c r="E154" s="8"/>
+      <c r="F154" s="17">
         <f>ROUND(F152+F153,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G154" s="10"/>
-      <c r="H154" s="11">
-        <f>F154+F144</f>
-        <v>468.08</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="12.75">
-      <c r="A155" s="22" t="s">
+      <c r="G154" s="8"/>
+    </row>
+    <row r="155" spans="1:7" ht="12.75">
+      <c r="A155" s="18" t="s">
         <v>57</v>
       </c>
       <c r="B155" s="3"/>
@@ -3525,12 +3304,11 @@
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="4"/>
-      <c r="G155" s="21" t="s">
+      <c r="G155" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H155" s="23"/>
-    </row>
-    <row r="156" spans="1:8" ht="12.75">
+    </row>
+    <row r="156" spans="1:7" ht="12.75">
       <c r="A156" s="1" t="s">
         <v>0</v>
       </c>
@@ -3546,30 +3324,28 @@
         <v>3</v>
       </c>
       <c r="G156" s="4"/>
-      <c r="H156" s="5"/>
-    </row>
-    <row r="157" spans="1:8" ht="12.75">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="7" t="s">
+    </row>
+    <row r="157" spans="1:7" ht="12.75">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E157" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F157" s="7" t="s">
+      <c r="F157" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G157" s="7" t="s">
+      <c r="G157" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H157" s="5"/>
-    </row>
-    <row r="158" spans="1:8" ht="12.75">
-      <c r="A158" s="8" t="s">
+    </row>
+    <row r="158" spans="1:7" ht="12.75">
+      <c r="A158" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B158" s="3"/>
@@ -3578,31 +3354,29 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="4"/>
-      <c r="H158" s="9"/>
-    </row>
-    <row r="159" spans="1:8" ht="12.75">
-      <c r="A159" s="10"/>
-      <c r="B159" s="10" t="s">
+    </row>
+    <row r="159" spans="1:7" ht="12.75">
+      <c r="A159" s="8"/>
+      <c r="B159" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C159" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D159" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E159" s="10">
+      <c r="E159" s="8">
         <v>50</v>
       </c>
-      <c r="F159" s="10"/>
-      <c r="G159" s="10"/>
-      <c r="H159" s="11"/>
-    </row>
-    <row r="160" spans="1:8" ht="12.75">
-      <c r="A160" s="10" t="s">
+      <c r="F159" s="8"/>
+      <c r="G159" s="8"/>
+    </row>
+    <row r="160" spans="1:7" ht="12.75">
+      <c r="A160" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C160" s="3"/>
@@ -3610,10 +3384,9 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="4"/>
-      <c r="H160" s="11"/>
-    </row>
-    <row r="161" spans="1:8" ht="12.75">
-      <c r="A161" s="12" t="s">
+    </row>
+    <row r="161" spans="1:7" ht="12.75">
+      <c r="A161" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B161" s="3"/>
@@ -3622,427 +3395,393 @@
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="11"/>
-    </row>
-    <row r="162" spans="1:8" ht="12.75">
-      <c r="A162" s="13"/>
-      <c r="B162" s="14" t="s">
+    </row>
+    <row r="162" spans="1:7" ht="12.75">
+      <c r="A162" s="10"/>
+      <c r="B162" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C162" s="15" t="s">
+      <c r="C162" s="12" t="s">
         <v>60</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="4"/>
-      <c r="F162" s="15"/>
+      <c r="F162" s="12"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="16"/>
-    </row>
-    <row r="163" spans="1:8" ht="12.75">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="17" t="s">
+    </row>
+    <row r="163" spans="1:7" ht="12.75">
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D163" s="17">
+      <c r="D163" s="13">
         <v>50</v>
       </c>
-      <c r="E163" s="17">
+      <c r="E163" s="13">
         <v>211.86</v>
       </c>
-      <c r="F163" s="17">
+      <c r="F163" s="13">
         <f>D163*E163</f>
         <v>10593</v>
       </c>
-      <c r="G163" s="17" t="s">
+      <c r="G163" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H163" s="16"/>
-    </row>
-    <row r="164" spans="1:8" ht="12.75">
-      <c r="A164" s="14" t="s">
+    </row>
+    <row r="164" spans="1:7" ht="12.75">
+      <c r="A164" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B164" s="13"/>
-      <c r="C164" s="15" t="s">
+      <c r="B164" s="10"/>
+      <c r="C164" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="15"/>
+      <c r="F164" s="12"/>
       <c r="G164" s="4"/>
-      <c r="H164" s="16"/>
-    </row>
-    <row r="165" spans="1:8" ht="12.75">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="17" t="s">
+    </row>
+    <row r="165" spans="1:7" ht="12.75">
+      <c r="A165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D165" s="17"/>
-      <c r="E165" s="17"/>
-      <c r="F165" s="17">
+      <c r="D165" s="13"/>
+      <c r="E165" s="13"/>
+      <c r="F165" s="13">
         <f>F163*5%</f>
         <v>529.65</v>
       </c>
-      <c r="G165" s="17" t="s">
+      <c r="G165" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H165" s="16"/>
-    </row>
-    <row r="166" spans="1:8" ht="12.75">
-      <c r="A166" s="13"/>
-      <c r="B166" s="14" t="s">
+    </row>
+    <row r="166" spans="1:7" ht="12.75">
+      <c r="A166" s="10"/>
+      <c r="B166" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C166" s="15" t="s">
+      <c r="C166" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="4"/>
-      <c r="F166" s="15"/>
+      <c r="F166" s="12"/>
       <c r="G166" s="4"/>
-      <c r="H166" s="16"/>
-    </row>
-    <row r="167" spans="1:8" ht="12.75">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="17" t="s">
+    </row>
+    <row r="167" spans="1:7" ht="12.75">
+      <c r="A167" s="5"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D167" s="17">
+      <c r="D167" s="13">
         <v>7</v>
       </c>
-      <c r="E167" s="17">
+      <c r="E167" s="13">
         <v>675</v>
       </c>
-      <c r="F167" s="17">
+      <c r="F167" s="13">
         <f>D167*E167</f>
         <v>4725</v>
       </c>
-      <c r="G167" s="17" t="s">
+      <c r="G167" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H167" s="16"/>
-    </row>
-    <row r="168" spans="1:8" ht="12.75">
-      <c r="A168" s="14" t="s">
+    </row>
+    <row r="168" spans="1:7" ht="12.75">
+      <c r="A168" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B168" s="13"/>
-      <c r="C168" s="18" t="s">
+      <c r="B168" s="10"/>
+      <c r="C168" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="4"/>
-      <c r="F168" s="15"/>
+      <c r="F168" s="12"/>
       <c r="G168" s="4"/>
-      <c r="H168" s="16"/>
-    </row>
-    <row r="169" spans="1:8" ht="12.75">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="17" t="s">
+    </row>
+    <row r="169" spans="1:7" ht="12.75">
+      <c r="A169" s="5"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D169" s="17"/>
-      <c r="E169" s="17"/>
-      <c r="F169" s="17">
+      <c r="D169" s="13"/>
+      <c r="E169" s="13"/>
+      <c r="F169" s="13">
         <f>(F163+F165+F167)*1%</f>
         <v>158.47649999999999</v>
       </c>
-      <c r="G169" s="17" t="s">
+      <c r="G169" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H169" s="16"/>
-    </row>
-    <row r="170" spans="1:8" ht="12.75">
-      <c r="A170" s="12" t="s">
+    </row>
+    <row r="170" spans="1:7" ht="12.75">
+      <c r="A170" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="4"/>
-      <c r="D170" s="10">
+      <c r="D170" s="8">
         <v>50</v>
       </c>
-      <c r="E170" s="10" t="s">
+      <c r="E170" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F170" s="10">
+      <c r="F170" s="8">
         <f>F163+F165+F167+F169</f>
         <v>16006.1265</v>
       </c>
-      <c r="G170" s="10"/>
-      <c r="H170" s="11"/>
-    </row>
-    <row r="171" spans="1:8" ht="12.75">
-      <c r="A171" s="12" t="s">
+      <c r="G170" s="8"/>
+    </row>
+    <row r="171" spans="1:7" ht="12.75">
+      <c r="A171" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="4"/>
-      <c r="D171" s="10">
+      <c r="D171" s="8">
         <v>1</v>
       </c>
-      <c r="E171" s="10" t="s">
+      <c r="E171" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F171" s="10">
+      <c r="F171" s="8">
         <f>F170/D170</f>
         <v>320.12252999999998</v>
       </c>
-      <c r="G171" s="10"/>
-      <c r="H171" s="11"/>
-    </row>
-    <row r="172" spans="1:8" ht="12.75">
-      <c r="A172" s="12" t="s">
+      <c r="G171" s="8"/>
+    </row>
+    <row r="172" spans="1:7" ht="12.75">
+      <c r="A172" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="4"/>
-      <c r="E172" s="19">
+      <c r="E172" s="15">
         <f>F163*105%*101%/D170</f>
         <v>224.67752999999999</v>
       </c>
-      <c r="F172" s="10">
+      <c r="F172" s="8">
         <f>E172*1%</f>
         <v>2.2467752999999999</v>
       </c>
-      <c r="G172" s="10"/>
-      <c r="H172" s="11"/>
-    </row>
-    <row r="173" spans="1:8" ht="12.75">
-      <c r="A173" s="12" t="s">
+      <c r="G172" s="8"/>
+    </row>
+    <row r="173" spans="1:7" ht="12.75">
+      <c r="A173" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="4"/>
-      <c r="E173" s="10"/>
-      <c r="F173" s="10">
+      <c r="E173" s="8"/>
+      <c r="F173" s="8">
         <f>F171+F172</f>
         <v>322.36930530000001</v>
       </c>
-      <c r="G173" s="10"/>
-      <c r="H173" s="11"/>
-    </row>
-    <row r="174" spans="1:8" ht="12.75">
-      <c r="A174" s="12" t="s">
+      <c r="G173" s="8"/>
+    </row>
+    <row r="174" spans="1:7" ht="12.75">
+      <c r="A174" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="4"/>
-      <c r="E174" s="10">
+      <c r="E174" s="8">
         <f>F173</f>
         <v>322.36930530000001</v>
       </c>
-      <c r="F174" s="10">
+      <c r="F174" s="8">
         <f>E174*15%</f>
         <v>48.355395799999997</v>
       </c>
-      <c r="G174" s="10"/>
-      <c r="H174" s="11"/>
-    </row>
-    <row r="175" spans="1:8" ht="12.75">
-      <c r="A175" s="20" t="s">
+      <c r="G174" s="8"/>
+    </row>
+    <row r="175" spans="1:7" ht="12.75">
+      <c r="A175" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="4"/>
-      <c r="E175" s="10"/>
-      <c r="F175" s="21">
+      <c r="E175" s="8"/>
+      <c r="F175" s="17">
         <f>ROUND(F173+F174,2)</f>
         <v>370.72</v>
       </c>
-      <c r="G175" s="10"/>
-      <c r="H175" s="11"/>
-    </row>
-    <row r="176" spans="1:8" ht="12.75">
-      <c r="A176" s="14">
+      <c r="G175" s="8"/>
+    </row>
+    <row r="176" spans="1:7" ht="12.75">
+      <c r="A176" s="11">
         <v>1001</v>
       </c>
-      <c r="B176" s="13"/>
-      <c r="C176" s="15" t="s">
+      <c r="B176" s="10"/>
+      <c r="C176" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="4"/>
-      <c r="F176" s="15"/>
+      <c r="F176" s="12"/>
       <c r="G176" s="4"/>
-      <c r="H176" s="16"/>
-    </row>
-    <row r="177" spans="1:8" ht="12.75">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="17" t="s">
+    </row>
+    <row r="177" spans="1:7" ht="12.75">
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D177" s="17">
+      <c r="D177" s="13">
         <v>1</v>
       </c>
-      <c r="E177" s="17">
+      <c r="E177" s="13">
         <v>806</v>
       </c>
-      <c r="F177" s="17">
+      <c r="F177" s="13">
         <f>E177*D177</f>
         <v>806</v>
       </c>
-      <c r="G177" s="17" t="s">
+      <c r="G177" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H177" s="16"/>
-    </row>
-    <row r="178" spans="1:8" ht="12.75">
-      <c r="A178" s="14" t="s">
+    </row>
+    <row r="178" spans="1:7" ht="12.75">
+      <c r="A178" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B178" s="13"/>
-      <c r="C178" s="18" t="s">
+      <c r="B178" s="10"/>
+      <c r="C178" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="4"/>
-      <c r="F178" s="15"/>
+      <c r="F178" s="12"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="16"/>
-    </row>
-    <row r="179" spans="1:8" ht="12.75">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="17" t="s">
+    </row>
+    <row r="179" spans="1:7" ht="12.75">
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D179" s="17"/>
-      <c r="E179" s="17"/>
-      <c r="F179" s="17">
+      <c r="D179" s="13"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="13">
         <f>F177*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G179" s="17" t="s">
+      <c r="G179" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H179" s="16">
-        <f>F179+F169</f>
-        <v>166.53649999999999</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" ht="12.75">
-      <c r="A180" s="17">
+    </row>
+    <row r="180" spans="1:7" ht="12.75">
+      <c r="A180" s="13">
         <v>14.40</v>
       </c>
-      <c r="B180" s="17"/>
-      <c r="C180" s="15" t="s">
+      <c r="B180" s="13"/>
+      <c r="C180" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="4"/>
-      <c r="F180" s="17"/>
-      <c r="G180" s="17"/>
-      <c r="H180" s="16"/>
-    </row>
-    <row r="181" spans="1:8" ht="12.75">
-      <c r="A181" s="17"/>
-      <c r="B181" s="17"/>
-      <c r="C181" s="17" t="s">
+      <c r="F180" s="13"/>
+      <c r="G180" s="13"/>
+    </row>
+    <row r="181" spans="1:7" ht="12.75">
+      <c r="A181" s="13"/>
+      <c r="B181" s="13"/>
+      <c r="C181" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D181" s="17">
+      <c r="D181" s="13">
         <v>13.13</v>
       </c>
-      <c r="E181" s="17">
+      <c r="E181" s="13">
         <v>498.87</v>
       </c>
-      <c r="F181" s="17">
+      <c r="F181" s="13">
         <f>D181*E181</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G181" s="17" t="s">
+      <c r="G181" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H181" s="16"/>
-    </row>
-    <row r="182" spans="1:8" ht="12.75">
-      <c r="A182" s="12" t="s">
+    </row>
+    <row r="182" spans="1:7" ht="12.75">
+      <c r="A182" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="4"/>
-      <c r="D182" s="10">
+      <c r="D182" s="8">
         <v>50</v>
       </c>
-      <c r="E182" s="10" t="s">
+      <c r="E182" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F182" s="10">
+      <c r="F182" s="8">
         <f>F177+F179+F181</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G182" s="10"/>
-      <c r="H182" s="11"/>
-    </row>
-    <row r="183" spans="1:8" ht="12.75">
-      <c r="A183" s="12" t="s">
+      <c r="G182" s="8"/>
+    </row>
+    <row r="183" spans="1:7" ht="12.75">
+      <c r="A183" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="4"/>
-      <c r="D183" s="10">
+      <c r="D183" s="8">
         <v>1</v>
       </c>
-      <c r="E183" s="10" t="s">
+      <c r="E183" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F183" s="10">
+      <c r="F183" s="8">
         <f>F182/D182</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G183" s="10"/>
-      <c r="H183" s="11"/>
-    </row>
-    <row r="184" spans="1:8" ht="12.75">
-      <c r="A184" s="12" t="s">
+      <c r="G183" s="8"/>
+    </row>
+    <row r="184" spans="1:7" ht="12.75">
+      <c r="A184" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="4"/>
-      <c r="E184" s="10">
+      <c r="E184" s="8">
         <f>F183</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F184" s="10">
+      <c r="F184" s="8">
         <f>E184*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G184" s="10"/>
-      <c r="H184" s="11">
-        <f>E184+E174</f>
-        <v>469.65376730000003</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="12.75">
-      <c r="A185" s="20" t="s">
+      <c r="G184" s="8"/>
+    </row>
+    <row r="185" spans="1:7" ht="12.75">
+      <c r="A185" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="4"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="21">
+      <c r="E185" s="8"/>
+      <c r="F185" s="17">
         <f>ROUND(F183+F184,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G185" s="10"/>
-      <c r="H185" s="11">
-        <f>F185+F175</f>
-        <v>540.10</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="12.75">
-      <c r="A186" s="22" t="s">
+      <c r="G185" s="8"/>
+    </row>
+    <row r="186" spans="1:7" ht="12.75">
+      <c r="A186" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B186" s="3"/>
@@ -4050,12 +3789,11 @@
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
       <c r="F186" s="4"/>
-      <c r="G186" s="21" t="s">
+      <c r="G186" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H186" s="23"/>
-    </row>
-    <row r="187" spans="1:8" ht="12.75">
+    </row>
+    <row r="187" spans="1:7" ht="12.75">
       <c r="A187" s="1" t="s">
         <v>0</v>
       </c>
@@ -4071,30 +3809,28 @@
         <v>3</v>
       </c>
       <c r="G187" s="4"/>
-      <c r="H187" s="5"/>
-    </row>
-    <row r="188" spans="1:8" ht="12.75">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="7" t="s">
+    </row>
+    <row r="188" spans="1:7" ht="12.75">
+      <c r="A188" s="5"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="7" t="s">
+      <c r="D188" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="E188" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F188" s="7" t="s">
+      <c r="F188" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G188" s="7" t="s">
+      <c r="G188" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H188" s="5"/>
-    </row>
-    <row r="189" spans="1:8" ht="12.75">
-      <c r="A189" s="8" t="s">
+    </row>
+    <row r="189" spans="1:7" ht="12.75">
+      <c r="A189" s="7" t="s">
         <v>62</v>
       </c>
       <c r="B189" s="3"/>
@@ -4103,31 +3839,29 @@
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="9"/>
-    </row>
-    <row r="190" spans="1:8" ht="12.75">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10" t="s">
+    </row>
+    <row r="190" spans="1:7" ht="12.75">
+      <c r="A190" s="8"/>
+      <c r="B190" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C190" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D190" s="10" t="s">
+      <c r="D190" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E190" s="10">
+      <c r="E190" s="8">
         <v>50</v>
       </c>
-      <c r="F190" s="10"/>
-      <c r="G190" s="10"/>
-      <c r="H190" s="11"/>
-    </row>
-    <row r="191" spans="1:8" ht="12.75">
-      <c r="A191" s="10" t="s">
+      <c r="F190" s="8"/>
+      <c r="G190" s="8"/>
+    </row>
+    <row r="191" spans="1:7" ht="12.75">
+      <c r="A191" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B191" s="12" t="s">
+      <c r="B191" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C191" s="3"/>
@@ -4135,10 +3869,9 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="4"/>
-      <c r="H191" s="11"/>
-    </row>
-    <row r="192" spans="1:8" ht="12.75">
-      <c r="A192" s="12" t="s">
+    </row>
+    <row r="192" spans="1:7" ht="12.75">
+      <c r="A192" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B192" s="3"/>
@@ -4147,427 +3880,393 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="4"/>
-      <c r="H192" s="11"/>
-    </row>
-    <row r="193" spans="1:8" ht="12.75">
-      <c r="A193" s="13"/>
-      <c r="B193" s="14" t="s">
+    </row>
+    <row r="193" spans="1:7" ht="12.75">
+      <c r="A193" s="10"/>
+      <c r="B193" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C193" s="15" t="s">
+      <c r="C193" s="12" t="s">
         <v>64</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="15"/>
+      <c r="F193" s="12"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="16"/>
-    </row>
-    <row r="194" spans="1:8" ht="12.75">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="17" t="s">
+    </row>
+    <row r="194" spans="1:7" ht="12.75">
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D194" s="17">
+      <c r="D194" s="13">
         <v>50</v>
       </c>
-      <c r="E194" s="17">
+      <c r="E194" s="13">
         <v>329.66</v>
       </c>
-      <c r="F194" s="17">
+      <c r="F194" s="13">
         <f>D194*E194</f>
         <v>16483</v>
       </c>
-      <c r="G194" s="17" t="s">
+      <c r="G194" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H194" s="16"/>
-    </row>
-    <row r="195" spans="1:8" ht="12.75">
-      <c r="A195" s="14" t="s">
+    </row>
+    <row r="195" spans="1:7" ht="12.75">
+      <c r="A195" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B195" s="13"/>
-      <c r="C195" s="15" t="s">
+      <c r="B195" s="10"/>
+      <c r="C195" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="15"/>
+      <c r="F195" s="12"/>
       <c r="G195" s="4"/>
-      <c r="H195" s="16"/>
-    </row>
-    <row r="196" spans="1:8" ht="12.75">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="17" t="s">
+    </row>
+    <row r="196" spans="1:7" ht="12.75">
+      <c r="A196" s="5"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D196" s="17"/>
-      <c r="E196" s="17"/>
-      <c r="F196" s="17">
+      <c r="D196" s="13"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="13">
         <f>F194*5%</f>
         <v>824.15</v>
       </c>
-      <c r="G196" s="17" t="s">
+      <c r="G196" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H196" s="16"/>
-    </row>
-    <row r="197" spans="1:8" ht="12.75">
-      <c r="A197" s="13"/>
-      <c r="B197" s="14" t="s">
+    </row>
+    <row r="197" spans="1:7" ht="12.75">
+      <c r="A197" s="10"/>
+      <c r="B197" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C197" s="15" t="s">
+      <c r="C197" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="15"/>
+      <c r="F197" s="12"/>
       <c r="G197" s="4"/>
-      <c r="H197" s="16"/>
-    </row>
-    <row r="198" spans="1:8" ht="12.75">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="17" t="s">
+    </row>
+    <row r="198" spans="1:7" ht="12.75">
+      <c r="A198" s="5"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D198" s="17">
+      <c r="D198" s="13">
         <v>7</v>
       </c>
-      <c r="E198" s="17">
+      <c r="E198" s="13">
         <v>675</v>
       </c>
-      <c r="F198" s="17">
+      <c r="F198" s="13">
         <f>D198*E198</f>
         <v>4725</v>
       </c>
-      <c r="G198" s="17" t="s">
+      <c r="G198" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H198" s="16"/>
-    </row>
-    <row r="199" spans="1:8" ht="12.75">
-      <c r="A199" s="14" t="s">
+    </row>
+    <row r="199" spans="1:7" ht="12.75">
+      <c r="A199" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B199" s="13"/>
-      <c r="C199" s="18" t="s">
+      <c r="B199" s="10"/>
+      <c r="C199" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="15"/>
+      <c r="F199" s="12"/>
       <c r="G199" s="4"/>
-      <c r="H199" s="16"/>
-    </row>
-    <row r="200" spans="1:8" ht="12.75">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="17" t="s">
+    </row>
+    <row r="200" spans="1:7" ht="12.75">
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D200" s="17"/>
-      <c r="E200" s="17"/>
-      <c r="F200" s="17">
+      <c r="D200" s="13"/>
+      <c r="E200" s="13"/>
+      <c r="F200" s="13">
         <f>(F194+F196+F198)*1%</f>
         <v>220.32149999999999</v>
       </c>
-      <c r="G200" s="17" t="s">
+      <c r="G200" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H200" s="16"/>
-    </row>
-    <row r="201" spans="1:8" ht="12.75">
-      <c r="A201" s="12" t="s">
+    </row>
+    <row r="201" spans="1:7" ht="12.75">
+      <c r="A201" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="10">
+      <c r="D201" s="8">
         <v>50</v>
       </c>
-      <c r="E201" s="10" t="s">
+      <c r="E201" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F201" s="10">
+      <c r="F201" s="8">
         <f>F194+F196+F198+F200</f>
         <v>22252.4715</v>
       </c>
-      <c r="G201" s="10"/>
-      <c r="H201" s="11"/>
-    </row>
-    <row r="202" spans="1:8" ht="12.75">
-      <c r="A202" s="12" t="s">
+      <c r="G201" s="8"/>
+    </row>
+    <row r="202" spans="1:7" ht="12.75">
+      <c r="A202" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="10">
+      <c r="D202" s="8">
         <v>1</v>
       </c>
-      <c r="E202" s="10" t="s">
+      <c r="E202" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F202" s="10">
+      <c r="F202" s="8">
         <f>F201/D201</f>
         <v>445.04942999999997</v>
       </c>
-      <c r="G202" s="10"/>
-      <c r="H202" s="11"/>
-    </row>
-    <row r="203" spans="1:8" ht="12.75">
-      <c r="A203" s="12" t="s">
+      <c r="G202" s="8"/>
+    </row>
+    <row r="203" spans="1:7" ht="12.75">
+      <c r="A203" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="4"/>
-      <c r="E203" s="19">
+      <c r="E203" s="15">
         <f>F194*105%*101%/D201</f>
         <v>349.60442999999998</v>
       </c>
-      <c r="F203" s="10">
+      <c r="F203" s="8">
         <f>E203*1%</f>
         <v>3.4960442999999999</v>
       </c>
-      <c r="G203" s="10"/>
-      <c r="H203" s="11"/>
-    </row>
-    <row r="204" spans="1:8" ht="12.75">
-      <c r="A204" s="12" t="s">
+      <c r="G203" s="8"/>
+    </row>
+    <row r="204" spans="1:7" ht="12.75">
+      <c r="A204" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="4"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10">
+      <c r="E204" s="8"/>
+      <c r="F204" s="8">
         <f>F202+F203</f>
         <v>448.54547430000002</v>
       </c>
-      <c r="G204" s="10"/>
-      <c r="H204" s="11"/>
-    </row>
-    <row r="205" spans="1:8" ht="12.75">
-      <c r="A205" s="12" t="s">
+      <c r="G204" s="8"/>
+    </row>
+    <row r="205" spans="1:7" ht="12.75">
+      <c r="A205" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="4"/>
-      <c r="E205" s="10">
+      <c r="E205" s="8">
         <f>F204</f>
         <v>448.54547430000002</v>
       </c>
-      <c r="F205" s="10">
+      <c r="F205" s="8">
         <f>E205*15%</f>
         <v>67.281821149999999</v>
       </c>
-      <c r="G205" s="10"/>
-      <c r="H205" s="11"/>
-    </row>
-    <row r="206" spans="1:8" ht="12.75">
-      <c r="A206" s="20" t="s">
+      <c r="G205" s="8"/>
+    </row>
+    <row r="206" spans="1:7" ht="12.75">
+      <c r="A206" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="4"/>
-      <c r="E206" s="10"/>
-      <c r="F206" s="21">
+      <c r="E206" s="8"/>
+      <c r="F206" s="17">
         <f>ROUND(F204+F205,2)</f>
         <v>515.83</v>
       </c>
-      <c r="G206" s="10"/>
-      <c r="H206" s="11"/>
-    </row>
-    <row r="207" spans="1:8" ht="12.75">
-      <c r="A207" s="14">
+      <c r="G206" s="8"/>
+    </row>
+    <row r="207" spans="1:7" ht="12.75">
+      <c r="A207" s="11">
         <v>1001</v>
       </c>
-      <c r="B207" s="13"/>
-      <c r="C207" s="15" t="s">
+      <c r="B207" s="10"/>
+      <c r="C207" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="15"/>
+      <c r="F207" s="12"/>
       <c r="G207" s="4"/>
-      <c r="H207" s="16"/>
-    </row>
-    <row r="208" spans="1:8" ht="12.75">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="17" t="s">
+    </row>
+    <row r="208" spans="1:7" ht="12.75">
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D208" s="17">
+      <c r="D208" s="13">
         <v>1</v>
       </c>
-      <c r="E208" s="17">
+      <c r="E208" s="13">
         <v>806</v>
       </c>
-      <c r="F208" s="17">
+      <c r="F208" s="13">
         <f>E208*D208</f>
         <v>806</v>
       </c>
-      <c r="G208" s="17" t="s">
+      <c r="G208" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H208" s="16"/>
-    </row>
-    <row r="209" spans="1:8" ht="12.75">
-      <c r="A209" s="14" t="s">
+    </row>
+    <row r="209" spans="1:7" ht="12.75">
+      <c r="A209" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B209" s="13"/>
-      <c r="C209" s="18" t="s">
+      <c r="B209" s="10"/>
+      <c r="C209" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D209" s="3"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="15"/>
+      <c r="F209" s="12"/>
       <c r="G209" s="4"/>
-      <c r="H209" s="16"/>
-    </row>
-    <row r="210" spans="1:8" ht="12.75">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="17" t="s">
+    </row>
+    <row r="210" spans="1:7" ht="12.75">
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D210" s="17"/>
-      <c r="E210" s="17"/>
-      <c r="F210" s="17">
+      <c r="D210" s="13"/>
+      <c r="E210" s="13"/>
+      <c r="F210" s="13">
         <f>F208*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G210" s="17" t="s">
+      <c r="G210" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H210" s="16">
-        <f>F210+F200</f>
-        <v>228.38149999999999</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="12.75">
-      <c r="A211" s="17">
+    </row>
+    <row r="211" spans="1:7" ht="12.75">
+      <c r="A211" s="13">
         <v>14.40</v>
       </c>
-      <c r="B211" s="17"/>
-      <c r="C211" s="15" t="s">
+      <c r="B211" s="13"/>
+      <c r="C211" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="17"/>
-      <c r="G211" s="17"/>
-      <c r="H211" s="16"/>
-    </row>
-    <row r="212" spans="1:8" ht="12.75">
-      <c r="A212" s="17"/>
-      <c r="B212" s="17"/>
-      <c r="C212" s="17" t="s">
+      <c r="F211" s="13"/>
+      <c r="G211" s="13"/>
+    </row>
+    <row r="212" spans="1:7" ht="12.75">
+      <c r="A212" s="13"/>
+      <c r="B212" s="13"/>
+      <c r="C212" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D212" s="17">
+      <c r="D212" s="13">
         <v>13.13</v>
       </c>
-      <c r="E212" s="17">
+      <c r="E212" s="13">
         <v>498.87</v>
       </c>
-      <c r="F212" s="17">
+      <c r="F212" s="13">
         <f>D212*E212</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G212" s="17" t="s">
+      <c r="G212" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H212" s="16"/>
-    </row>
-    <row r="213" spans="1:8" ht="12.75">
-      <c r="A213" s="12" t="s">
+    </row>
+    <row r="213" spans="1:7" ht="12.75">
+      <c r="A213" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="10">
+      <c r="D213" s="8">
         <v>50</v>
       </c>
-      <c r="E213" s="10" t="s">
+      <c r="E213" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F213" s="10">
+      <c r="F213" s="8">
         <f>F208+F210+F212</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G213" s="10"/>
-      <c r="H213" s="11"/>
-    </row>
-    <row r="214" spans="1:8" ht="12.75">
-      <c r="A214" s="12" t="s">
+      <c r="G213" s="8"/>
+    </row>
+    <row r="214" spans="1:7" ht="12.75">
+      <c r="A214" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="4"/>
-      <c r="D214" s="10">
+      <c r="D214" s="8">
         <v>1</v>
       </c>
-      <c r="E214" s="10" t="s">
+      <c r="E214" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F214" s="10">
+      <c r="F214" s="8">
         <f>F213/D213</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G214" s="10"/>
-      <c r="H214" s="11"/>
-    </row>
-    <row r="215" spans="1:8" ht="12.75">
-      <c r="A215" s="12" t="s">
+      <c r="G214" s="8"/>
+    </row>
+    <row r="215" spans="1:7" ht="12.75">
+      <c r="A215" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="4"/>
-      <c r="E215" s="10">
+      <c r="E215" s="8">
         <f>F214</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F215" s="10">
+      <c r="F215" s="8">
         <f>E215*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G215" s="10"/>
-      <c r="H215" s="11">
-        <f>E215+E205</f>
-        <v>595.82993629999999</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="12.75">
-      <c r="A216" s="20" t="s">
+      <c r="G215" s="8"/>
+    </row>
+    <row r="216" spans="1:7" ht="12.75">
+      <c r="A216" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="4"/>
-      <c r="E216" s="10"/>
-      <c r="F216" s="21">
+      <c r="E216" s="8"/>
+      <c r="F216" s="17">
         <f>ROUND(F214+F215,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G216" s="10"/>
-      <c r="H216" s="11">
-        <f>F216+F206</f>
-        <v>685.21</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="12.75">
-      <c r="A217" s="22" t="s">
+      <c r="G216" s="8"/>
+    </row>
+    <row r="217" spans="1:7" ht="12.75">
+      <c r="A217" s="18" t="s">
         <v>65</v>
       </c>
       <c r="B217" s="3"/>
@@ -4575,12 +4274,11 @@
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
       <c r="F217" s="4"/>
-      <c r="G217" s="21" t="s">
+      <c r="G217" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H217" s="23"/>
-    </row>
-    <row r="218" spans="1:8" ht="12.75">
+    </row>
+    <row r="218" spans="1:7" ht="12.75">
       <c r="A218" s="1" t="s">
         <v>0</v>
       </c>
@@ -4596,30 +4294,28 @@
         <v>3</v>
       </c>
       <c r="G218" s="4"/>
-      <c r="H218" s="5"/>
-    </row>
-    <row r="219" spans="1:8" ht="12.75">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="7" t="s">
+    </row>
+    <row r="219" spans="1:7" ht="12.75">
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
+      <c r="C219" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="7" t="s">
+      <c r="D219" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E219" s="7" t="s">
+      <c r="E219" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F219" s="7" t="s">
+      <c r="F219" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G219" s="7" t="s">
+      <c r="G219" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H219" s="5"/>
-    </row>
-    <row r="220" spans="1:8" ht="12.75">
-      <c r="A220" s="8" t="s">
+    </row>
+    <row r="220" spans="1:7" ht="12.75">
+      <c r="A220" s="7" t="s">
         <v>66</v>
       </c>
       <c r="B220" s="3"/>
@@ -4628,31 +4324,29 @@
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="4"/>
-      <c r="H220" s="9"/>
-    </row>
-    <row r="221" spans="1:8" ht="12.75">
-      <c r="A221" s="10"/>
-      <c r="B221" s="10" t="s">
+    </row>
+    <row r="221" spans="1:7" ht="12.75">
+      <c r="A221" s="8"/>
+      <c r="B221" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="C221" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E221" s="10">
+      <c r="E221" s="8">
         <v>50</v>
       </c>
-      <c r="F221" s="10"/>
-      <c r="G221" s="10"/>
-      <c r="H221" s="11"/>
-    </row>
-    <row r="222" spans="1:8" ht="12.75">
-      <c r="A222" s="10" t="s">
+      <c r="F221" s="8"/>
+      <c r="G221" s="8"/>
+    </row>
+    <row r="222" spans="1:7" ht="12.75">
+      <c r="A222" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B222" s="12" t="s">
+      <c r="B222" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C222" s="3"/>
@@ -4660,10 +4354,9 @@
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="4"/>
-      <c r="H222" s="11"/>
-    </row>
-    <row r="223" spans="1:8" ht="12.75">
-      <c r="A223" s="12" t="s">
+    </row>
+    <row r="223" spans="1:7" ht="12.75">
+      <c r="A223" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B223" s="3"/>
@@ -4672,440 +4365,405 @@
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="4"/>
-      <c r="H223" s="11"/>
-    </row>
-    <row r="224" spans="1:8" ht="12.75">
-      <c r="A224" s="13"/>
-      <c r="B224" s="14" t="s">
+    </row>
+    <row r="224" spans="1:7" ht="12.75">
+      <c r="A224" s="10"/>
+      <c r="B224" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C224" s="15" t="s">
+      <c r="C224" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="15"/>
+      <c r="F224" s="12"/>
       <c r="G224" s="4"/>
-      <c r="H224" s="16"/>
-    </row>
-    <row r="225" spans="1:8" ht="12.75">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="17" t="s">
+    </row>
+    <row r="225" spans="1:7" ht="12.75">
+      <c r="A225" s="5"/>
+      <c r="B225" s="5"/>
+      <c r="C225" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D225" s="17">
+      <c r="D225" s="13">
         <v>50</v>
       </c>
-      <c r="E225" s="17">
+      <c r="E225" s="13">
         <v>466.95</v>
       </c>
-      <c r="F225" s="17">
+      <c r="F225" s="13">
         <f>D225*E225</f>
         <v>23347.50</v>
       </c>
-      <c r="G225" s="17" t="s">
+      <c r="G225" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H225" s="16"/>
-    </row>
-    <row r="226" spans="1:8" ht="12.75">
-      <c r="A226" s="14" t="s">
+    </row>
+    <row r="226" spans="1:7" ht="12.75">
+      <c r="A226" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B226" s="13"/>
-      <c r="C226" s="15" t="s">
+      <c r="B226" s="10"/>
+      <c r="C226" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="15"/>
+      <c r="F226" s="12"/>
       <c r="G226" s="4"/>
-      <c r="H226" s="16"/>
-    </row>
-    <row r="227" spans="1:8" ht="12.75">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="17" t="s">
+    </row>
+    <row r="227" spans="1:7" ht="12.75">
+      <c r="A227" s="5"/>
+      <c r="B227" s="5"/>
+      <c r="C227" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D227" s="17"/>
-      <c r="E227" s="17"/>
-      <c r="F227" s="17">
+      <c r="D227" s="13"/>
+      <c r="E227" s="13"/>
+      <c r="F227" s="13">
         <f>F225*5%</f>
         <v>1167.375</v>
       </c>
-      <c r="G227" s="17" t="s">
+      <c r="G227" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H227" s="16"/>
-    </row>
-    <row r="228" spans="1:8" ht="12.75">
-      <c r="A228" s="13"/>
-      <c r="B228" s="14" t="s">
+    </row>
+    <row r="228" spans="1:7" ht="12.75">
+      <c r="A228" s="10"/>
+      <c r="B228" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C228" s="15" t="s">
+      <c r="C228" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="15"/>
+      <c r="F228" s="12"/>
       <c r="G228" s="4"/>
-      <c r="H228" s="16"/>
-    </row>
-    <row r="229" spans="1:8" ht="12.75">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="17" t="s">
+    </row>
+    <row r="229" spans="1:7" ht="12.75">
+      <c r="A229" s="5"/>
+      <c r="B229" s="5"/>
+      <c r="C229" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D229" s="17">
+      <c r="D229" s="13">
         <v>7</v>
       </c>
-      <c r="E229" s="17">
+      <c r="E229" s="13">
         <v>675</v>
       </c>
-      <c r="F229" s="17">
+      <c r="F229" s="13">
         <f>D229*E229</f>
         <v>4725</v>
       </c>
-      <c r="G229" s="17" t="s">
+      <c r="G229" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H229" s="16"/>
-    </row>
-    <row r="230" spans="1:8" ht="12.75">
-      <c r="A230" s="14" t="s">
+    </row>
+    <row r="230" spans="1:7" ht="12.75">
+      <c r="A230" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B230" s="13"/>
-      <c r="C230" s="18" t="s">
+      <c r="B230" s="10"/>
+      <c r="C230" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="15"/>
+      <c r="F230" s="12"/>
       <c r="G230" s="4"/>
-      <c r="H230" s="16"/>
-    </row>
-    <row r="231" spans="1:8" ht="12.75">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="17" t="s">
+    </row>
+    <row r="231" spans="1:7" ht="12.75">
+      <c r="A231" s="5"/>
+      <c r="B231" s="5"/>
+      <c r="C231" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D231" s="17"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="17">
+      <c r="D231" s="13"/>
+      <c r="E231" s="13"/>
+      <c r="F231" s="13">
         <f>(F225+F227+F229)*1%</f>
         <v>292.39875</v>
       </c>
-      <c r="G231" s="17" t="s">
+      <c r="G231" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H231" s="16"/>
-    </row>
-    <row r="232" spans="1:8" ht="12.75">
-      <c r="A232" s="12" t="s">
+    </row>
+    <row r="232" spans="1:7" ht="12.75">
+      <c r="A232" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B232" s="3"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="10">
+      <c r="D232" s="8">
         <v>50</v>
       </c>
-      <c r="E232" s="10" t="s">
+      <c r="E232" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F232" s="10">
+      <c r="F232" s="8">
         <f>F225+F227+F229+F231</f>
         <v>29532.27375</v>
       </c>
-      <c r="G232" s="10"/>
-      <c r="H232" s="11"/>
-    </row>
-    <row r="233" spans="1:8" ht="12.75">
-      <c r="A233" s="12" t="s">
+      <c r="G232" s="8"/>
+    </row>
+    <row r="233" spans="1:7" ht="12.75">
+      <c r="A233" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B233" s="3"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="10">
+      <c r="D233" s="8">
         <v>1</v>
       </c>
-      <c r="E233" s="10" t="s">
+      <c r="E233" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F233" s="10">
+      <c r="F233" s="8">
         <f>F232/D232</f>
         <v>590.64547500000003</v>
       </c>
-      <c r="G233" s="10"/>
-      <c r="H233" s="11"/>
-    </row>
-    <row r="234" spans="1:8" ht="12.75">
-      <c r="A234" s="12" t="s">
+      <c r="G233" s="8"/>
+    </row>
+    <row r="234" spans="1:7" ht="12.75">
+      <c r="A234" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="4"/>
-      <c r="E234" s="19">
+      <c r="E234" s="15">
         <f>F225*105%*101%/D232</f>
         <v>495.20047499999998</v>
       </c>
-      <c r="F234" s="10">
+      <c r="F234" s="8">
         <f>E234*1%</f>
         <v>4.9520047500000004</v>
       </c>
-      <c r="G234" s="10"/>
-      <c r="H234" s="11"/>
-    </row>
-    <row r="235" spans="1:8" ht="12.75">
-      <c r="A235" s="12" t="s">
+      <c r="G234" s="8"/>
+    </row>
+    <row r="235" spans="1:7" ht="12.75">
+      <c r="A235" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="4"/>
-      <c r="E235" s="10"/>
-      <c r="F235" s="10">
+      <c r="E235" s="8"/>
+      <c r="F235" s="8">
         <f>F233+F234</f>
         <v>595.59747979999997</v>
       </c>
-      <c r="G235" s="10"/>
-      <c r="H235" s="11"/>
-    </row>
-    <row r="236" spans="1:8" ht="12.75">
-      <c r="A236" s="12" t="s">
+      <c r="G235" s="8"/>
+    </row>
+    <row r="236" spans="1:7" ht="12.75">
+      <c r="A236" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="4"/>
-      <c r="E236" s="10">
+      <c r="E236" s="8">
         <f>F235</f>
         <v>595.59747979999997</v>
       </c>
-      <c r="F236" s="10">
+      <c r="F236" s="8">
         <f>E236*15%</f>
         <v>89.339621960000002</v>
       </c>
-      <c r="G236" s="10"/>
-      <c r="H236" s="11"/>
-    </row>
-    <row r="237" spans="1:8" ht="12.75">
-      <c r="A237" s="20" t="s">
+      <c r="G236" s="8"/>
+    </row>
+    <row r="237" spans="1:7" ht="12.75">
+      <c r="A237" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="4"/>
-      <c r="E237" s="10"/>
-      <c r="F237" s="21">
+      <c r="E237" s="8"/>
+      <c r="F237" s="17">
         <f>ROUND(F235+F236,2)</f>
         <v>684.94</v>
       </c>
-      <c r="G237" s="10"/>
-      <c r="H237" s="11"/>
-    </row>
-    <row r="238" spans="1:8" ht="12.75">
-      <c r="A238" s="14">
+      <c r="G237" s="8"/>
+    </row>
+    <row r="238" spans="1:7" ht="12.75">
+      <c r="A238" s="11">
         <v>1001</v>
       </c>
-      <c r="B238" s="13"/>
-      <c r="C238" s="15" t="s">
+      <c r="B238" s="10"/>
+      <c r="C238" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="15"/>
+      <c r="F238" s="12"/>
       <c r="G238" s="4"/>
-      <c r="H238" s="16"/>
-    </row>
-    <row r="239" spans="1:8" ht="12.75">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="17" t="s">
+    </row>
+    <row r="239" spans="1:7" ht="12.75">
+      <c r="A239" s="5"/>
+      <c r="B239" s="5"/>
+      <c r="C239" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D239" s="17">
+      <c r="D239" s="13">
         <v>1</v>
       </c>
-      <c r="E239" s="17">
+      <c r="E239" s="13">
         <v>806</v>
       </c>
-      <c r="F239" s="17">
+      <c r="F239" s="13">
         <f>E239*D239</f>
         <v>806</v>
       </c>
-      <c r="G239" s="17" t="s">
+      <c r="G239" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H239" s="16"/>
-    </row>
-    <row r="240" spans="1:8" ht="12.75">
-      <c r="A240" s="14" t="s">
+    </row>
+    <row r="240" spans="1:7" ht="12.75">
+      <c r="A240" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B240" s="13"/>
-      <c r="C240" s="18" t="s">
+      <c r="B240" s="10"/>
+      <c r="C240" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="15"/>
+      <c r="F240" s="12"/>
       <c r="G240" s="4"/>
-      <c r="H240" s="16"/>
-    </row>
-    <row r="241" spans="1:8" ht="12.75">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="17" t="s">
+    </row>
+    <row r="241" spans="1:7" ht="12.75">
+      <c r="A241" s="5"/>
+      <c r="B241" s="5"/>
+      <c r="C241" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D241" s="17"/>
-      <c r="E241" s="17"/>
-      <c r="F241" s="17">
+      <c r="D241" s="13"/>
+      <c r="E241" s="13"/>
+      <c r="F241" s="13">
         <f>F239*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G241" s="17" t="s">
+      <c r="G241" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H241" s="16">
-        <f>F241+F231</f>
-        <v>300.45875</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" ht="12.75">
-      <c r="A242" s="17">
+    </row>
+    <row r="242" spans="1:7" ht="12.75">
+      <c r="A242" s="13">
         <v>14.40</v>
       </c>
-      <c r="B242" s="17"/>
-      <c r="C242" s="15" t="s">
+      <c r="B242" s="13"/>
+      <c r="C242" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="17"/>
-      <c r="G242" s="17"/>
-      <c r="H242" s="16"/>
-    </row>
-    <row r="243" spans="1:8" ht="12.75">
-      <c r="A243" s="17"/>
-      <c r="B243" s="17"/>
-      <c r="C243" s="17" t="s">
+      <c r="F242" s="13"/>
+      <c r="G242" s="13"/>
+    </row>
+    <row r="243" spans="1:7" ht="12.75">
+      <c r="A243" s="13"/>
+      <c r="B243" s="13"/>
+      <c r="C243" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D243" s="17">
+      <c r="D243" s="13">
         <v>13.13</v>
       </c>
-      <c r="E243" s="17">
+      <c r="E243" s="13">
         <v>498.87</v>
       </c>
-      <c r="F243" s="17">
+      <c r="F243" s="13">
         <f>D243*E243</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G243" s="17" t="s">
+      <c r="G243" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H243" s="16"/>
-    </row>
-    <row r="244" spans="1:8" ht="12.75">
-      <c r="A244" s="12" t="s">
+    </row>
+    <row r="244" spans="1:7" ht="12.75">
+      <c r="A244" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="4"/>
-      <c r="D244" s="10">
+      <c r="D244" s="8">
         <v>50</v>
       </c>
-      <c r="E244" s="10" t="s">
+      <c r="E244" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F244" s="10">
+      <c r="F244" s="8">
         <f>F239+F241+F243</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G244" s="10"/>
-      <c r="H244" s="11"/>
-    </row>
-    <row r="245" spans="1:8" ht="12.75">
-      <c r="A245" s="12" t="s">
+      <c r="G244" s="8"/>
+    </row>
+    <row r="245" spans="1:7" ht="12.75">
+      <c r="A245" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="4"/>
-      <c r="D245" s="10">
+      <c r="D245" s="8">
         <v>1</v>
       </c>
-      <c r="E245" s="10" t="s">
+      <c r="E245" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F245" s="10">
+      <c r="F245" s="8">
         <f>F244/D244</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G245" s="10"/>
-      <c r="H245" s="11"/>
-    </row>
-    <row r="246" spans="1:8" ht="12.75">
-      <c r="A246" s="12" t="s">
+      <c r="G245" s="8"/>
+    </row>
+    <row r="246" spans="1:7" ht="12.75">
+      <c r="A246" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
       <c r="D246" s="4"/>
-      <c r="E246" s="10">
+      <c r="E246" s="8">
         <f>F245</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F246" s="10">
+      <c r="F246" s="8">
         <f>E246*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G246" s="10"/>
-      <c r="H246" s="11">
-        <f>E246+E236</f>
-        <v>742.88194180000005</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="12.75">
-      <c r="A247" s="20" t="s">
+      <c r="G246" s="8"/>
+    </row>
+    <row r="247" spans="1:7" ht="12.75">
+      <c r="A247" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
       <c r="D247" s="4"/>
-      <c r="E247" s="10"/>
-      <c r="F247" s="21">
+      <c r="E247" s="8"/>
+      <c r="F247" s="17">
         <f>ROUND(F245+F246,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G247" s="10"/>
-      <c r="H247" s="11">
-        <f>F247+F237</f>
-        <v>854.32</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" ht="12.75">
-      <c r="A248" s="24" t="s">
+      <c r="G247" s="8"/>
+    </row>
+    <row r="248" spans="1:7" ht="12.75">
+      <c r="A248" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B248" s="25"/>
-      <c r="C248" s="25"/>
-      <c r="D248" s="25"/>
-      <c r="E248" s="25"/>
-      <c r="F248" s="26"/>
-      <c r="G248" s="27" t="s">
+      <c r="B248" s="20"/>
+      <c r="C248" s="20"/>
+      <c r="D248" s="20"/>
+      <c r="E248" s="20"/>
+      <c r="F248" s="21"/>
+      <c r="G248" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H248" s="23"/>
-    </row>
-    <row r="249" spans="1:8" ht="12.75">
+    </row>
+    <row r="249" spans="1:7" ht="12.75">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -5121,30 +4779,28 @@
         <v>3</v>
       </c>
       <c r="G249" s="4"/>
-      <c r="H249" s="5"/>
-    </row>
-    <row r="250" spans="1:8" ht="12.75">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="7" t="s">
+    </row>
+    <row r="250" spans="1:7" ht="12.75">
+      <c r="A250" s="5"/>
+      <c r="B250" s="5"/>
+      <c r="C250" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="7" t="s">
+      <c r="D250" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E250" s="7" t="s">
+      <c r="E250" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F250" s="7" t="s">
+      <c r="F250" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G250" s="7" t="s">
+      <c r="G250" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H250" s="5"/>
-    </row>
-    <row r="251" spans="1:8" ht="12.75">
-      <c r="A251" s="8" t="s">
+    </row>
+    <row r="251" spans="1:7" ht="12.75">
+      <c r="A251" s="7" t="s">
         <v>70</v>
       </c>
       <c r="B251" s="3"/>
@@ -5153,31 +4809,29 @@
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="4"/>
-      <c r="H251" s="9"/>
-    </row>
-    <row r="252" spans="1:8" ht="12.75">
-      <c r="A252" s="10"/>
-      <c r="B252" s="10" t="s">
+    </row>
+    <row r="252" spans="1:7" ht="12.75">
+      <c r="A252" s="8"/>
+      <c r="B252" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C252" s="10" t="s">
+      <c r="C252" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E252" s="10">
+      <c r="E252" s="8">
         <v>50</v>
       </c>
-      <c r="F252" s="10"/>
-      <c r="G252" s="10"/>
-      <c r="H252" s="11"/>
-    </row>
-    <row r="253" spans="1:8" ht="12.75">
-      <c r="A253" s="10" t="s">
+      <c r="F252" s="8"/>
+      <c r="G252" s="8"/>
+    </row>
+    <row r="253" spans="1:7" ht="12.75">
+      <c r="A253" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B253" s="12" t="s">
+      <c r="B253" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C253" s="3"/>
@@ -5185,10 +4839,9 @@
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="G253" s="4"/>
-      <c r="H253" s="11"/>
-    </row>
-    <row r="254" spans="1:8" ht="12.75">
-      <c r="A254" s="12" t="s">
+    </row>
+    <row r="254" spans="1:7" ht="12.75">
+      <c r="A254" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B254" s="3"/>
@@ -5197,427 +4850,393 @@
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="G254" s="4"/>
-      <c r="H254" s="11"/>
-    </row>
-    <row r="255" spans="1:8" ht="12.75">
-      <c r="A255" s="13"/>
-      <c r="B255" s="14" t="s">
+    </row>
+    <row r="255" spans="1:7" ht="12.75">
+      <c r="A255" s="10"/>
+      <c r="B255" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C255" s="15" t="s">
+      <c r="C255" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="4"/>
-      <c r="F255" s="15"/>
+      <c r="F255" s="12"/>
       <c r="G255" s="4"/>
-      <c r="H255" s="16"/>
-    </row>
-    <row r="256" spans="1:8" ht="12.75">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="17" t="s">
+    </row>
+    <row r="256" spans="1:7" ht="12.75">
+      <c r="A256" s="5"/>
+      <c r="B256" s="5"/>
+      <c r="C256" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D256" s="17">
+      <c r="D256" s="13">
         <v>50</v>
       </c>
-      <c r="E256" s="17">
+      <c r="E256" s="13">
         <v>425.42</v>
       </c>
-      <c r="F256" s="17">
+      <c r="F256" s="13">
         <f>D256*E256</f>
         <v>21271</v>
       </c>
-      <c r="G256" s="17" t="s">
+      <c r="G256" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H256" s="16"/>
-    </row>
-    <row r="257" spans="1:8" ht="12.75">
-      <c r="A257" s="14" t="s">
+    </row>
+    <row r="257" spans="1:7" ht="12.75">
+      <c r="A257" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B257" s="13"/>
-      <c r="C257" s="15" t="s">
+      <c r="B257" s="10"/>
+      <c r="C257" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="4"/>
-      <c r="F257" s="15"/>
+      <c r="F257" s="12"/>
       <c r="G257" s="4"/>
-      <c r="H257" s="16"/>
-    </row>
-    <row r="258" spans="1:8" ht="12.75">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="17" t="s">
+    </row>
+    <row r="258" spans="1:7" ht="12.75">
+      <c r="A258" s="5"/>
+      <c r="B258" s="5"/>
+      <c r="C258" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D258" s="17"/>
-      <c r="E258" s="17"/>
-      <c r="F258" s="17">
+      <c r="D258" s="13"/>
+      <c r="E258" s="13"/>
+      <c r="F258" s="13">
         <f>F256*5%</f>
         <v>1063.55</v>
       </c>
-      <c r="G258" s="17" t="s">
+      <c r="G258" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H258" s="16"/>
-    </row>
-    <row r="259" spans="1:8" ht="12.75">
-      <c r="A259" s="13"/>
-      <c r="B259" s="14" t="s">
+    </row>
+    <row r="259" spans="1:7" ht="12.75">
+      <c r="A259" s="10"/>
+      <c r="B259" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C259" s="15" t="s">
+      <c r="C259" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="15"/>
+      <c r="F259" s="12"/>
       <c r="G259" s="4"/>
-      <c r="H259" s="16"/>
-    </row>
-    <row r="260" spans="1:8" ht="12.75">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
-      <c r="C260" s="17" t="s">
+    </row>
+    <row r="260" spans="1:7" ht="12.75">
+      <c r="A260" s="5"/>
+      <c r="B260" s="5"/>
+      <c r="C260" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D260" s="17">
+      <c r="D260" s="13">
         <v>7</v>
       </c>
-      <c r="E260" s="17">
+      <c r="E260" s="13">
         <v>675</v>
       </c>
-      <c r="F260" s="17">
+      <c r="F260" s="13">
         <f>D260*E260</f>
         <v>4725</v>
       </c>
-      <c r="G260" s="17" t="s">
+      <c r="G260" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H260" s="16"/>
-    </row>
-    <row r="261" spans="1:8" ht="12.75">
-      <c r="A261" s="14" t="s">
+    </row>
+    <row r="261" spans="1:7" ht="12.75">
+      <c r="A261" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B261" s="13"/>
-      <c r="C261" s="18" t="s">
+      <c r="B261" s="10"/>
+      <c r="C261" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="15"/>
+      <c r="F261" s="12"/>
       <c r="G261" s="4"/>
-      <c r="H261" s="16"/>
-    </row>
-    <row r="262" spans="1:8" ht="12.75">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
-      <c r="C262" s="17" t="s">
+    </row>
+    <row r="262" spans="1:7" ht="12.75">
+      <c r="A262" s="5"/>
+      <c r="B262" s="5"/>
+      <c r="C262" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D262" s="17"/>
-      <c r="E262" s="17"/>
-      <c r="F262" s="17">
+      <c r="D262" s="13"/>
+      <c r="E262" s="13"/>
+      <c r="F262" s="13">
         <f>(F256+F258+F260)*1%</f>
         <v>270.59550000000002</v>
       </c>
-      <c r="G262" s="17" t="s">
+      <c r="G262" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H262" s="16"/>
-    </row>
-    <row r="263" spans="1:8" ht="12.75">
-      <c r="A263" s="12" t="s">
+    </row>
+    <row r="263" spans="1:7" ht="12.75">
+      <c r="A263" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B263" s="3"/>
       <c r="C263" s="4"/>
-      <c r="D263" s="10">
+      <c r="D263" s="8">
         <v>50</v>
       </c>
-      <c r="E263" s="10" t="s">
+      <c r="E263" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F263" s="10">
+      <c r="F263" s="8">
         <f>F256+F258+F260+F262</f>
         <v>27330.145499999999</v>
       </c>
-      <c r="G263" s="10"/>
-      <c r="H263" s="11"/>
-    </row>
-    <row r="264" spans="1:8" ht="12.75">
-      <c r="A264" s="12" t="s">
+      <c r="G263" s="8"/>
+    </row>
+    <row r="264" spans="1:7" ht="12.75">
+      <c r="A264" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B264" s="3"/>
       <c r="C264" s="4"/>
-      <c r="D264" s="10">
+      <c r="D264" s="8">
         <v>1</v>
       </c>
-      <c r="E264" s="10" t="s">
+      <c r="E264" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F264" s="10">
+      <c r="F264" s="8">
         <f>F263/D263</f>
         <v>546.60290999999995</v>
       </c>
-      <c r="G264" s="10"/>
-      <c r="H264" s="11"/>
-    </row>
-    <row r="265" spans="1:8" ht="12.75">
-      <c r="A265" s="12" t="s">
+      <c r="G264" s="8"/>
+    </row>
+    <row r="265" spans="1:7" ht="12.75">
+      <c r="A265" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
       <c r="D265" s="4"/>
-      <c r="E265" s="19">
+      <c r="E265" s="15">
         <f>F256*105%*101%/D263</f>
         <v>451.15791000000002</v>
       </c>
-      <c r="F265" s="10">
+      <c r="F265" s="8">
         <f>E265*1%</f>
         <v>4.5115790999999996</v>
       </c>
-      <c r="G265" s="10"/>
-      <c r="H265" s="11"/>
-    </row>
-    <row r="266" spans="1:8" ht="12.75">
-      <c r="A266" s="12" t="s">
+      <c r="G265" s="8"/>
+    </row>
+    <row r="266" spans="1:7" ht="12.75">
+      <c r="A266" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
       <c r="D266" s="4"/>
-      <c r="E266" s="10"/>
-      <c r="F266" s="10">
+      <c r="E266" s="8"/>
+      <c r="F266" s="8">
         <f>F264+F265</f>
         <v>551.11448910000001</v>
       </c>
-      <c r="G266" s="10"/>
-      <c r="H266" s="11"/>
-    </row>
-    <row r="267" spans="1:8" ht="12.75">
-      <c r="A267" s="12" t="s">
+      <c r="G266" s="8"/>
+    </row>
+    <row r="267" spans="1:7" ht="12.75">
+      <c r="A267" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
       <c r="D267" s="4"/>
-      <c r="E267" s="10">
+      <c r="E267" s="8">
         <f>F266</f>
         <v>551.11448910000001</v>
       </c>
-      <c r="F267" s="10">
+      <c r="F267" s="8">
         <f>E267*15%</f>
         <v>82.66717337</v>
       </c>
-      <c r="G267" s="10"/>
-      <c r="H267" s="11"/>
-    </row>
-    <row r="268" spans="1:8" ht="12.75">
-      <c r="A268" s="20" t="s">
+      <c r="G267" s="8"/>
+    </row>
+    <row r="268" spans="1:7" ht="12.75">
+      <c r="A268" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
       <c r="D268" s="4"/>
-      <c r="E268" s="10"/>
-      <c r="F268" s="21">
+      <c r="E268" s="8"/>
+      <c r="F268" s="17">
         <f>ROUND(F266+F267,2)</f>
         <v>633.78</v>
       </c>
-      <c r="G268" s="10"/>
-      <c r="H268" s="11"/>
-    </row>
-    <row r="269" spans="1:8" ht="12.75">
-      <c r="A269" s="14">
+      <c r="G268" s="8"/>
+    </row>
+    <row r="269" spans="1:7" ht="12.75">
+      <c r="A269" s="11">
         <v>1001</v>
       </c>
-      <c r="B269" s="13"/>
-      <c r="C269" s="15" t="s">
+      <c r="B269" s="10"/>
+      <c r="C269" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="15"/>
+      <c r="F269" s="12"/>
       <c r="G269" s="4"/>
-      <c r="H269" s="16"/>
-    </row>
-    <row r="270" spans="1:8" ht="12.75">
-      <c r="A270" s="6"/>
-      <c r="B270" s="6"/>
-      <c r="C270" s="17" t="s">
+    </row>
+    <row r="270" spans="1:7" ht="12.75">
+      <c r="A270" s="5"/>
+      <c r="B270" s="5"/>
+      <c r="C270" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D270" s="17">
+      <c r="D270" s="13">
         <v>1</v>
       </c>
-      <c r="E270" s="17">
+      <c r="E270" s="13">
         <v>806</v>
       </c>
-      <c r="F270" s="17">
+      <c r="F270" s="13">
         <f>E270*D270</f>
         <v>806</v>
       </c>
-      <c r="G270" s="17" t="s">
+      <c r="G270" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H270" s="16"/>
-    </row>
-    <row r="271" spans="1:8" ht="12.75">
-      <c r="A271" s="14" t="s">
+    </row>
+    <row r="271" spans="1:7" ht="12.75">
+      <c r="A271" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B271" s="13"/>
-      <c r="C271" s="18" t="s">
+      <c r="B271" s="10"/>
+      <c r="C271" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D271" s="3"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="15"/>
+      <c r="F271" s="12"/>
       <c r="G271" s="4"/>
-      <c r="H271" s="16"/>
-    </row>
-    <row r="272" spans="1:8" ht="12.75">
-      <c r="A272" s="6"/>
-      <c r="B272" s="6"/>
-      <c r="C272" s="17" t="s">
+    </row>
+    <row r="272" spans="1:7" ht="12.75">
+      <c r="A272" s="5"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D272" s="17"/>
-      <c r="E272" s="17"/>
-      <c r="F272" s="17">
+      <c r="D272" s="13"/>
+      <c r="E272" s="13"/>
+      <c r="F272" s="13">
         <f>F270*1%</f>
         <v>8.06</v>
       </c>
-      <c r="G272" s="17" t="s">
+      <c r="G272" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H272" s="16">
-        <f>F272+F262</f>
-        <v>278.65550000000002</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" ht="12.75">
-      <c r="A273" s="17">
+    </row>
+    <row r="273" spans="1:7" ht="12.75">
+      <c r="A273" s="13">
         <v>14.40</v>
       </c>
-      <c r="B273" s="17"/>
-      <c r="C273" s="15" t="s">
+      <c r="B273" s="13"/>
+      <c r="C273" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="17"/>
-      <c r="G273" s="17"/>
-      <c r="H273" s="16"/>
-    </row>
-    <row r="274" spans="1:8" ht="12.75">
-      <c r="A274" s="17"/>
-      <c r="B274" s="17"/>
-      <c r="C274" s="17" t="s">
+      <c r="F273" s="13"/>
+      <c r="G273" s="13"/>
+    </row>
+    <row r="274" spans="1:7" ht="12.75">
+      <c r="A274" s="13"/>
+      <c r="B274" s="13"/>
+      <c r="C274" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D274" s="17">
+      <c r="D274" s="13">
         <v>13.13</v>
       </c>
-      <c r="E274" s="17">
+      <c r="E274" s="13">
         <v>498.87</v>
       </c>
-      <c r="F274" s="17">
+      <c r="F274" s="13">
         <f>D274*E274</f>
         <v>6550.1630999999998</v>
       </c>
-      <c r="G274" s="17" t="s">
+      <c r="G274" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H274" s="16"/>
-    </row>
-    <row r="275" spans="1:8" ht="12.75">
-      <c r="A275" s="12" t="s">
+    </row>
+    <row r="275" spans="1:7" ht="12.75">
+      <c r="A275" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B275" s="3"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="10">
+      <c r="D275" s="8">
         <v>50</v>
       </c>
-      <c r="E275" s="10" t="s">
+      <c r="E275" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F275" s="10">
+      <c r="F275" s="8">
         <f>F270+F272+F274</f>
         <v>7364.2231000000002</v>
       </c>
-      <c r="G275" s="10"/>
-      <c r="H275" s="11"/>
-    </row>
-    <row r="276" spans="1:8" ht="12.75">
-      <c r="A276" s="12" t="s">
+      <c r="G275" s="8"/>
+    </row>
+    <row r="276" spans="1:7" ht="12.75">
+      <c r="A276" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B276" s="3"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="10">
+      <c r="D276" s="8">
         <v>1</v>
       </c>
-      <c r="E276" s="10" t="s">
+      <c r="E276" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F276" s="10">
+      <c r="F276" s="8">
         <f>F275/D275</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="G276" s="10"/>
-      <c r="H276" s="11"/>
-    </row>
-    <row r="277" spans="1:8" ht="12.75">
-      <c r="A277" s="12" t="s">
+      <c r="G276" s="8"/>
+    </row>
+    <row r="277" spans="1:7" ht="12.75">
+      <c r="A277" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
       <c r="D277" s="4"/>
-      <c r="E277" s="10">
+      <c r="E277" s="8">
         <f>F276</f>
         <v>147.28446199999999</v>
       </c>
-      <c r="F277" s="10">
+      <c r="F277" s="8">
         <f>E277*15%</f>
         <v>22.092669300000001</v>
       </c>
-      <c r="G277" s="10"/>
-      <c r="H277" s="11">
-        <f>E277+E267</f>
-        <v>698.39895109999998</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" ht="12.75">
-      <c r="A278" s="20" t="s">
+      <c r="G277" s="8"/>
+    </row>
+    <row r="278" spans="1:7" ht="12.75">
+      <c r="A278" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
       <c r="D278" s="4"/>
-      <c r="E278" s="10"/>
-      <c r="F278" s="21">
+      <c r="E278" s="8"/>
+      <c r="F278" s="17">
         <f>ROUND(F276+F277,2)</f>
         <v>169.38</v>
       </c>
-      <c r="G278" s="10"/>
-      <c r="H278" s="11">
-        <f>F278+F268</f>
-        <v>803.16</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" ht="12.75">
-      <c r="A279" s="22" t="s">
+      <c r="G278" s="8"/>
+    </row>
+    <row r="279" spans="1:7" ht="12.75">
+      <c r="A279" s="18" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="3"/>
@@ -5625,10 +5244,9 @@
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
       <c r="F279" s="4"/>
-      <c r="G279" s="21" t="s">
+      <c r="G279" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H279" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="387">
